--- a/database/event/7557/event_7557_evp_summary.xlsx
+++ b/database/event/7557/event_7557_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -508,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.699400000000001</v>
+        <v>8.591799999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>8.264430000000001</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3.346909915175848</v>
+        <v>3.0495</v>
       </c>
       <c r="E2" t="n">
-        <v>104.109</v>
+        <v>8.591799999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>19.04334736992366</v>
+        <v>3.1935</v>
       </c>
       <c r="G2" t="n">
-        <v>85.06562012851957</v>
+        <v>5.3983</v>
       </c>
       <c r="H2" t="n">
-        <v>19.20253527372097</v>
+        <v>3.1935</v>
       </c>
       <c r="I2" t="n">
-        <v>19.58278349696297</v>
+        <v>2.5884</v>
       </c>
       <c r="J2" t="n">
-        <v>85.06562012851957</v>
+        <v>5.3983</v>
       </c>
       <c r="K2" t="n">
         <v>103</v>
@@ -541,7 +529,7 @@
         <v>122</v>
       </c>
       <c r="M2" t="n">
-        <v>104.6484</v>
+        <v>7.9867</v>
       </c>
       <c r="N2" t="n">
         <v>225</v>
@@ -554,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.5922</v>
+        <v>6.7059</v>
       </c>
       <c r="C3" t="n">
-        <v>7.21259</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.585500547579606</v>
+        <v>2.2877</v>
       </c>
       <c r="E3" t="n">
-        <v>80.4246</v>
+        <v>6.7059</v>
       </c>
       <c r="F3" t="n">
-        <v>32.23135130576114</v>
+        <v>3.0515</v>
       </c>
       <c r="G3" t="n">
-        <v>48.19321920767315</v>
+        <v>3.6543</v>
       </c>
       <c r="H3" t="n">
-        <v>42.97615245206443</v>
+        <v>3.0515</v>
       </c>
       <c r="I3" t="n">
-        <v>46.38020413143587</v>
+        <v>3.0515</v>
       </c>
       <c r="J3" t="n">
-        <v>48.19321920767315</v>
+        <v>3.6543</v>
       </c>
       <c r="K3" t="n">
         <v>109</v>
@@ -587,7 +575,7 @@
         <v>102</v>
       </c>
       <c r="M3" t="n">
-        <v>94.57340000000001</v>
+        <v>6.7058</v>
       </c>
       <c r="N3" t="n">
         <v>211</v>
@@ -600,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.2712</v>
+        <v>6.1346</v>
       </c>
       <c r="C4" t="n">
-        <v>5.95764</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1.849544773011568</v>
+        <v>2.0569</v>
       </c>
       <c r="E4" t="n">
-        <v>57.5319</v>
+        <v>6.1346</v>
       </c>
       <c r="F4" t="n">
-        <v>27.46842162376566</v>
+        <v>2.5166</v>
       </c>
       <c r="G4" t="n">
-        <v>30.06351127567722</v>
+        <v>3.618</v>
       </c>
       <c r="H4" t="n">
-        <v>32.12700047159483</v>
+        <v>2.5166</v>
       </c>
       <c r="I4" t="n">
-        <v>31.17273313085439</v>
+        <v>2.5166</v>
       </c>
       <c r="J4" t="n">
-        <v>30.06351127567722</v>
+        <v>3.618</v>
       </c>
       <c r="K4" t="n">
         <v>98</v>
@@ -633,7 +621,7 @@
         <v>169</v>
       </c>
       <c r="M4" t="n">
-        <v>61.2362</v>
+        <v>6.1346</v>
       </c>
       <c r="N4" t="n">
         <v>267</v>
@@ -646,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.2117</v>
+        <v>5.5449</v>
       </c>
       <c r="C5" t="n">
-        <v>5.901115</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1.820251306290401</v>
+        <v>1.8187</v>
       </c>
       <c r="E5" t="n">
-        <v>56.6207</v>
+        <v>5.5449</v>
       </c>
       <c r="F5" t="n">
-        <v>21.30405525494842</v>
+        <v>3.0604</v>
       </c>
       <c r="G5" t="n">
-        <v>35.31667517652168</v>
+        <v>2.4845</v>
       </c>
       <c r="H5" t="n">
-        <v>22.04619507378895</v>
+        <v>3.0604</v>
       </c>
       <c r="I5" t="n">
-        <v>22.4827533920818</v>
+        <v>2.4805</v>
       </c>
       <c r="J5" t="n">
-        <v>35.31667517652168</v>
+        <v>2.4845</v>
       </c>
       <c r="K5" t="n">
         <v>103</v>
@@ -679,7 +667,7 @@
         <v>122</v>
       </c>
       <c r="M5" t="n">
-        <v>57.7994</v>
+        <v>4.965</v>
       </c>
       <c r="N5" t="n">
         <v>225</v>
@@ -688,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.524</v>
+        <v>4.2196</v>
       </c>
       <c r="C6" t="n">
-        <v>5.2478</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1.502318540079867</v>
+        <v>1.2833</v>
       </c>
       <c r="E6" t="n">
-        <v>46.7311</v>
+        <v>4.2196</v>
       </c>
       <c r="F6" t="n">
-        <v>29.23019810054671</v>
+        <v>4.2064</v>
       </c>
       <c r="G6" t="n">
-        <v>17.50091687577796</v>
+        <v>0.0132</v>
       </c>
       <c r="H6" t="n">
-        <v>35.77741314605943</v>
+        <v>4.3627</v>
       </c>
       <c r="I6" t="n">
-        <v>28.33854506618569</v>
+        <v>3.5361</v>
       </c>
       <c r="J6" t="n">
-        <v>17.50091687577796</v>
+        <v>0.0132</v>
       </c>
       <c r="K6" t="n">
         <v>80</v>
@@ -725,7 +713,7 @@
         <v>52</v>
       </c>
       <c r="M6" t="n">
-        <v>45.8395</v>
+        <v>3.5493</v>
       </c>
       <c r="N6" t="n">
         <v>132</v>
@@ -734,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.4397</v>
+        <v>4.0996</v>
       </c>
       <c r="C7" t="n">
-        <v>4.217715</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1.072282956504208</v>
+        <v>1.2348</v>
       </c>
       <c r="E7" t="n">
-        <v>33.3544</v>
+        <v>4.0996</v>
       </c>
       <c r="F7" t="n">
-        <v>33.23322787724921</v>
+        <v>1.505</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1212018197227742</v>
+        <v>2.5946</v>
       </c>
       <c r="H7" t="n">
-        <v>45.68847367178308</v>
+        <v>1.505</v>
       </c>
       <c r="I7" t="n">
-        <v>36.18889003705591</v>
+        <v>1.505</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1212018197227742</v>
+        <v>2.5946</v>
       </c>
       <c r="K7" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="L7" t="n">
-        <v>52</v>
+        <v>169</v>
       </c>
       <c r="M7" t="n">
-        <v>36.3101</v>
+        <v>4.0996</v>
       </c>
       <c r="N7" t="n">
-        <v>132</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8286</v>
+        <v>3.557</v>
       </c>
       <c r="C8" t="n">
-        <v>3.63717</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8633229703376574</v>
+        <v>1.0156</v>
       </c>
       <c r="E8" t="n">
-        <v>26.8545</v>
+        <v>3.557</v>
       </c>
       <c r="F8" t="n">
-        <v>-14.61942111469549</v>
+        <v>2.169</v>
       </c>
       <c r="G8" t="n">
-        <v>41.47394225134232</v>
+        <v>1.388</v>
       </c>
       <c r="H8" t="n">
-        <v>-14.61942111469549</v>
+        <v>2.169</v>
       </c>
       <c r="I8" t="n">
-        <v>-15.77739506437434</v>
+        <v>1.758</v>
       </c>
       <c r="J8" t="n">
-        <v>41.47394225134232</v>
+        <v>1.388</v>
       </c>
       <c r="K8" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L8" t="n">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="M8" t="n">
-        <v>25.6965</v>
+        <v>3.146</v>
       </c>
       <c r="N8" t="n">
-        <v>211</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9">
@@ -830,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.8091</v>
+        <v>3.5033</v>
       </c>
       <c r="C9" t="n">
-        <v>3.618645</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8570115319041155</v>
+        <v>0.9939</v>
       </c>
       <c r="E9" t="n">
-        <v>26.6582</v>
+        <v>3.5033</v>
       </c>
       <c r="F9" t="n">
-        <v>33.43687641425932</v>
+        <v>3.516</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.778678858288114</v>
+        <v>-0.0127</v>
       </c>
       <c r="H9" t="n">
-        <v>46.26039212479488</v>
+        <v>3.516</v>
       </c>
       <c r="I9" t="n">
-        <v>36.64189475231277</v>
+        <v>2.8498</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.778678858288114</v>
+        <v>-0.0127</v>
       </c>
       <c r="K9" t="n">
         <v>80</v>
@@ -863,7 +851,7 @@
         <v>52</v>
       </c>
       <c r="M9" t="n">
-        <v>29.8632</v>
+        <v>2.8371</v>
       </c>
       <c r="N9" t="n">
         <v>132</v>
@@ -872,277 +860,277 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7892</v>
+        <v>3.4395</v>
       </c>
       <c r="C10" t="n">
-        <v>3.59974</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8505934304452312</v>
+        <v>0.9681</v>
       </c>
       <c r="E10" t="n">
-        <v>26.4586</v>
+        <v>3.4395</v>
       </c>
       <c r="F10" t="n">
-        <v>26.45855611562202</v>
+        <v>2.175</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1.2645</v>
       </c>
       <c r="H10" t="n">
-        <v>30.20501949648192</v>
+        <v>2.175</v>
       </c>
       <c r="I10" t="n">
-        <v>29.00878110058165</v>
+        <v>1.7629</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.2645</v>
       </c>
       <c r="K10" t="n">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M10" t="n">
-        <v>29.0088</v>
+        <v>3.0274</v>
       </c>
       <c r="N10" t="n">
-        <v>97</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.7076</v>
+        <v>3.0832</v>
       </c>
       <c r="C11" t="n">
-        <v>3.522219999999999</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8245163049372484</v>
+        <v>0.8242</v>
       </c>
       <c r="E11" t="n">
-        <v>25.6474</v>
+        <v>3.0832</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.389231821346081</v>
+        <v>3.0832</v>
       </c>
       <c r="G11" t="n">
-        <v>29.03663296693038</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.389231821346081</v>
+        <v>3.0832</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.456345322758875</v>
+        <v>3.0832</v>
       </c>
       <c r="J11" t="n">
-        <v>29.03663296693038</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L11" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>25.5803</v>
+        <v>3.0832</v>
       </c>
       <c r="N11" t="n">
-        <v>225</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.6743</v>
+        <v>2.517</v>
       </c>
       <c r="C12" t="n">
-        <v>3.490585</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.813998023931044</v>
+        <v>0.5954</v>
       </c>
       <c r="E12" t="n">
-        <v>25.3202</v>
+        <v>2.517</v>
       </c>
       <c r="F12" t="n">
-        <v>10.13535472419093</v>
+        <v>2.6238</v>
       </c>
       <c r="G12" t="n">
-        <v>15.18486481114173</v>
+        <v>-0.1068</v>
       </c>
       <c r="H12" t="n">
-        <v>10.13535472419093</v>
+        <v>2.6238</v>
       </c>
       <c r="I12" t="n">
-        <v>10.33605481773926</v>
+        <v>2.6238</v>
       </c>
       <c r="J12" t="n">
-        <v>15.18486481114173</v>
+        <v>-0.1068</v>
       </c>
       <c r="K12" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="L12" t="n">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="M12" t="n">
-        <v>25.5209</v>
+        <v>2.517</v>
       </c>
       <c r="N12" t="n">
-        <v>225</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2177</v>
+        <v>2.2692</v>
       </c>
       <c r="C13" t="n">
-        <v>3.056815</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6755144745505033</v>
+        <v>0.4953</v>
       </c>
       <c r="E13" t="n">
-        <v>21.0126</v>
+        <v>2.2692</v>
       </c>
       <c r="F13" t="n">
-        <v>21.01255075818534</v>
+        <v>1.1574</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.1118</v>
       </c>
       <c r="H13" t="n">
-        <v>21.65709620610033</v>
+        <v>1.1574</v>
       </c>
       <c r="I13" t="n">
-        <v>24.44464324252908</v>
+        <v>1.1574</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1.1118</v>
       </c>
       <c r="K13" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M13" t="n">
-        <v>24.4446</v>
+        <v>2.2692</v>
       </c>
       <c r="N13" t="n">
-        <v>114</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.8612</v>
+        <v>2.0421</v>
       </c>
       <c r="C14" t="n">
-        <v>2.71814</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5747839932823072</v>
+        <v>0.4036</v>
       </c>
       <c r="E14" t="n">
-        <v>17.8792</v>
+        <v>2.0421</v>
       </c>
       <c r="F14" t="n">
-        <v>23.66864441801915</v>
+        <v>-0.7327</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.78941563928188</v>
+        <v>2.7748</v>
       </c>
       <c r="H14" t="n">
-        <v>25.47209239517285</v>
+        <v>-0.7327</v>
       </c>
       <c r="I14" t="n">
-        <v>28.24628067583524</v>
+        <v>-0.7327</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.78941563928188</v>
+        <v>2.7748</v>
       </c>
       <c r="K14" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L14" t="n">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="M14" t="n">
-        <v>22.4569</v>
+        <v>2.0421</v>
       </c>
       <c r="N14" t="n">
-        <v>171</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5932</v>
+        <v>1.9614</v>
       </c>
       <c r="C15" t="n">
-        <v>2.46354</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5030817993328789</v>
+        <v>0.371</v>
       </c>
       <c r="E15" t="n">
-        <v>15.6489</v>
+        <v>1.9614</v>
       </c>
       <c r="F15" t="n">
-        <v>3.599329873506689</v>
+        <v>1.9614</v>
       </c>
       <c r="G15" t="n">
-        <v>12.04953072424059</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.599329873506689</v>
+        <v>1.9614</v>
       </c>
       <c r="I15" t="n">
-        <v>3.884425309031972</v>
+        <v>1.9614</v>
       </c>
       <c r="J15" t="n">
-        <v>12.04953072424059</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="L15" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>15.934</v>
+        <v>1.9614</v>
       </c>
       <c r="N15" t="n">
-        <v>211</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -1152,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0371</v>
+        <v>1.9007</v>
       </c>
       <c r="C16" t="n">
-        <v>1.935245</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3645233198393008</v>
+        <v>0.3465</v>
       </c>
       <c r="E16" t="n">
-        <v>11.3389</v>
+        <v>1.9007</v>
       </c>
       <c r="F16" t="n">
-        <v>11.33886104477971</v>
+        <v>1.9007</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>11.33886104477971</v>
+        <v>1.9007</v>
       </c>
       <c r="I16" t="n">
-        <v>12.79831840697908</v>
+        <v>1.9007</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1185,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>12.7983</v>
+        <v>1.9007</v>
       </c>
       <c r="N16" t="n">
         <v>114</v>
@@ -1194,265 +1182,265 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9346</v>
+        <v>1.7801</v>
       </c>
       <c r="C17" t="n">
-        <v>1.83787</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.340415359997316</v>
+        <v>0.2978</v>
       </c>
       <c r="E17" t="n">
-        <v>10.589</v>
+        <v>1.7801</v>
       </c>
       <c r="F17" t="n">
-        <v>10.18810854324795</v>
+        <v>0.1191</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4008503914502839</v>
+        <v>1.661</v>
       </c>
       <c r="H17" t="n">
-        <v>10.18810854324795</v>
+        <v>0.1191</v>
       </c>
       <c r="I17" t="n">
-        <v>9.885491457804946</v>
+        <v>0.0965</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4008503914502839</v>
+        <v>1.661</v>
       </c>
       <c r="K17" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="L17" t="n">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="M17" t="n">
-        <v>10.2863</v>
+        <v>1.7575</v>
       </c>
       <c r="N17" t="n">
-        <v>267</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2403</v>
+        <v>1.5134</v>
       </c>
       <c r="C18" t="n">
-        <v>1.178285</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1879383348087753</v>
+        <v>0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>5.846</v>
+        <v>1.5134</v>
       </c>
       <c r="F18" t="n">
-        <v>5.846009150589975</v>
+        <v>1.681</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.1676</v>
       </c>
       <c r="H18" t="n">
-        <v>5.846009150589975</v>
+        <v>1.681</v>
       </c>
       <c r="I18" t="n">
-        <v>6.598465773933238</v>
+        <v>1.681</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.1676</v>
       </c>
       <c r="K18" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M18" t="n">
-        <v>6.5985</v>
+        <v>1.5134</v>
       </c>
       <c r="N18" t="n">
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1415</v>
+        <v>1.2997</v>
       </c>
       <c r="C19" t="n">
-        <v>1.084425</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1677019466073845</v>
+        <v>0.1037</v>
       </c>
       <c r="E19" t="n">
-        <v>5.2165</v>
+        <v>1.2997</v>
       </c>
       <c r="F19" t="n">
-        <v>11.90968906610466</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.693152932398609</v>
+        <v>0.3224</v>
       </c>
       <c r="H19" t="n">
-        <v>11.90968906610466</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>11.20218278494992</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.693152932398609</v>
+        <v>0.3224</v>
       </c>
       <c r="K19" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="L19" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="M19" t="n">
-        <v>4.509</v>
+        <v>1.2997</v>
       </c>
       <c r="N19" t="n">
-        <v>133</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0223</v>
+        <v>1.2004</v>
       </c>
       <c r="C20" t="n">
-        <v>0.971185</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1437603598209078</v>
+        <v>0.0636</v>
       </c>
       <c r="E20" t="n">
-        <v>4.4718</v>
+        <v>1.2004</v>
       </c>
       <c r="F20" t="n">
-        <v>3.281602303349516</v>
+        <v>1.2004</v>
       </c>
       <c r="G20" t="n">
-        <v>1.190206919927125</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3.281602303349516</v>
+        <v>1.2004</v>
       </c>
       <c r="I20" t="n">
-        <v>3.639004534407384</v>
+        <v>1.2004</v>
       </c>
       <c r="J20" t="n">
-        <v>1.190206919927125</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L20" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.8292</v>
+        <v>1.2004</v>
       </c>
       <c r="N20" t="n">
-        <v>171</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5562</v>
+        <v>1.0946</v>
       </c>
       <c r="C21" t="n">
-        <v>0.52839</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.05470142051126408</v>
+        <v>0.0208</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7015</v>
+        <v>1.0946</v>
       </c>
       <c r="F21" t="n">
-        <v>13.64004382416263</v>
+        <v>0.22</v>
       </c>
       <c r="G21" t="n">
-        <v>-11.93850163914489</v>
+        <v>0.8746</v>
       </c>
       <c r="H21" t="n">
-        <v>13.64004382416263</v>
+        <v>0.22</v>
       </c>
       <c r="I21" t="n">
-        <v>10.80399510824763</v>
+        <v>0.22</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.93850163914489</v>
+        <v>0.8746</v>
       </c>
       <c r="K21" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="L21" t="n">
-        <v>52</v>
+        <v>169</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1345</v>
+        <v>1.0946</v>
       </c>
       <c r="N21" t="n">
-        <v>132</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4932</v>
+        <v>0.9623</v>
       </c>
       <c r="C22" t="n">
-        <v>0.46854</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.04319384990840349</v>
+        <v>-0.0326</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3436</v>
+        <v>0.9623</v>
       </c>
       <c r="F22" t="n">
-        <v>1.019740096129625</v>
+        <v>1.1693</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3238476400853623</v>
+        <v>-0.207</v>
       </c>
       <c r="H22" t="n">
-        <v>1.019740096129625</v>
+        <v>1.1693</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9591614765575684</v>
+        <v>1.1693</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3238476400853623</v>
+        <v>-0.207</v>
       </c>
       <c r="K22" t="n">
         <v>95</v>
@@ -1461,7 +1449,7 @@
         <v>38</v>
       </c>
       <c r="M22" t="n">
-        <v>1.283</v>
+        <v>0.9623</v>
       </c>
       <c r="N22" t="n">
         <v>133</v>
@@ -1470,35 +1458,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.469</v>
+        <v>0.8855</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.4455499999999999</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1331886886357205</v>
+        <v>-0.0636</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.143</v>
+        <v>0.8855</v>
       </c>
       <c r="F23" t="n">
-        <v>2.898418687281105</v>
+        <v>0.5506</v>
       </c>
       <c r="G23" t="n">
-        <v>-7.041385545595237</v>
+        <v>0.3349</v>
       </c>
       <c r="H23" t="n">
-        <v>2.898418687281105</v>
+        <v>0.5506</v>
       </c>
       <c r="I23" t="n">
-        <v>2.726235398927772</v>
+        <v>0.5506</v>
       </c>
       <c r="J23" t="n">
-        <v>-7.041385545595237</v>
+        <v>0.3349</v>
       </c>
       <c r="K23" t="n">
         <v>95</v>
@@ -1507,7 +1495,7 @@
         <v>38</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.3152</v>
+        <v>0.8855</v>
       </c>
       <c r="N23" t="n">
         <v>133</v>
@@ -1516,265 +1504,265 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.0533</v>
+        <v>0.5413</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.000635</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2544078558384615</v>
+        <v>-0.2027</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.9136</v>
+        <v>0.5413</v>
       </c>
       <c r="F24" t="n">
-        <v>-17.20425374858601</v>
+        <v>0.9825</v>
       </c>
       <c r="G24" t="n">
-        <v>9.290643921581321</v>
+        <v>-0.4412</v>
       </c>
       <c r="H24" t="n">
-        <v>-17.16202944576959</v>
+        <v>0.9825</v>
       </c>
       <c r="I24" t="n">
-        <v>-18.52139811474144</v>
+        <v>0.9825</v>
       </c>
       <c r="J24" t="n">
-        <v>9.290643921581321</v>
+        <v>-0.4412</v>
       </c>
       <c r="K24" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L24" t="n">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="M24" t="n">
-        <v>-9.2308</v>
+        <v>0.5413000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>211</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-1.1429</v>
+        <v>0.3202</v>
       </c>
       <c r="C25" t="n">
-        <v>-1.085755</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2741133089513432</v>
+        <v>-0.292</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.5266</v>
+        <v>0.3202</v>
       </c>
       <c r="F25" t="n">
-        <v>1.776029528562995</v>
+        <v>-0.4371</v>
       </c>
       <c r="G25" t="n">
-        <v>-10.3025971075433</v>
+        <v>0.7573</v>
       </c>
       <c r="H25" t="n">
-        <v>1.776029528562995</v>
+        <v>-0.4371</v>
       </c>
       <c r="I25" t="n">
-        <v>1.969458487119361</v>
+        <v>-0.4371</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.3025971075433</v>
+        <v>0.7573</v>
       </c>
       <c r="K25" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="L25" t="n">
-        <v>59</v>
+        <v>169</v>
       </c>
       <c r="M25" t="n">
-        <v>-8.3331</v>
+        <v>0.3202</v>
       </c>
       <c r="N25" t="n">
-        <v>171</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.8218</v>
+        <v>0.2431</v>
       </c>
       <c r="C26" t="n">
-        <v>-1.73071</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4337676879157147</v>
+        <v>-0.3232</v>
       </c>
       <c r="E26" t="n">
-        <v>-13.4928</v>
+        <v>0.2431</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.141389868939664</v>
+        <v>0.5855</v>
       </c>
       <c r="G26" t="n">
-        <v>-12.35138623427354</v>
+        <v>-0.3424</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.141389868939664</v>
+        <v>0.5855</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.107487199565219</v>
+        <v>0.4746</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.35138623427354</v>
+        <v>-0.3424</v>
       </c>
       <c r="K26" t="n">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="L26" t="n">
-        <v>169</v>
+        <v>52</v>
       </c>
       <c r="M26" t="n">
-        <v>-13.4589</v>
+        <v>0.1322</v>
       </c>
       <c r="N26" t="n">
-        <v>267</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.8283</v>
+        <v>-0.0636</v>
       </c>
       <c r="C27" t="n">
-        <v>-1.736885</v>
+        <v>-0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4353886211749335</v>
+        <v>-0.4471</v>
       </c>
       <c r="E27" t="n">
-        <v>-13.5432</v>
+        <v>-0.0636</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.095579254764061</v>
+        <v>-0.0636</v>
       </c>
       <c r="G27" t="n">
-        <v>-7.447617592442273</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-6.095579254764061</v>
+        <v>-0.0636</v>
       </c>
       <c r="I27" t="n">
-        <v>-6.759454223104703</v>
+        <v>-0.0636</v>
       </c>
       <c r="J27" t="n">
-        <v>-7.447617592442273</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="L27" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-14.2071</v>
+        <v>-0.0636</v>
       </c>
       <c r="N27" t="n">
-        <v>171</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-2.0754</v>
+        <v>-0.204</v>
       </c>
       <c r="C28" t="n">
-        <v>-1.97163</v>
+        <v>-0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4984240207063884</v>
+        <v>-0.5038</v>
       </c>
       <c r="E28" t="n">
-        <v>-15.504</v>
+        <v>-0.204</v>
       </c>
       <c r="F28" t="n">
-        <v>-15.50397575294119</v>
+        <v>-0.7369</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.5329</v>
       </c>
       <c r="H28" t="n">
-        <v>-15.46897010280852</v>
+        <v>-0.7369</v>
       </c>
       <c r="I28" t="n">
-        <v>-17.46002566059575</v>
+        <v>-0.7369</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.5329</v>
       </c>
       <c r="K28" t="n">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="M28" t="n">
-        <v>-17.46</v>
+        <v>-0.204</v>
       </c>
       <c r="N28" t="n">
-        <v>114</v>
+        <v>267</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-2.3861</v>
+        <v>-0.2858</v>
       </c>
       <c r="C29" t="n">
-        <v>-2.266795</v>
+        <v>-0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5816339894165762</v>
+        <v>-0.5368000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>-18.0923</v>
+        <v>-0.2858</v>
       </c>
       <c r="F29" t="n">
-        <v>-13.16777553721733</v>
+        <v>-0.1751</v>
       </c>
       <c r="G29" t="n">
-        <v>-4.924529196051455</v>
+        <v>-0.1107</v>
       </c>
       <c r="H29" t="n">
-        <v>-13.16777553721733</v>
+        <v>-0.1751</v>
       </c>
       <c r="I29" t="n">
-        <v>-14.60188970463703</v>
+        <v>-0.1751</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.924529196051455</v>
+        <v>-0.1107</v>
       </c>
       <c r="K29" t="n">
         <v>112</v>
@@ -1783,7 +1771,7 @@
         <v>59</v>
       </c>
       <c r="M29" t="n">
-        <v>-19.5264</v>
+        <v>-0.2858</v>
       </c>
       <c r="N29" t="n">
         <v>171</v>
@@ -1792,308 +1780,308 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.6446</v>
+        <v>-0.4115</v>
       </c>
       <c r="C30" t="n">
-        <v>-2.51237</v>
+        <v>-0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6543484866723301</v>
+        <v>-0.5876</v>
       </c>
       <c r="E30" t="n">
-        <v>-20.3542</v>
+        <v>-0.4115</v>
       </c>
       <c r="F30" t="n">
-        <v>-20.35416161717812</v>
+        <v>-0.7056</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.2941</v>
       </c>
       <c r="H30" t="n">
-        <v>-20.80336554959746</v>
+        <v>-0.7056</v>
       </c>
       <c r="I30" t="n">
-        <v>-19.97946988426687</v>
+        <v>-0.7056</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.2941</v>
       </c>
       <c r="K30" t="n">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M30" t="n">
-        <v>-19.9795</v>
+        <v>-0.4115</v>
       </c>
       <c r="N30" t="n">
-        <v>97</v>
+        <v>211</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.6976</v>
+        <v>-0.6786</v>
       </c>
       <c r="C31" t="n">
-        <v>-2.56272</v>
+        <v>-0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6696576671139264</v>
+        <v>-0.6955</v>
       </c>
       <c r="E31" t="n">
-        <v>-20.8304</v>
+        <v>-0.6786</v>
       </c>
       <c r="F31" t="n">
-        <v>-21.14069998091118</v>
+        <v>-0.6786</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3103310532837735</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-21.82729606766714</v>
+        <v>-0.6786</v>
       </c>
       <c r="I31" t="n">
-        <v>-22.2595197521754</v>
+        <v>-0.6786</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3103310532837735</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="L31" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-21.9492</v>
+        <v>-0.6786</v>
       </c>
       <c r="N31" t="n">
-        <v>225</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-3.0615</v>
+        <v>-0.9315</v>
       </c>
       <c r="C32" t="n">
-        <v>-2.908425</v>
+        <v>-0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7787605590021139</v>
+        <v>-0.7977</v>
       </c>
       <c r="E32" t="n">
-        <v>-24.2241</v>
+        <v>-0.9315</v>
       </c>
       <c r="F32" t="n">
-        <v>-5.224961816675203</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>-18.99916126431928</v>
+        <v>-1</v>
       </c>
       <c r="H32" t="n">
-        <v>-5.224961816675203</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>-4.138583617168478</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>-18.99916126431928</v>
+        <v>-1</v>
       </c>
       <c r="K32" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="L32" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="M32" t="n">
-        <v>-23.1377</v>
+        <v>-0.9315</v>
       </c>
       <c r="N32" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-3.1241</v>
+        <v>-1.0009</v>
       </c>
       <c r="C33" t="n">
-        <v>-2.967895</v>
+        <v>-0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7982268045332329</v>
+        <v>-0.8257</v>
       </c>
       <c r="E33" t="n">
-        <v>-24.8296</v>
+        <v>-1.0009</v>
       </c>
       <c r="F33" t="n">
-        <v>-7.879159664252018</v>
+        <v>-1.0009</v>
       </c>
       <c r="G33" t="n">
-        <v>-16.95048037856052</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-7.879159664252018</v>
+        <v>-1.0009</v>
       </c>
       <c r="I33" t="n">
-        <v>-7.411090773306354</v>
+        <v>-1.0009</v>
       </c>
       <c r="J33" t="n">
-        <v>-16.95048037856052</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L33" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-24.3616</v>
+        <v>-1.0009</v>
       </c>
       <c r="N33" t="n">
-        <v>133</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-3.3691</v>
+        <v>-1.0025</v>
       </c>
       <c r="C34" t="n">
-        <v>-3.200645</v>
+        <v>-0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8765118722373327</v>
+        <v>-0.8264</v>
       </c>
       <c r="E34" t="n">
-        <v>-27.2648</v>
+        <v>-1.0025</v>
       </c>
       <c r="F34" t="n">
-        <v>-27.26477507057779</v>
+        <v>-1.0025</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-31.7298173590458</v>
+        <v>-1.0025</v>
       </c>
       <c r="I34" t="n">
-        <v>-35.81385325674476</v>
+        <v>-1.0025</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-35.8139</v>
+        <v>-1.0025</v>
       </c>
       <c r="N34" t="n">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-3.4033</v>
+        <v>-1.1192</v>
       </c>
       <c r="C35" t="n">
-        <v>-3.233135</v>
+        <v>-0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8876946014785546</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>-27.6126</v>
+        <v>-1.1192</v>
       </c>
       <c r="F35" t="n">
-        <v>-27.61262500518145</v>
+        <v>-1.0649</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.0543</v>
       </c>
       <c r="H35" t="n">
-        <v>-32.4112513874021</v>
+        <v>-1.0649</v>
       </c>
       <c r="I35" t="n">
-        <v>-31.12763747106935</v>
+        <v>-1.0649</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.0543</v>
       </c>
       <c r="K35" t="n">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M35" t="n">
-        <v>-31.1276</v>
+        <v>-1.1192</v>
       </c>
       <c r="N35" t="n">
-        <v>97</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-3.4408</v>
+        <v>-1.2644</v>
       </c>
       <c r="C36" t="n">
-        <v>-3.26876</v>
+        <v>-0</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9000605515732307</v>
+        <v>-0.9322</v>
       </c>
       <c r="E36" t="n">
-        <v>-27.9973</v>
+        <v>-1.2644</v>
       </c>
       <c r="F36" t="n">
-        <v>-27.99728020329615</v>
+        <v>-1.2644</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-33.18183852144507</v>
+        <v>-1.2644</v>
       </c>
       <c r="I36" t="n">
-        <v>-31.86770630277398</v>
+        <v>-1.2644</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2105,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-31.8677</v>
+        <v>-1.2644</v>
       </c>
       <c r="N36" t="n">
         <v>97</v>
@@ -2114,139 +2102,139 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-3.4874</v>
+        <v>-1.6564</v>
       </c>
       <c r="C37" t="n">
-        <v>-3.31303</v>
+        <v>-0</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9155173026576134</v>
+        <v>-1.0905</v>
       </c>
       <c r="E37" t="n">
-        <v>-28.4781</v>
+        <v>-1.6564</v>
       </c>
       <c r="F37" t="n">
-        <v>-28.47807784561661</v>
+        <v>-1.6564</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-34.170842501446</v>
+        <v>-1.6564</v>
       </c>
       <c r="I37" t="n">
-        <v>-32.81754180831942</v>
+        <v>-1.6564</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-32.8175</v>
+        <v>-1.6564</v>
       </c>
       <c r="N37" t="n">
-        <v>97</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-3.7634</v>
+        <v>-2.4414</v>
       </c>
       <c r="C38" t="n">
-        <v>-3.57523</v>
+        <v>-0</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.009708234789413</v>
+        <v>-1.4076</v>
       </c>
       <c r="E38" t="n">
-        <v>-31.408</v>
+        <v>-2.4414</v>
       </c>
       <c r="F38" t="n">
-        <v>-16.72027207769275</v>
+        <v>-1.4414</v>
       </c>
       <c r="G38" t="n">
-        <v>-14.6877085560132</v>
+        <v>-1</v>
       </c>
       <c r="H38" t="n">
-        <v>-16.66206910782569</v>
+        <v>-1.4414</v>
       </c>
       <c r="I38" t="n">
-        <v>-16.16715616402889</v>
+        <v>-1.4414</v>
       </c>
       <c r="J38" t="n">
-        <v>-14.6877085560132</v>
+        <v>-1</v>
       </c>
       <c r="K38" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L38" t="n">
-        <v>169</v>
+        <v>38</v>
       </c>
       <c r="M38" t="n">
-        <v>-30.8549</v>
+        <v>-2.4414</v>
       </c>
       <c r="N38" t="n">
-        <v>267</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-3.9148</v>
+        <v>-2.4801</v>
       </c>
       <c r="C39" t="n">
-        <v>-3.71906</v>
+        <v>-0</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.063307019018204</v>
+        <v>-1.4233</v>
       </c>
       <c r="E39" t="n">
-        <v>-33.0752</v>
+        <v>-2.4801</v>
       </c>
       <c r="F39" t="n">
-        <v>-11.7247945013144</v>
+        <v>-1.5202</v>
       </c>
       <c r="G39" t="n">
-        <v>-21.35042971726651</v>
+        <v>-0.9599</v>
       </c>
       <c r="H39" t="n">
-        <v>-11.7247945013144</v>
+        <v>-1.5202</v>
       </c>
       <c r="I39" t="n">
-        <v>-11.37653327850308</v>
+        <v>-1.2322</v>
       </c>
       <c r="J39" t="n">
-        <v>-21.35042971726651</v>
+        <v>-0.9599</v>
       </c>
       <c r="K39" t="n">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="L39" t="n">
-        <v>169</v>
+        <v>52</v>
       </c>
       <c r="M39" t="n">
-        <v>-32.727</v>
+        <v>-2.1921</v>
       </c>
       <c r="N39" t="n">
-        <v>267</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40">
@@ -2256,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-4.2588</v>
+        <v>-2.9542</v>
       </c>
       <c r="C40" t="n">
-        <v>-4.045859999999999</v>
+        <v>-0</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.190530013739822</v>
+        <v>-1.6148</v>
       </c>
       <c r="E40" t="n">
-        <v>-37.0326</v>
+        <v>-2.9542</v>
       </c>
       <c r="F40" t="n">
-        <v>-23.1043165013104</v>
+        <v>-1.3329</v>
       </c>
       <c r="G40" t="n">
-        <v>-13.92830572265769</v>
+        <v>-1.6213</v>
       </c>
       <c r="H40" t="n">
-        <v>-24.60896664584993</v>
+        <v>-1.3329</v>
       </c>
       <c r="I40" t="n">
-        <v>-26.55819172670934</v>
+        <v>-1.3329</v>
       </c>
       <c r="J40" t="n">
-        <v>-13.92830572265769</v>
+        <v>-1.6213</v>
       </c>
       <c r="K40" t="n">
         <v>109</v>
@@ -2289,7 +2277,7 @@
         <v>102</v>
       </c>
       <c r="M40" t="n">
-        <v>-40.4865</v>
+        <v>-2.9542</v>
       </c>
       <c r="N40" t="n">
         <v>211</v>
@@ -2298,47 +2286,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.7429</v>
+        <v>-3.0362</v>
       </c>
       <c r="C41" t="n">
-        <v>-4.505755</v>
+        <v>-0</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.38292367820936</v>
+        <v>-1.6479</v>
       </c>
       <c r="E41" t="n">
-        <v>-43.0172</v>
+        <v>-3.0362</v>
       </c>
       <c r="F41" t="n">
-        <v>-24.4275817507075</v>
+        <v>-3.0826</v>
       </c>
       <c r="G41" t="n">
-        <v>-18.58963709187413</v>
+        <v>0.0464</v>
       </c>
       <c r="H41" t="n">
-        <v>-26.68079237749519</v>
+        <v>-3.0826</v>
       </c>
       <c r="I41" t="n">
-        <v>-25.09579481051528</v>
+        <v>-2.4985</v>
       </c>
       <c r="J41" t="n">
-        <v>-18.58963709187413</v>
+        <v>0.0464</v>
       </c>
       <c r="K41" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="L41" t="n">
-        <v>38</v>
+        <v>122</v>
       </c>
       <c r="M41" t="n">
-        <v>-43.6854</v>
+        <v>-2.4521</v>
       </c>
       <c r="N41" t="n">
-        <v>133</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -2356,52 +2344,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -2441,10 +2429,10 @@
         <v>1.43</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7585428171663797</v>
+        <v>1.0668</v>
       </c>
       <c r="J2" t="n">
-        <v>15.17085634332759</v>
+        <v>21.336</v>
       </c>
     </row>
     <row r="3">
@@ -2481,10 +2469,10 @@
         <v>1.43</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7585428171663797</v>
+        <v>1.0668</v>
       </c>
       <c r="J3" t="n">
-        <v>15.17085634332759</v>
+        <v>21.336</v>
       </c>
     </row>
     <row r="4">
@@ -2521,10 +2509,10 @@
         <v>1.39</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6853265386966185</v>
+        <v>0.9815</v>
       </c>
       <c r="J4" t="n">
-        <v>13.70653077393237</v>
+        <v>19.63</v>
       </c>
     </row>
     <row r="5">
@@ -2561,10 +2549,10 @@
         <v>1.05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07732473428362643</v>
+        <v>0.0737</v>
       </c>
       <c r="J5" t="n">
-        <v>1.546494685672529</v>
+        <v>1.474</v>
       </c>
     </row>
     <row r="6">
@@ -2601,10 +2589,10 @@
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2747817432236427</v>
+        <v>-0.6879</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.495634864472855</v>
+        <v>-13.758</v>
       </c>
     </row>
     <row r="7">
@@ -2641,10 +2629,10 @@
         <v>1.24</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1926132493434612</v>
+        <v>0.4667</v>
       </c>
       <c r="J7" t="n">
-        <v>3.852264986869225</v>
+        <v>9.334</v>
       </c>
     </row>
     <row r="8">
@@ -2681,10 +2669,10 @@
         <v>1.03</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1526476957616162</v>
+        <v>0.1258</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.052953915232323</v>
+        <v>2.516</v>
       </c>
     </row>
     <row r="9">
@@ -2721,10 +2709,10 @@
         <v>0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3440536544950932</v>
+        <v>-0.2342</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.881073089901864</v>
+        <v>-4.684</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2749,10 @@
         <v>0.84</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3975146701108343</v>
+        <v>-0.3014</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.950293402216686</v>
+        <v>-6.028</v>
       </c>
     </row>
     <row r="11">
@@ -2801,10 +2789,10 @@
         <v>0.63</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6816956497939453</v>
+        <v>-0.5961</v>
       </c>
       <c r="J11" t="n">
-        <v>-13.63391299587891</v>
+        <v>-11.922</v>
       </c>
     </row>
     <row r="12">
@@ -2841,10 +2829,10 @@
         <v>2.02</v>
       </c>
       <c r="I12" t="n">
-        <v>1.638975042264319</v>
+        <v>2.0114</v>
       </c>
       <c r="J12" t="n">
-        <v>29.50155076075773</v>
+        <v>36.2052</v>
       </c>
     </row>
     <row r="13">
@@ -2881,10 +2869,10 @@
         <v>1.31</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4478279261779671</v>
+        <v>0.6748</v>
       </c>
       <c r="J13" t="n">
-        <v>8.060902671203408</v>
+        <v>12.1464</v>
       </c>
     </row>
     <row r="14">
@@ -2921,10 +2909,10 @@
         <v>1.28</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3930654228740048</v>
+        <v>0.6056</v>
       </c>
       <c r="J14" t="n">
-        <v>7.075177611732086</v>
+        <v>10.9008</v>
       </c>
     </row>
     <row r="15">
@@ -2961,10 +2949,10 @@
         <v>1.23</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3006225406122752</v>
+        <v>0.4892</v>
       </c>
       <c r="J15" t="n">
-        <v>5.411205731020954</v>
+        <v>8.8056</v>
       </c>
     </row>
     <row r="16">
@@ -3001,10 +2989,10 @@
         <v>1.14</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1334154165155585</v>
+        <v>0.2697</v>
       </c>
       <c r="J16" t="n">
-        <v>2.401477497280054</v>
+        <v>4.8546</v>
       </c>
     </row>
     <row r="17">
@@ -3041,10 +3029,10 @@
         <v>1.28</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1822524765664347</v>
+        <v>0.5454</v>
       </c>
       <c r="J17" t="n">
-        <v>3.280544578195824</v>
+        <v>9.8172</v>
       </c>
     </row>
     <row r="18">
@@ -3081,10 +3069,10 @@
         <v>1.27</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1630379429100989</v>
+        <v>0.5321</v>
       </c>
       <c r="J18" t="n">
-        <v>2.934682972381781</v>
+        <v>9.5778</v>
       </c>
     </row>
     <row r="19">
@@ -3121,10 +3109,10 @@
         <v>0.68</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6688041282677093</v>
+        <v>-0.5158</v>
       </c>
       <c r="J19" t="n">
-        <v>-12.03847430881877</v>
+        <v>-9.2844</v>
       </c>
     </row>
     <row r="20">
@@ -3161,10 +3149,10 @@
         <v>0.59</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7869512976550918</v>
+        <v>-0.6339</v>
       </c>
       <c r="J20" t="n">
-        <v>-14.16512335779165</v>
+        <v>-11.4102</v>
       </c>
     </row>
     <row r="21">
@@ -3201,10 +3189,10 @@
         <v>0.47</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9392445785008036</v>
+        <v>-0.7804</v>
       </c>
       <c r="J21" t="n">
-        <v>-16.90640241301447</v>
+        <v>-14.0472</v>
       </c>
     </row>
     <row r="22">
@@ -3241,10 +3229,10 @@
         <v>2.28</v>
       </c>
       <c r="I22" t="n">
-        <v>2.07236080405586</v>
+        <v>2.2791</v>
       </c>
       <c r="J22" t="n">
-        <v>41.4472160811172</v>
+        <v>45.582</v>
       </c>
     </row>
     <row r="23">
@@ -3281,10 +3269,10 @@
         <v>1.35</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5996436367049318</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>11.99287273409864</v>
+        <v>17.712</v>
       </c>
     </row>
     <row r="24">
@@ -3321,10 +3309,10 @@
         <v>1.08</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1221971495398051</v>
+        <v>0.1608</v>
       </c>
       <c r="J24" t="n">
-        <v>2.443942990796102</v>
+        <v>3.216</v>
       </c>
     </row>
     <row r="25">
@@ -3361,10 +3349,10 @@
         <v>0.91</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.154199723816878</v>
+        <v>-0.4593</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.08399447633756</v>
+        <v>-9.186</v>
       </c>
     </row>
     <row r="26">
@@ -3401,10 +3389,10 @@
         <v>0.57</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6351629487521533</v>
+        <v>-1.2297</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.70325897504307</v>
+        <v>-24.594</v>
       </c>
     </row>
     <row r="27">
@@ -3441,10 +3429,10 @@
         <v>1.66</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9740070836800305</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>19.48014167360061</v>
+        <v>19.466</v>
       </c>
     </row>
     <row r="28">
@@ -3481,10 +3469,10 @@
         <v>0.96</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2426947462447083</v>
+        <v>-0.0582</v>
       </c>
       <c r="J28" t="n">
-        <v>-4.853894924894166</v>
+        <v>-1.164</v>
       </c>
     </row>
     <row r="29">
@@ -3521,10 +3509,10 @@
         <v>0.78</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4730565099871384</v>
+        <v>-0.3896</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.461130199742767</v>
+        <v>-7.792</v>
       </c>
     </row>
     <row r="30">
@@ -3561,10 +3549,10 @@
         <v>0.73</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5411636215823501</v>
+        <v>-0.4611</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.823272431647</v>
+        <v>-9.222</v>
       </c>
     </row>
     <row r="31">
@@ -3601,10 +3589,10 @@
         <v>0.43</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.9297127212821021</v>
+        <v>-0.8337</v>
       </c>
       <c r="J31" t="n">
-        <v>-18.59425442564204</v>
+        <v>-16.674</v>
       </c>
     </row>
     <row r="32">
@@ -3641,10 +3629,10 @@
         <v>1.19</v>
       </c>
       <c r="I32" t="n">
-        <v>0.04805858510861599</v>
+        <v>0.4331</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8650545319550879</v>
+        <v>7.7958</v>
       </c>
     </row>
     <row r="33">
@@ -3681,10 +3669,10 @@
         <v>0.86</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3598548989747538</v>
+        <v>-0.2061</v>
       </c>
       <c r="J33" t="n">
-        <v>-6.477388181545567</v>
+        <v>-3.7098</v>
       </c>
     </row>
     <row r="34">
@@ -3721,10 +3709,10 @@
         <v>0.8</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4202542084833671</v>
+        <v>-0.3253</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.564575752700609</v>
+        <v>-5.8554</v>
       </c>
     </row>
     <row r="35">
@@ -3761,10 +3749,10 @@
         <v>0.67</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5708139249966908</v>
+        <v>-0.5212</v>
       </c>
       <c r="J35" t="n">
-        <v>-10.27465064994044</v>
+        <v>-9.381600000000001</v>
       </c>
     </row>
     <row r="36">
@@ -3801,10 +3789,10 @@
         <v>0.62</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6293848510343564</v>
+        <v>-0.5884</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.32892731861842</v>
+        <v>-10.5912</v>
       </c>
     </row>
     <row r="37">
@@ -3841,10 +3829,10 @@
         <v>1.74</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8775204429154353</v>
+        <v>1.5968</v>
       </c>
       <c r="J37" t="n">
-        <v>15.79536797247784</v>
+        <v>28.7424</v>
       </c>
     </row>
     <row r="38">
@@ -3881,10 +3869,10 @@
         <v>1.7</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8291568369687644</v>
+        <v>1.5241</v>
       </c>
       <c r="J38" t="n">
-        <v>14.92482306543776</v>
+        <v>27.4338</v>
       </c>
     </row>
     <row r="39">
@@ -3921,10 +3909,10 @@
         <v>1.36</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4111763664224471</v>
+        <v>0.8071</v>
       </c>
       <c r="J39" t="n">
-        <v>7.401174595604049</v>
+        <v>14.5278</v>
       </c>
     </row>
     <row r="40">
@@ -3961,10 +3949,10 @@
         <v>1.19</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1936968594662322</v>
+        <v>0.4014</v>
       </c>
       <c r="J40" t="n">
-        <v>3.48654347039218</v>
+        <v>7.2252</v>
       </c>
     </row>
     <row r="41">
@@ -4001,10 +3989,10 @@
         <v>0.88</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2298310320159161</v>
+        <v>-0.5717</v>
       </c>
       <c r="J41" t="n">
-        <v>-4.13695857628649</v>
+        <v>-10.2906</v>
       </c>
     </row>
     <row r="42">
@@ -4041,10 +4029,10 @@
         <v>2.32</v>
       </c>
       <c r="I42" t="n">
-        <v>1.788449852211331</v>
+        <v>1.4473</v>
       </c>
       <c r="J42" t="n">
-        <v>28.61519763538129</v>
+        <v>23.1568</v>
       </c>
     </row>
     <row r="43">
@@ -4081,10 +4069,10 @@
         <v>2.01</v>
       </c>
       <c r="I43" t="n">
-        <v>1.412078623508877</v>
+        <v>1.165</v>
       </c>
       <c r="J43" t="n">
-        <v>22.59325797614204</v>
+        <v>18.64</v>
       </c>
     </row>
     <row r="44">
@@ -4121,10 +4109,10 @@
         <v>1.19</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2422526583396716</v>
+        <v>0.2155</v>
       </c>
       <c r="J44" t="n">
-        <v>3.876042533434746</v>
+        <v>3.448</v>
       </c>
     </row>
     <row r="45">
@@ -4161,10 +4149,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.06970175641025214</v>
+        <v>-0.1884</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.115228102564034</v>
+        <v>-3.0144</v>
       </c>
     </row>
     <row r="46">
@@ -4201,10 +4189,10 @@
         <v>0.79</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2721499118968602</v>
+        <v>-0.4608</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.354398590349764</v>
+        <v>-7.3728</v>
       </c>
     </row>
     <row r="47">
@@ -4241,10 +4229,10 @@
         <v>0.98</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.2605877970745041</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>-4.169404753192065</v>
+        <v>1.0032</v>
       </c>
     </row>
     <row r="48">
@@ -4281,10 +4269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.5022285199229404</v>
+        <v>-0.243</v>
       </c>
       <c r="J48" t="n">
-        <v>-8.035656318767046</v>
+        <v>-3.888</v>
       </c>
     </row>
     <row r="49">
@@ -4321,10 +4309,10 @@
         <v>0.75</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.5809654992374415</v>
+        <v>-0.3455</v>
       </c>
       <c r="J49" t="n">
-        <v>-9.295447987799063</v>
+        <v>-5.528</v>
       </c>
     </row>
     <row r="50">
@@ -4361,10 +4349,10 @@
         <v>0.6</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.7755198973812727</v>
+        <v>-0.5898</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.40831835810036</v>
+        <v>-9.4368</v>
       </c>
     </row>
     <row r="51">
@@ -4401,10 +4389,10 @@
         <v>0.55</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8444851126452061</v>
+        <v>-0.657</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.5117618023233</v>
+        <v>-10.512</v>
       </c>
     </row>
     <row r="52">
@@ -4441,10 +4429,10 @@
         <v>1.24</v>
       </c>
       <c r="I52" t="n">
-        <v>0.105618055387585</v>
+        <v>0.501</v>
       </c>
       <c r="J52" t="n">
-        <v>1.901124996976529</v>
+        <v>9.018000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -4481,10 +4469,10 @@
         <v>1.12</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.06148415929164185</v>
+        <v>0.3245</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.106714867249553</v>
+        <v>5.841</v>
       </c>
     </row>
     <row r="54">
@@ -4521,10 +4509,10 @@
         <v>0.64</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.6190627132111582</v>
+        <v>-0.5634</v>
       </c>
       <c r="J54" t="n">
-        <v>-11.14312883780085</v>
+        <v>-10.1412</v>
       </c>
     </row>
     <row r="55">
@@ -4561,10 +4549,10 @@
         <v>0.6</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.6655186273088013</v>
+        <v>-0.6159</v>
       </c>
       <c r="J55" t="n">
-        <v>-11.97933529155842</v>
+        <v>-11.0862</v>
       </c>
     </row>
     <row r="56">
@@ -4601,10 +4589,10 @@
         <v>0.57</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7000307304340887</v>
+        <v>-0.6542</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.6005531478136</v>
+        <v>-11.7756</v>
       </c>
     </row>
     <row r="57">
@@ -4641,10 +4629,10 @@
         <v>1.74</v>
       </c>
       <c r="I57" t="n">
-        <v>0.852318251278279</v>
+        <v>1.5857</v>
       </c>
       <c r="J57" t="n">
-        <v>15.34172852300902</v>
+        <v>28.5426</v>
       </c>
     </row>
     <row r="58">
@@ -4681,10 +4669,10 @@
         <v>1.55</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6154656794504366</v>
+        <v>1.2263</v>
       </c>
       <c r="J58" t="n">
-        <v>11.07838223010786</v>
+        <v>22.0734</v>
       </c>
     </row>
     <row r="59">
@@ -4721,10 +4709,10 @@
         <v>1.5</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5518507517169123</v>
+        <v>1.1242</v>
       </c>
       <c r="J59" t="n">
-        <v>9.933313530904423</v>
+        <v>20.2356</v>
       </c>
     </row>
     <row r="60">
@@ -4761,10 +4749,10 @@
         <v>1.27</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2725378090794897</v>
+        <v>0.5809</v>
       </c>
       <c r="J60" t="n">
-        <v>4.905680563430815</v>
+        <v>10.4562</v>
       </c>
     </row>
     <row r="61">
@@ -4801,10 +4789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1744601404964168</v>
+        <v>-0.412</v>
       </c>
       <c r="J61" t="n">
-        <v>-3.140282528935502</v>
+        <v>-7.416</v>
       </c>
     </row>
     <row r="62">
@@ -4841,10 +4829,10 @@
         <v>2.26</v>
       </c>
       <c r="I62" t="n">
-        <v>1.638686731492054</v>
+        <v>2.1469</v>
       </c>
       <c r="J62" t="n">
-        <v>37.68979482431724</v>
+        <v>49.3787</v>
       </c>
     </row>
     <row r="63">
@@ -4881,10 +4869,10 @@
         <v>1.08</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.06767540767679787</v>
+        <v>0.1386</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.556534376566351</v>
+        <v>3.1878</v>
       </c>
     </row>
     <row r="64">
@@ -4921,10 +4909,10 @@
         <v>1.08</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.06767540767679787</v>
+        <v>0.1386</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.556534376566351</v>
+        <v>3.1878</v>
       </c>
     </row>
     <row r="65">
@@ -4961,10 +4949,10 @@
         <v>1.05</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1019002082279427</v>
+        <v>0.0477</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.343704789242683</v>
+        <v>1.0971</v>
       </c>
     </row>
     <row r="66">
@@ -5001,10 +4989,10 @@
         <v>1.02</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.135559518631</v>
+        <v>-0.0561</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.117868928513001</v>
+        <v>-1.2903</v>
       </c>
     </row>
     <row r="67">
@@ -5041,10 +5029,10 @@
         <v>1.7</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8956807968662628</v>
+        <v>0.9899</v>
       </c>
       <c r="J67" t="n">
-        <v>20.60065832792404</v>
+        <v>22.7677</v>
       </c>
     </row>
     <row r="68">
@@ -5081,10 +5069,10 @@
         <v>1.35</v>
       </c>
       <c r="I68" t="n">
-        <v>0.34524371360853</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="J68" t="n">
-        <v>7.94060541299619</v>
+        <v>13.5746</v>
       </c>
     </row>
     <row r="69">
@@ -5121,10 +5109,10 @@
         <v>0.65</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5138772150809775</v>
+        <v>-0.5812</v>
       </c>
       <c r="J69" t="n">
-        <v>-11.81917594686248</v>
+        <v>-13.3676</v>
       </c>
     </row>
     <row r="70">
@@ -5161,10 +5149,10 @@
         <v>0.62</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5443949664399732</v>
+        <v>-0.6186</v>
       </c>
       <c r="J70" t="n">
-        <v>-12.52108422811938</v>
+        <v>-14.2278</v>
       </c>
     </row>
     <row r="71">
@@ -5201,10 +5189,10 @@
         <v>0.59</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5745578722513978</v>
+        <v>-0.6553</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.21483106178215</v>
+        <v>-15.0719</v>
       </c>
     </row>
     <row r="72">
@@ -5241,10 +5229,10 @@
         <v>1.2</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1723426939804397</v>
+        <v>0.4483</v>
       </c>
       <c r="J72" t="n">
-        <v>3.446853879608795</v>
+        <v>8.965999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -5281,10 +5269,10 @@
         <v>1.04</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.06209059560599109</v>
+        <v>0.1865</v>
       </c>
       <c r="J73" t="n">
-        <v>-1.241811912119822</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="74">
@@ -5321,10 +5309,10 @@
         <v>0.78</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.342472951931588</v>
+        <v>-0.3578</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.84945903863176</v>
+        <v>-7.156</v>
       </c>
     </row>
     <row r="75">
@@ -5361,10 +5349,10 @@
         <v>0.7</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4298360336193559</v>
+        <v>-0.4786</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.596720672387118</v>
+        <v>-9.571999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -5401,10 +5389,10 @@
         <v>0.41</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7405949854774698</v>
+        <v>-0.846</v>
       </c>
       <c r="J76" t="n">
-        <v>-14.8118997095494</v>
+        <v>-16.92</v>
       </c>
     </row>
     <row r="77">
@@ -5441,10 +5429,10 @@
         <v>1.57</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8728330332489924</v>
+        <v>0.7537</v>
       </c>
       <c r="J77" t="n">
-        <v>17.45666066497985</v>
+        <v>15.074</v>
       </c>
     </row>
     <row r="78">
@@ -5481,10 +5469,10 @@
         <v>1.5</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7593089220854264</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="J78" t="n">
-        <v>15.18617844170853</v>
+        <v>13.478</v>
       </c>
     </row>
     <row r="79">
@@ -5521,10 +5509,10 @@
         <v>1.46</v>
       </c>
       <c r="I79" t="n">
-        <v>0.6936089521705007</v>
+        <v>0.6267</v>
       </c>
       <c r="J79" t="n">
-        <v>13.87217904341001</v>
+        <v>12.534</v>
       </c>
     </row>
     <row r="80">
@@ -5561,10 +5549,10 @@
         <v>1.26</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3821298667672093</v>
+        <v>0.3479</v>
       </c>
       <c r="J80" t="n">
-        <v>7.642597335344186</v>
+        <v>6.958</v>
       </c>
     </row>
     <row r="81">
@@ -5601,10 +5589,10 @@
         <v>0.72</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3220001583777005</v>
+        <v>-0.5351</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.440003167554009</v>
+        <v>-10.702</v>
       </c>
     </row>
     <row r="82">
@@ -5641,10 +5629,10 @@
         <v>1.37</v>
       </c>
       <c r="I82" t="n">
-        <v>0.642894385544423</v>
+        <v>0.976</v>
       </c>
       <c r="J82" t="n">
-        <v>13.50078209643288</v>
+        <v>20.496</v>
       </c>
     </row>
     <row r="83">
@@ -5681,10 +5669,10 @@
         <v>1.23</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4144923655220904</v>
+        <v>0.6504</v>
       </c>
       <c r="J83" t="n">
-        <v>8.704339675963899</v>
+        <v>13.6584</v>
       </c>
     </row>
     <row r="84">
@@ -5721,10 +5709,10 @@
         <v>1.1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2196728129070607</v>
+        <v>0.2629</v>
       </c>
       <c r="J84" t="n">
-        <v>4.613129071048275</v>
+        <v>5.5209</v>
       </c>
     </row>
     <row r="85">
@@ -5761,10 +5749,10 @@
         <v>1.07</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1709768229779556</v>
+        <v>0.1704</v>
       </c>
       <c r="J85" t="n">
-        <v>3.590513282537068</v>
+        <v>3.5784</v>
       </c>
     </row>
     <row r="86">
@@ -5801,10 +5789,10 @@
         <v>0.99</v>
       </c>
       <c r="I86" t="n">
-        <v>0.03795472388822283</v>
+        <v>-0.1632</v>
       </c>
       <c r="J86" t="n">
-        <v>0.7970492016526795</v>
+        <v>-3.4272</v>
       </c>
     </row>
     <row r="87">
@@ -5841,10 +5829,10 @@
         <v>1.11</v>
       </c>
       <c r="I87" t="n">
-        <v>0.06641503608127608</v>
+        <v>0.2879</v>
       </c>
       <c r="J87" t="n">
-        <v>1.394715757706798</v>
+        <v>6.0459</v>
       </c>
     </row>
     <row r="88">
@@ -5881,10 +5869,10 @@
         <v>1.05</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.02286344719179446</v>
+        <v>0.182</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.4801323910276837</v>
+        <v>3.822</v>
       </c>
     </row>
     <row r="89">
@@ -5921,10 +5909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1429559344955511</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.002074624406572</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="90">
@@ -5961,10 +5949,10 @@
         <v>0.77</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3146125596270281</v>
+        <v>-0.3963</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.60686375216759</v>
+        <v>-8.3223</v>
       </c>
     </row>
     <row r="91">
@@ -6001,10 +5989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5380545847307867</v>
+        <v>-0.6766</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.29914627934652</v>
+        <v>-14.2086</v>
       </c>
     </row>
     <row r="92">
@@ -6041,10 +6029,10 @@
         <v>1.36</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3933195283919438</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J92" t="n">
-        <v>9.046349153014708</v>
+        <v>14.0852</v>
       </c>
     </row>
     <row r="93">
@@ -6081,10 +6069,10 @@
         <v>1.03</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.04985601748628092</v>
+        <v>0.1133</v>
       </c>
       <c r="J93" t="n">
-        <v>-1.146688402184461</v>
+        <v>2.6059</v>
       </c>
     </row>
     <row r="94">
@@ -6121,10 +6109,10 @@
         <v>0.93</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1472573476697369</v>
+        <v>-0.1545</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.386918996403948</v>
+        <v>-3.5535</v>
       </c>
     </row>
     <row r="95">
@@ -6161,10 +6149,10 @@
         <v>0.92</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1572391751033728</v>
+        <v>-0.1743</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.616501027377574</v>
+        <v>-4.0089</v>
       </c>
     </row>
     <row r="96">
@@ -6201,10 +6189,10 @@
         <v>0.53</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5656419809128389</v>
+        <v>-0.7232</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.00976556099529</v>
+        <v>-16.6336</v>
       </c>
     </row>
     <row r="97">
@@ -6241,10 +6229,10 @@
         <v>1.44</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5580017761322307</v>
+        <v>1.1274</v>
       </c>
       <c r="J97" t="n">
-        <v>12.8340408510413</v>
+        <v>25.9302</v>
       </c>
     </row>
     <row r="98">
@@ -6281,10 +6269,10 @@
         <v>1.32</v>
       </c>
       <c r="I98" t="n">
-        <v>0.39429780531249</v>
+        <v>0.8683999999999999</v>
       </c>
       <c r="J98" t="n">
-        <v>9.068849522187271</v>
+        <v>19.9732</v>
       </c>
     </row>
     <row r="99">
@@ -6321,10 +6309,10 @@
         <v>1.24</v>
       </c>
       <c r="I99" t="n">
-        <v>0.283430093946031</v>
+        <v>0.6792</v>
       </c>
       <c r="J99" t="n">
-        <v>6.518892160758712</v>
+        <v>15.6216</v>
       </c>
     </row>
     <row r="100">
@@ -6361,10 +6349,10 @@
         <v>0.93</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1001768047814619</v>
+        <v>-0.372</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.304066509973624</v>
+        <v>-8.555999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6401,10 +6389,10 @@
         <v>0.8</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2427336124550861</v>
+        <v>-0.7159</v>
       </c>
       <c r="J101" t="n">
-        <v>-5.58287308646698</v>
+        <v>-16.4657</v>
       </c>
     </row>
     <row r="102">
@@ -6441,10 +6429,10 @@
         <v>1.13</v>
       </c>
       <c r="I102" t="n">
-        <v>0.0751991237069998</v>
+        <v>0.282</v>
       </c>
       <c r="J102" t="n">
-        <v>2.707168453451993</v>
+        <v>10.152</v>
       </c>
     </row>
     <row r="103">
@@ -6481,10 +6469,10 @@
         <v>1.04</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.03633411579649671</v>
+        <v>0.12</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.308028168673881</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="104">
@@ -6521,10 +6509,10 @@
         <v>1.01</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.06673601785772033</v>
+        <v>0.0477</v>
       </c>
       <c r="J104" t="n">
-        <v>-2.402496642877932</v>
+        <v>1.7172</v>
       </c>
     </row>
     <row r="105">
@@ -6561,10 +6549,10 @@
         <v>0.9</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1750258108404948</v>
+        <v>-0.224</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.300929190257812</v>
+        <v>-8.064</v>
       </c>
     </row>
     <row r="106">
@@ -6601,10 +6589,10 @@
         <v>0.86</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2182261731413218</v>
+        <v>-0.29</v>
       </c>
       <c r="J106" t="n">
-        <v>-7.856142233087583</v>
+        <v>-10.44</v>
       </c>
     </row>
     <row r="107">
@@ -6641,10 +6629,10 @@
         <v>1.34</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3976694775200841</v>
+        <v>0.923</v>
       </c>
       <c r="J107" t="n">
-        <v>14.31610119072303</v>
+        <v>33.228</v>
       </c>
     </row>
     <row r="108">
@@ -6681,10 +6669,10 @@
         <v>1.27</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3003709311899487</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="J108" t="n">
-        <v>10.81335352283815</v>
+        <v>27.4536</v>
       </c>
     </row>
     <row r="109">
@@ -6721,10 +6709,10 @@
         <v>1.16</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1495885003016105</v>
+        <v>0.4792</v>
       </c>
       <c r="J109" t="n">
-        <v>5.385186010857977</v>
+        <v>17.2512</v>
       </c>
     </row>
     <row r="110">
@@ -6761,10 +6749,10 @@
         <v>1.02</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.02327816017582887</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="J110" t="n">
-        <v>-0.8380137663298395</v>
+        <v>0.3168</v>
       </c>
     </row>
     <row r="111">
@@ -6801,10 +6789,10 @@
         <v>0.85</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.208129586341352</v>
+        <v>-0.5868</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.492665108288671</v>
+        <v>-21.1248</v>
       </c>
     </row>
     <row r="112">
@@ -6841,10 +6829,10 @@
         <v>1.14</v>
       </c>
       <c r="I112" t="n">
-        <v>0.06877761813715204</v>
+        <v>0.3624</v>
       </c>
       <c r="J112" t="n">
-        <v>1.306774744605889</v>
+        <v>6.8856</v>
       </c>
     </row>
     <row r="113">
@@ -6881,10 +6869,10 @@
         <v>0.85</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2410095428259955</v>
+        <v>-0.2184</v>
       </c>
       <c r="J113" t="n">
-        <v>-4.579181313693914</v>
+        <v>-4.1496</v>
       </c>
     </row>
     <row r="114">
@@ -6921,10 +6909,10 @@
         <v>0.8</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2820364481139181</v>
+        <v>-0.3193</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.358692514164445</v>
+        <v>-6.0667</v>
       </c>
     </row>
     <row r="115">
@@ -6961,10 +6949,10 @@
         <v>0.68</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.395401576009231</v>
+        <v>-0.5043</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.512629944175389</v>
+        <v>-9.5817</v>
       </c>
     </row>
     <row r="116">
@@ -7001,10 +6989,10 @@
         <v>0.62</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.453339089424289</v>
+        <v>-0.5859</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.613442699061491</v>
+        <v>-11.1321</v>
       </c>
     </row>
     <row r="117">
@@ -7041,10 +7029,10 @@
         <v>1.58</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8447710498255653</v>
+        <v>1.3541</v>
       </c>
       <c r="J117" t="n">
-        <v>16.05064994668574</v>
+        <v>25.7279</v>
       </c>
     </row>
     <row r="118">
@@ -7081,10 +7069,10 @@
         <v>1.57</v>
       </c>
       <c r="I118" t="n">
-        <v>0.8312116393059257</v>
+        <v>1.3348</v>
       </c>
       <c r="J118" t="n">
-        <v>15.79302114681259</v>
+        <v>25.3612</v>
       </c>
     </row>
     <row r="119">
@@ -7121,10 +7109,10 @@
         <v>1.51</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7488414707257558</v>
+        <v>1.2168</v>
       </c>
       <c r="J119" t="n">
-        <v>14.22798794378936</v>
+        <v>23.1192</v>
       </c>
     </row>
     <row r="120">
@@ -7161,10 +7149,10 @@
         <v>0.98</v>
       </c>
       <c r="I120" t="n">
-        <v>0.005725047290005576</v>
+        <v>-0.2408</v>
       </c>
       <c r="J120" t="n">
-        <v>0.1087758985101059</v>
+        <v>-4.5752</v>
       </c>
     </row>
     <row r="121">
@@ -7201,10 +7189,10 @@
         <v>0.62</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3464724006588814</v>
+        <v>-1.1318</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.582975612518747</v>
+        <v>-21.5042</v>
       </c>
     </row>
     <row r="122">
@@ -7241,10 +7229,10 @@
         <v>1.27</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2580541554620672</v>
+        <v>0.5533</v>
       </c>
       <c r="J122" t="n">
-        <v>4.903028953779276</v>
+        <v>10.5127</v>
       </c>
     </row>
     <row r="123">
@@ -7281,10 +7269,10 @@
         <v>1.02</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.07023475885442972</v>
+        <v>0.1517</v>
       </c>
       <c r="J123" t="n">
-        <v>-1.334460418234165</v>
+        <v>2.8823</v>
       </c>
     </row>
     <row r="124">
@@ -7321,10 +7309,10 @@
         <v>0.63</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.4393768573790066</v>
+        <v>-0.5694</v>
       </c>
       <c r="J124" t="n">
-        <v>-8.348160290201125</v>
+        <v>-10.8186</v>
       </c>
     </row>
     <row r="125">
@@ -7361,10 +7349,10 @@
         <v>0.57</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4967289702307962</v>
+        <v>-0.6481</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.437850434385128</v>
+        <v>-12.3139</v>
       </c>
     </row>
     <row r="126">
@@ -7401,10 +7389,10 @@
         <v>0.54</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5250628627796126</v>
+        <v>-0.6861</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.976194392812639</v>
+        <v>-13.0359</v>
       </c>
     </row>
     <row r="127">
@@ -7441,10 +7429,10 @@
         <v>1.61</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8735508330671826</v>
+        <v>1.4039</v>
       </c>
       <c r="J127" t="n">
-        <v>16.59746582827647</v>
+        <v>26.6741</v>
       </c>
     </row>
     <row r="128">
@@ -7481,10 +7469,10 @@
         <v>1.52</v>
       </c>
       <c r="I128" t="n">
-        <v>0.750774303615427</v>
+        <v>1.2291</v>
       </c>
       <c r="J128" t="n">
-        <v>14.26471176869311</v>
+        <v>23.3529</v>
       </c>
     </row>
     <row r="129">
@@ -7521,10 +7509,10 @@
         <v>1.33</v>
       </c>
       <c r="I129" t="n">
-        <v>0.4838262024603981</v>
+        <v>0.8219</v>
       </c>
       <c r="J129" t="n">
-        <v>9.192697846747564</v>
+        <v>15.6161</v>
       </c>
     </row>
     <row r="130">
@@ -7561,10 +7549,10 @@
         <v>1.03</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0678274713483385</v>
+        <v>-0.0097</v>
       </c>
       <c r="J130" t="n">
-        <v>1.288721955618432</v>
+        <v>-0.1843</v>
       </c>
     </row>
     <row r="131">
@@ -7601,10 +7589,10 @@
         <v>0.85</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1353847301704289</v>
+        <v>-0.6248</v>
       </c>
       <c r="J131" t="n">
-        <v>-2.57230987323815</v>
+        <v>-11.8712</v>
       </c>
     </row>
     <row r="132">
@@ -7641,10 +7629,10 @@
         <v>1.34</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3648158616791456</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="J132" t="n">
-        <v>10.57965998869522</v>
+        <v>27.115</v>
       </c>
     </row>
     <row r="133">
@@ -7681,10 +7669,10 @@
         <v>1.18</v>
       </c>
       <c r="I133" t="n">
-        <v>0.184177305660905</v>
+        <v>0.5503</v>
       </c>
       <c r="J133" t="n">
-        <v>5.341141864166245</v>
+        <v>15.9587</v>
       </c>
     </row>
     <row r="134">
@@ -7721,10 +7709,10 @@
         <v>1.01</v>
       </c>
       <c r="I134" t="n">
-        <v>0.00706512652592291</v>
+        <v>-0.0231</v>
       </c>
       <c r="J134" t="n">
-        <v>0.2048886692517644</v>
+        <v>-0.6699000000000001</v>
       </c>
     </row>
     <row r="135">
@@ -7761,10 +7749,10 @@
         <v>1.01</v>
       </c>
       <c r="I135" t="n">
-        <v>0.00706512652592291</v>
+        <v>-0.0231</v>
       </c>
       <c r="J135" t="n">
-        <v>0.2048886692517644</v>
+        <v>-0.6699000000000001</v>
       </c>
     </row>
     <row r="136">
@@ -7801,10 +7789,10 @@
         <v>0.99</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.01366937427911778</v>
+        <v>-0.1424</v>
       </c>
       <c r="J136" t="n">
-        <v>-0.3964118540944156</v>
+        <v>-4.1296</v>
       </c>
     </row>
     <row r="137">
@@ -7841,10 +7829,10 @@
         <v>1.5</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5061157177960177</v>
+        <v>0.7692</v>
       </c>
       <c r="J137" t="n">
-        <v>14.67735581608451</v>
+        <v>22.3068</v>
       </c>
     </row>
     <row r="138">
@@ -7881,10 +7869,10 @@
         <v>1.05</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.03330104475093468</v>
+        <v>0.1424</v>
       </c>
       <c r="J138" t="n">
-        <v>-0.9657302977771056</v>
+        <v>4.1296</v>
       </c>
     </row>
     <row r="139">
@@ -7921,10 +7909,10 @@
         <v>0.96</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1088136557437525</v>
+        <v>-0.1069</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.155596016568821</v>
+        <v>-3.1001</v>
       </c>
     </row>
     <row r="140">
@@ -7961,10 +7949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.248791994553257</v>
+        <v>-0.3652</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.214967842044452</v>
+        <v>-10.5908</v>
       </c>
     </row>
     <row r="141">
@@ -8001,10 +7989,10 @@
         <v>0.6</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4422730488947356</v>
+        <v>-0.6435</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.82591841794733</v>
+        <v>-18.6615</v>
       </c>
     </row>
     <row r="142">
@@ -8041,10 +8029,10 @@
         <v>1.36</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3303164055993151</v>
+        <v>0.9489</v>
       </c>
       <c r="J142" t="n">
-        <v>7.597277328784248</v>
+        <v>21.8247</v>
       </c>
     </row>
     <row r="143">
@@ -8081,10 +8069,10 @@
         <v>1.31</v>
       </c>
       <c r="I143" t="n">
-        <v>0.273809169233608</v>
+        <v>0.8367</v>
       </c>
       <c r="J143" t="n">
-        <v>6.297610892372983</v>
+        <v>19.2441</v>
       </c>
     </row>
     <row r="144">
@@ -8121,10 +8109,10 @@
         <v>1.26</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2172299008477278</v>
+        <v>0.7187</v>
       </c>
       <c r="J144" t="n">
-        <v>4.996287719497738</v>
+        <v>16.5301</v>
       </c>
     </row>
     <row r="145">
@@ -8161,10 +8149,10 @@
         <v>1.08</v>
       </c>
       <c r="I145" t="n">
-        <v>0.02806384086816172</v>
+        <v>0.1961</v>
       </c>
       <c r="J145" t="n">
-        <v>0.6454683399677195</v>
+        <v>4.5103</v>
       </c>
     </row>
     <row r="146">
@@ -8201,10 +8189,10 @@
         <v>0.8</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2692743805107871</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="J146" t="n">
-        <v>-6.193310751748104</v>
+        <v>-16.5669</v>
       </c>
     </row>
     <row r="147">
@@ -8241,10 +8229,10 @@
         <v>1.28</v>
       </c>
       <c r="I147" t="n">
-        <v>0.1852630908232144</v>
+        <v>0.4866</v>
       </c>
       <c r="J147" t="n">
-        <v>4.261051088933931</v>
+        <v>11.1918</v>
       </c>
     </row>
     <row r="148">
@@ -8281,10 +8269,10 @@
         <v>1.12</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.008705085943158362</v>
+        <v>0.253</v>
       </c>
       <c r="J148" t="n">
-        <v>-0.2002169766926423</v>
+        <v>5.819</v>
       </c>
     </row>
     <row r="149">
@@ -8321,10 +8309,10 @@
         <v>1.1</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.02718333365082964</v>
+        <v>0.2192</v>
       </c>
       <c r="J149" t="n">
-        <v>-0.6252166739690819</v>
+        <v>5.0416</v>
       </c>
     </row>
     <row r="150">
@@ -8361,10 +8349,10 @@
         <v>1.09</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.03640245613010924</v>
+        <v>0.2017</v>
       </c>
       <c r="J150" t="n">
-        <v>-0.8372564909925125</v>
+        <v>4.6391</v>
       </c>
     </row>
     <row r="151">
@@ -8401,10 +8389,10 @@
         <v>0.52</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5489290967073943</v>
+        <v>-0.7432</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.62536922427007</v>
+        <v>-17.0936</v>
       </c>
     </row>
     <row r="152">
@@ -8441,10 +8429,10 @@
         <v>1.47</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5140788845124118</v>
+        <v>0.6881</v>
       </c>
       <c r="J152" t="n">
-        <v>11.82381434378547</v>
+        <v>15.8263</v>
       </c>
     </row>
     <row r="153">
@@ -8481,10 +8469,10 @@
         <v>1.12</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1028704464059127</v>
+        <v>0.1968</v>
       </c>
       <c r="J153" t="n">
-        <v>2.366020267335992</v>
+        <v>4.5264</v>
       </c>
     </row>
     <row r="154">
@@ -8521,10 +8509,10 @@
         <v>1.08</v>
       </c>
       <c r="I154" t="n">
-        <v>0.05852682214036054</v>
+        <v>0.1236</v>
       </c>
       <c r="J154" t="n">
-        <v>1.346116909228293</v>
+        <v>2.8428</v>
       </c>
     </row>
     <row r="155">
@@ -8561,10 +8549,10 @@
         <v>1.01</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.01767869530263233</v>
+        <v>-0.0202</v>
       </c>
       <c r="J155" t="n">
-        <v>-0.4066099919605436</v>
+        <v>-0.4646</v>
       </c>
     </row>
     <row r="156">
@@ -8601,10 +8589,10 @@
         <v>0.97</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.05620105121714365</v>
+        <v>-0.1346</v>
       </c>
       <c r="J156" t="n">
-        <v>-1.292624177994304</v>
+        <v>-3.0958</v>
       </c>
     </row>
     <row r="157">
@@ -8641,10 +8629,10 @@
         <v>1.66</v>
       </c>
       <c r="I157" t="n">
-        <v>0.524801617256103</v>
+        <v>0.9356</v>
       </c>
       <c r="J157" t="n">
-        <v>12.07043719689037</v>
+        <v>21.5188</v>
       </c>
     </row>
     <row r="158">
@@ -8681,10 +8669,10 @@
         <v>0.97</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1592117457154502</v>
+        <v>-0.0994</v>
       </c>
       <c r="J158" t="n">
-        <v>-3.661870151455355</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="159">
@@ -8721,10 +8709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1941826333116248</v>
+        <v>-0.1611</v>
       </c>
       <c r="J159" t="n">
-        <v>-4.466200566167371</v>
+        <v>-3.7053</v>
       </c>
     </row>
     <row r="160">
@@ -8761,10 +8749,10 @@
         <v>0.76</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.40886730141571</v>
+        <v>-0.4432</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.40394793256133</v>
+        <v>-10.1936</v>
       </c>
     </row>
     <row r="161">
@@ -8801,10 +8789,10 @@
         <v>0.75</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4206045176759997</v>
+        <v>-0.4568</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.673903906547993</v>
+        <v>-10.5064</v>
       </c>
     </row>
     <row r="162">
@@ -8841,10 +8829,10 @@
         <v>1.08</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.04591308940201837</v>
+        <v>0.3016</v>
       </c>
       <c r="J162" t="n">
-        <v>-0.7346094304322939</v>
+        <v>4.8256</v>
       </c>
     </row>
     <row r="163">
@@ -8881,10 +8869,10 @@
         <v>0.77</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.3472396135053809</v>
+        <v>-0.3061</v>
       </c>
       <c r="J163" t="n">
-        <v>-5.555833816086094</v>
+        <v>-4.8976</v>
       </c>
     </row>
     <row r="164">
@@ -8921,10 +8909,10 @@
         <v>0.7</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.404707292130745</v>
+        <v>-0.4391</v>
       </c>
       <c r="J164" t="n">
-        <v>-6.47531667409192</v>
+        <v>-7.0256</v>
       </c>
     </row>
     <row r="165">
@@ -8961,10 +8949,10 @@
         <v>0.57</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.5262542188027173</v>
+        <v>-0.6287</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.420067500843476</v>
+        <v>-10.0592</v>
       </c>
     </row>
     <row r="166">
@@ -9001,10 +8989,10 @@
         <v>0.54</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.554608715643491</v>
+        <v>-0.6685</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.873739450295856</v>
+        <v>-10.696</v>
       </c>
     </row>
     <row r="167">
@@ -9041,10 +9029,10 @@
         <v>1.69</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7022867713991667</v>
+        <v>1.5154</v>
       </c>
       <c r="J167" t="n">
-        <v>11.23658834238667</v>
+        <v>24.2464</v>
       </c>
     </row>
     <row r="168">
@@ -9081,10 +9069,10 @@
         <v>1.37</v>
       </c>
       <c r="I168" t="n">
-        <v>0.399877593840549</v>
+        <v>0.8609</v>
       </c>
       <c r="J168" t="n">
-        <v>6.398041501448784</v>
+        <v>13.7744</v>
       </c>
     </row>
     <row r="169">
@@ -9121,10 +9109,10 @@
         <v>1.36</v>
       </c>
       <c r="I169" t="n">
-        <v>0.3915718955731409</v>
+        <v>0.8347</v>
       </c>
       <c r="J169" t="n">
-        <v>6.265150329170254</v>
+        <v>13.3552</v>
       </c>
     </row>
     <row r="170">
@@ -9161,10 +9149,10 @@
         <v>1.3</v>
       </c>
       <c r="I170" t="n">
-        <v>0.3406172299628932</v>
+        <v>0.6741</v>
       </c>
       <c r="J170" t="n">
-        <v>5.449875679406292</v>
+        <v>10.7856</v>
       </c>
     </row>
     <row r="171">
@@ -9201,10 +9189,10 @@
         <v>1.04</v>
       </c>
       <c r="I171" t="n">
-        <v>0.08246856719084034</v>
+        <v>-0.0008</v>
       </c>
       <c r="J171" t="n">
-        <v>1.319497075053445</v>
+        <v>-0.0128</v>
       </c>
     </row>
     <row r="172">
@@ -9241,10 +9229,10 @@
         <v>1.46</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4089933990538372</v>
+        <v>0.6916</v>
       </c>
       <c r="J172" t="n">
-        <v>9.815841577292094</v>
+        <v>16.5984</v>
       </c>
     </row>
     <row r="173">
@@ -9281,10 +9269,10 @@
         <v>1.23</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1336453479237378</v>
+        <v>0.3989</v>
       </c>
       <c r="J173" t="n">
-        <v>3.207488350169707</v>
+        <v>9.573600000000001</v>
       </c>
     </row>
     <row r="174">
@@ -9321,10 +9309,10 @@
         <v>1.1</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.01703082527301762</v>
+        <v>0.1934</v>
       </c>
       <c r="J174" t="n">
-        <v>-0.4087398065524228</v>
+        <v>4.6416</v>
       </c>
     </row>
     <row r="175">
@@ -9361,10 +9349,10 @@
         <v>0.82</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2822214545813619</v>
+        <v>-0.3718</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.773314909952687</v>
+        <v>-8.9232</v>
       </c>
     </row>
     <row r="176">
@@ -9401,10 +9389,10 @@
         <v>0.79</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3119269863030246</v>
+        <v>-0.4141</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.48624767127259</v>
+        <v>-9.9384</v>
       </c>
     </row>
     <row r="177">
@@ -9441,10 +9429,10 @@
         <v>1.74</v>
       </c>
       <c r="I177" t="n">
-        <v>0.6917048297416866</v>
+        <v>1.756</v>
       </c>
       <c r="J177" t="n">
-        <v>16.60091591380048</v>
+        <v>42.144</v>
       </c>
     </row>
     <row r="178">
@@ -9481,10 +9469,10 @@
         <v>1.32</v>
       </c>
       <c r="I178" t="n">
-        <v>0.299587388643952</v>
+        <v>0.9226</v>
       </c>
       <c r="J178" t="n">
-        <v>7.190097327454847</v>
+        <v>22.1424</v>
       </c>
     </row>
     <row r="179">
@@ -9521,10 +9509,10 @@
         <v>0.98</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.03357874209206525</v>
+        <v>-0.1541</v>
       </c>
       <c r="J179" t="n">
-        <v>-0.8058898102095661</v>
+        <v>-3.6984</v>
       </c>
     </row>
     <row r="180">
@@ -9561,10 +9549,10 @@
         <v>0.7</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3661965678062491</v>
+        <v>-0.9195</v>
       </c>
       <c r="J180" t="n">
-        <v>-8.788717627349978</v>
+        <v>-22.068</v>
       </c>
     </row>
     <row r="181">
@@ -9601,10 +9589,10 @@
         <v>0.5</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5871283889044885</v>
+        <v>-1.3378</v>
       </c>
       <c r="J181" t="n">
-        <v>-14.09108133370772</v>
+        <v>-32.1072</v>
       </c>
     </row>
     <row r="182">
@@ -9641,10 +9629,10 @@
         <v>1.62</v>
       </c>
       <c r="I182" t="n">
-        <v>0.7064001353148113</v>
+        <v>1.4561</v>
       </c>
       <c r="J182" t="n">
-        <v>14.12800270629623</v>
+        <v>29.122</v>
       </c>
     </row>
     <row r="183">
@@ -9681,10 +9669,10 @@
         <v>1.41</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4746387286616156</v>
+        <v>1.0379</v>
       </c>
       <c r="J183" t="n">
-        <v>9.492774573232312</v>
+        <v>20.758</v>
       </c>
     </row>
     <row r="184">
@@ -9721,10 +9709,10 @@
         <v>1.09</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1183949001881629</v>
+        <v>0.2079</v>
       </c>
       <c r="J184" t="n">
-        <v>2.367898003763258</v>
+        <v>4.158</v>
       </c>
     </row>
     <row r="185">
@@ -9761,10 +9749,10 @@
         <v>1.04</v>
       </c>
       <c r="I185" t="n">
-        <v>0.05950903620977767</v>
+        <v>0.0509</v>
       </c>
       <c r="J185" t="n">
-        <v>1.190180724195553</v>
+        <v>1.018</v>
       </c>
     </row>
     <row r="186">
@@ -9801,10 +9789,10 @@
         <v>0.83</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1586851880962989</v>
+        <v>-0.6571</v>
       </c>
       <c r="J186" t="n">
-        <v>-3.173703761925978</v>
+        <v>-13.142</v>
       </c>
     </row>
     <row r="187">
@@ -9841,10 +9829,10 @@
         <v>1.13</v>
       </c>
       <c r="I187" t="n">
-        <v>0.001135561749865493</v>
+        <v>0.3071</v>
       </c>
       <c r="J187" t="n">
-        <v>0.02271123499730986</v>
+        <v>6.142</v>
       </c>
     </row>
     <row r="188">
@@ -9881,10 +9869,10 @@
         <v>0.95</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2344960571714303</v>
+        <v>-0.0837</v>
       </c>
       <c r="J188" t="n">
-        <v>-4.689921143428606</v>
+        <v>-1.674</v>
       </c>
     </row>
     <row r="189">
@@ -9921,10 +9909,10 @@
         <v>0.95</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2344960571714303</v>
+        <v>-0.0837</v>
       </c>
       <c r="J189" t="n">
-        <v>-4.689921143428606</v>
+        <v>-1.674</v>
       </c>
     </row>
     <row r="190">
@@ -9961,10 +9949,10 @@
         <v>0.87</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3265354905140231</v>
+        <v>-0.2499</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.530709810280463</v>
+        <v>-4.998</v>
       </c>
     </row>
     <row r="191">
@@ -10001,10 +9989,10 @@
         <v>0.7</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5468821605612953</v>
+        <v>-0.504</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.93764321122591</v>
+        <v>-10.08</v>
       </c>
     </row>
     <row r="192">
@@ -10041,10 +10029,10 @@
         <v>1.45</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4815994810770521</v>
+        <v>1.1429</v>
       </c>
       <c r="J192" t="n">
-        <v>10.59518858369515</v>
+        <v>25.1438</v>
       </c>
     </row>
     <row r="193">
@@ -10081,10 +10069,10 @@
         <v>1.34</v>
       </c>
       <c r="I193" t="n">
-        <v>0.355193811948965</v>
+        <v>0.9079</v>
       </c>
       <c r="J193" t="n">
-        <v>7.81426386287723</v>
+        <v>19.9738</v>
       </c>
     </row>
     <row r="194">
@@ -10121,10 +10109,10 @@
         <v>1.23</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2269375067864765</v>
+        <v>0.6479</v>
       </c>
       <c r="J194" t="n">
-        <v>4.992625149302482</v>
+        <v>14.2538</v>
       </c>
     </row>
     <row r="195">
@@ -10161,10 +10149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.08225695087055636</v>
+        <v>-0.3449</v>
       </c>
       <c r="J195" t="n">
-        <v>-1.80965291915224</v>
+        <v>-7.5878</v>
       </c>
     </row>
     <row r="196">
@@ -10201,10 +10189,10 @@
         <v>0.82</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2062755711118006</v>
+        <v>-0.6703</v>
       </c>
       <c r="J196" t="n">
-        <v>-4.538062564459614</v>
+        <v>-14.7466</v>
       </c>
     </row>
     <row r="197">
@@ -10241,10 +10229,10 @@
         <v>1.26</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1109250731813106</v>
+        <v>0.4679</v>
       </c>
       <c r="J197" t="n">
-        <v>2.440351609988834</v>
+        <v>10.2938</v>
       </c>
     </row>
     <row r="198">
@@ -10281,10 +10269,10 @@
         <v>1.22</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0755184802468198</v>
+        <v>0.4128</v>
       </c>
       <c r="J198" t="n">
-        <v>1.661406565430036</v>
+        <v>9.0816</v>
       </c>
     </row>
     <row r="199">
@@ -10321,10 +10309,10 @@
         <v>1</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1649209954548805</v>
+        <v>0.0029</v>
       </c>
       <c r="J199" t="n">
-        <v>-3.628261900007371</v>
+        <v>0.0638</v>
       </c>
     </row>
     <row r="200">
@@ -10361,10 +10349,10 @@
         <v>0.83</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3804356801401279</v>
+        <v>-0.339</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.369584963082813</v>
+        <v>-7.458</v>
       </c>
     </row>
     <row r="201">
@@ -10401,10 +10389,10 @@
         <v>0.68</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5749559131207276</v>
+        <v>-0.5458</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.64903008865601</v>
+        <v>-12.0076</v>
       </c>
     </row>
     <row r="202">
@@ -10441,10 +10429,10 @@
         <v>2.21</v>
       </c>
       <c r="I202" t="n">
-        <v>1.104812729394687</v>
+        <v>1.3556</v>
       </c>
       <c r="J202" t="n">
-        <v>20.99144185849905</v>
+        <v>25.7564</v>
       </c>
     </row>
     <row r="203">
@@ -10481,10 +10469,10 @@
         <v>1.69</v>
       </c>
       <c r="I203" t="n">
-        <v>0.6278843039011964</v>
+        <v>0.8515</v>
       </c>
       <c r="J203" t="n">
-        <v>11.92980177412273</v>
+        <v>16.1785</v>
       </c>
     </row>
     <row r="204">
@@ -10521,10 +10509,10 @@
         <v>1.36</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2998613004474835</v>
+        <v>0.444</v>
       </c>
       <c r="J204" t="n">
-        <v>5.697364708502186</v>
+        <v>8.436</v>
       </c>
     </row>
     <row r="205">
@@ -10561,10 +10549,10 @@
         <v>1.11</v>
       </c>
       <c r="I205" t="n">
-        <v>0.03325632027877455</v>
+        <v>0.1046</v>
       </c>
       <c r="J205" t="n">
-        <v>0.6318700852967165</v>
+        <v>1.9874</v>
       </c>
     </row>
     <row r="206">
@@ -10601,10 +10589,10 @@
         <v>0.78</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3106293153729828</v>
+        <v>-0.4714</v>
       </c>
       <c r="J206" t="n">
-        <v>-5.901956992086673</v>
+        <v>-8.9566</v>
       </c>
     </row>
     <row r="207">
@@ -10641,10 +10629,10 @@
         <v>1.26</v>
       </c>
       <c r="I207" t="n">
-        <v>0.2030626735067586</v>
+        <v>0.5654</v>
       </c>
       <c r="J207" t="n">
-        <v>3.858190796628413</v>
+        <v>10.7426</v>
       </c>
     </row>
     <row r="208">
@@ -10681,10 +10669,10 @@
         <v>0.65</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.3721638597539689</v>
+        <v>-0.5229</v>
       </c>
       <c r="J208" t="n">
-        <v>-7.07111333532541</v>
+        <v>-9.9351</v>
       </c>
     </row>
     <row r="209">
@@ -10721,10 +10709,10 @@
         <v>0.64</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.3804822582375515</v>
+        <v>-0.5372</v>
       </c>
       <c r="J209" t="n">
-        <v>-7.229162906513478</v>
+        <v>-10.2068</v>
       </c>
     </row>
     <row r="210">
@@ -10761,10 +10749,10 @@
         <v>0.6</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4138658216588522</v>
+        <v>-0.593</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.863450611518192</v>
+        <v>-11.267</v>
       </c>
     </row>
     <row r="211">
@@ -10801,10 +10789,10 @@
         <v>0.59</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4222130753588421</v>
+        <v>-0.6065</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.022048431818</v>
+        <v>-11.5235</v>
       </c>
     </row>
     <row r="212">
@@ -10841,10 +10829,10 @@
         <v>1.15</v>
       </c>
       <c r="I212" t="n">
-        <v>0.04669609321413301</v>
+        <v>0.3457</v>
       </c>
       <c r="J212" t="n">
-        <v>0.9806179574967933</v>
+        <v>7.2597</v>
       </c>
     </row>
     <row r="213">
@@ -10881,10 +10869,10 @@
         <v>1.13</v>
       </c>
       <c r="I213" t="n">
-        <v>0.0247954534872829</v>
+        <v>0.3146</v>
       </c>
       <c r="J213" t="n">
-        <v>0.5207045232329409</v>
+        <v>6.6066</v>
       </c>
     </row>
     <row r="214">
@@ -10921,10 +10909,10 @@
         <v>0.83</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2947137387021422</v>
+        <v>-0.3086</v>
       </c>
       <c r="J214" t="n">
-        <v>-6.188988512744986</v>
+        <v>-6.4806</v>
       </c>
     </row>
     <row r="215">
@@ -10961,10 +10949,10 @@
         <v>0.77</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3599664821196246</v>
+        <v>-0.4007</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.559296124512117</v>
+        <v>-8.4147</v>
       </c>
     </row>
     <row r="216">
@@ -11001,10 +10989,10 @@
         <v>0.62</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5221339621203873</v>
+        <v>-0.6042</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.96481320452813</v>
+        <v>-12.6882</v>
       </c>
     </row>
     <row r="217">
@@ -11041,10 +11029,10 @@
         <v>1.54</v>
       </c>
       <c r="I217" t="n">
-        <v>0.6440120585150958</v>
+        <v>1.2811</v>
       </c>
       <c r="J217" t="n">
-        <v>13.52425322881701</v>
+        <v>26.9031</v>
       </c>
     </row>
     <row r="218">
@@ -11081,10 +11069,10 @@
         <v>1.46</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5424226370783091</v>
+        <v>1.1202</v>
       </c>
       <c r="J218" t="n">
-        <v>11.39087537864449</v>
+        <v>23.5242</v>
       </c>
     </row>
     <row r="219">
@@ -11121,10 +11109,10 @@
         <v>1.22</v>
       </c>
       <c r="I219" t="n">
-        <v>0.2432615369986747</v>
+        <v>0.5419</v>
       </c>
       <c r="J219" t="n">
-        <v>5.108492276972169</v>
+        <v>11.3799</v>
       </c>
     </row>
     <row r="220">
@@ -11161,10 +11149,10 @@
         <v>1.2</v>
       </c>
       <c r="I220" t="n">
-        <v>0.2187918666737055</v>
+        <v>0.4877</v>
       </c>
       <c r="J220" t="n">
-        <v>4.594629200147815</v>
+        <v>10.2417</v>
       </c>
     </row>
     <row r="221">
@@ -11201,10 +11189,10 @@
         <v>0.79</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.206956429119271</v>
+        <v>-0.763</v>
       </c>
       <c r="J221" t="n">
-        <v>-4.34608501150469</v>
+        <v>-16.023</v>
       </c>
     </row>
     <row r="222">
@@ -11241,10 +11229,10 @@
         <v>1.12</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.02600945641829539</v>
+        <v>0.3134</v>
       </c>
       <c r="J222" t="n">
-        <v>-0.4941796719476124</v>
+        <v>5.9546</v>
       </c>
     </row>
     <row r="223">
@@ -11281,10 +11269,10 @@
         <v>0.91</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2583717321488408</v>
+        <v>-0.1328</v>
       </c>
       <c r="J223" t="n">
-        <v>-4.909062910827975</v>
+        <v>-2.5232</v>
       </c>
     </row>
     <row r="224">
@@ -11321,10 +11309,10 @@
         <v>0.9</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2687821460904747</v>
+        <v>-0.1516</v>
       </c>
       <c r="J224" t="n">
-        <v>-5.10686077571902</v>
+        <v>-2.8804</v>
       </c>
     </row>
     <row r="225">
@@ -11361,10 +11349,10 @@
         <v>0.72</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4513404549638605</v>
+        <v>-0.4613</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.57546864431335</v>
+        <v>-8.764699999999999</v>
       </c>
     </row>
     <row r="226">
@@ -11401,10 +11389,10 @@
         <v>0.66</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5158994590336807</v>
+        <v>-0.5438</v>
       </c>
       <c r="J226" t="n">
-        <v>-9.802089721639934</v>
+        <v>-10.3322</v>
       </c>
     </row>
     <row r="227">
@@ -11441,10 +11429,10 @@
         <v>1.73</v>
       </c>
       <c r="I227" t="n">
-        <v>0.8775178394562344</v>
+        <v>1.605</v>
       </c>
       <c r="J227" t="n">
-        <v>16.67283894966845</v>
+        <v>30.495</v>
       </c>
     </row>
     <row r="228">
@@ -11481,10 +11469,10 @@
         <v>1.61</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7321559917890827</v>
+        <v>1.3827</v>
       </c>
       <c r="J228" t="n">
-        <v>13.91096384399257</v>
+        <v>26.2713</v>
       </c>
     </row>
     <row r="229">
@@ -11521,10 +11509,10 @@
         <v>1.22</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2484935055733751</v>
+        <v>0.4993</v>
       </c>
       <c r="J229" t="n">
-        <v>4.721376605894127</v>
+        <v>9.486700000000001</v>
       </c>
     </row>
     <row r="230">
@@ -11561,10 +11549,10 @@
         <v>1.05</v>
       </c>
       <c r="I230" t="n">
-        <v>0.02300779256905523</v>
+        <v>0.0427</v>
       </c>
       <c r="J230" t="n">
-        <v>0.4371480588120494</v>
+        <v>0.8113</v>
       </c>
     </row>
     <row r="231">
@@ -11601,10 +11589,10 @@
         <v>0.96</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.06324706903959697</v>
+        <v>-0.3293</v>
       </c>
       <c r="J231" t="n">
-        <v>-1.201694311752342</v>
+        <v>-6.2567</v>
       </c>
     </row>
     <row r="232">
@@ -11641,10 +11629,10 @@
         <v>1.41</v>
       </c>
       <c r="I232" t="n">
-        <v>0.3431619549525921</v>
+        <v>0.6681</v>
       </c>
       <c r="J232" t="n">
-        <v>7.549563008957026</v>
+        <v>14.6982</v>
       </c>
     </row>
     <row r="233">
@@ -11681,10 +11669,10 @@
         <v>0.96</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.1388934179565116</v>
+        <v>-0.0987</v>
       </c>
       <c r="J233" t="n">
-        <v>-3.055655195043256</v>
+        <v>-2.1714</v>
       </c>
     </row>
     <row r="234">
@@ -11721,10 +11709,10 @@
         <v>0.92</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1787204476703312</v>
+        <v>-0.1814</v>
       </c>
       <c r="J234" t="n">
-        <v>-3.931849848747286</v>
+        <v>-3.9908</v>
       </c>
     </row>
     <row r="235">
@@ -11761,10 +11749,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1892019311641173</v>
+        <v>-0.1998</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.16244248561058</v>
+        <v>-4.3956</v>
       </c>
     </row>
     <row r="236">
@@ -11801,10 +11789,10 @@
         <v>0.65</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4671178048084524</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="J236" t="n">
-        <v>-10.27659170578595</v>
+        <v>-12.7402</v>
       </c>
     </row>
     <row r="237">
@@ -11841,10 +11829,10 @@
         <v>1.43</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5242825711311649</v>
+        <v>1.1255</v>
       </c>
       <c r="J237" t="n">
-        <v>11.53421656488563</v>
+        <v>24.761</v>
       </c>
     </row>
     <row r="238">
@@ -11881,10 +11869,10 @@
         <v>1.21</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2603258555513092</v>
+        <v>0.626</v>
       </c>
       <c r="J238" t="n">
-        <v>5.727168822128801</v>
+        <v>13.772</v>
       </c>
     </row>
     <row r="239">
@@ -11921,10 +11909,10 @@
         <v>1.11</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1464739566668786</v>
+        <v>0.3345</v>
       </c>
       <c r="J239" t="n">
-        <v>3.222427046671329</v>
+        <v>7.359</v>
       </c>
     </row>
     <row r="240">
@@ -11961,10 +11949,10 @@
         <v>0.98</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.001248102015044087</v>
+        <v>-0.1872</v>
       </c>
       <c r="J240" t="n">
-        <v>-0.02745824433096991</v>
+        <v>-4.1184</v>
       </c>
     </row>
     <row r="241">
@@ -12001,10 +11989,10 @@
         <v>0.82</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.1575816394319385</v>
+        <v>-0.6567</v>
       </c>
       <c r="J241" t="n">
-        <v>-3.466796067502647</v>
+        <v>-14.4474</v>
       </c>
     </row>
     <row r="242">
@@ -12041,10 +12029,10 @@
         <v>1.36</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3683246223639395</v>
+        <v>0.6246</v>
       </c>
       <c r="J242" t="n">
-        <v>8.839790936734548</v>
+        <v>14.9904</v>
       </c>
     </row>
     <row r="243">
@@ -12081,10 +12069,10 @@
         <v>1.07</v>
       </c>
       <c r="I243" t="n">
-        <v>0.05075978709008661</v>
+        <v>0.2061</v>
       </c>
       <c r="J243" t="n">
-        <v>1.218234890162079</v>
+        <v>4.9464</v>
       </c>
     </row>
     <row r="244">
@@ -12121,10 +12109,10 @@
         <v>0.82</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2078611884816037</v>
+        <v>-0.3316</v>
       </c>
       <c r="J244" t="n">
-        <v>-4.98866852355849</v>
+        <v>-7.9584</v>
       </c>
     </row>
     <row r="245">
@@ -12161,10 +12149,10 @@
         <v>0.71</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3260306255962888</v>
+        <v>-0.4905</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.824735014310932</v>
+        <v>-11.772</v>
       </c>
     </row>
     <row r="246">
@@ -12201,10 +12189,10 @@
         <v>0.64</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3999580652402609</v>
+        <v>-0.5826</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.598993565766261</v>
+        <v>-13.9824</v>
       </c>
     </row>
     <row r="247">
@@ -12241,10 +12229,10 @@
         <v>1.34</v>
       </c>
       <c r="I247" t="n">
-        <v>0.3754957991318588</v>
+        <v>0.9263</v>
       </c>
       <c r="J247" t="n">
-        <v>9.011899179164612</v>
+        <v>22.2312</v>
       </c>
     </row>
     <row r="248">
@@ -12281,10 +12269,10 @@
         <v>1.22</v>
       </c>
       <c r="I248" t="n">
-        <v>0.230891578371499</v>
+        <v>0.6439</v>
       </c>
       <c r="J248" t="n">
-        <v>5.541397880915976</v>
+        <v>15.4536</v>
       </c>
     </row>
     <row r="249">
@@ -12321,10 +12309,10 @@
         <v>1.1</v>
       </c>
       <c r="I249" t="n">
-        <v>0.0976719750200271</v>
+        <v>0.2847</v>
       </c>
       <c r="J249" t="n">
-        <v>2.34412740048065</v>
+        <v>6.8328</v>
       </c>
     </row>
     <row r="250">
@@ -12361,10 +12349,10 @@
         <v>1.02</v>
       </c>
       <c r="I250" t="n">
-        <v>0.003579929968145796</v>
+        <v>0.0118</v>
       </c>
       <c r="J250" t="n">
-        <v>0.08591831923549911</v>
+        <v>0.2832</v>
       </c>
     </row>
     <row r="251">
@@ -12401,10 +12389,10 @@
         <v>0.93</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.08558282999346536</v>
+        <v>-0.3629</v>
       </c>
       <c r="J251" t="n">
-        <v>-2.053987919843169</v>
+        <v>-8.7096</v>
       </c>
     </row>
     <row r="252">
@@ -12441,10 +12429,10 @@
         <v>1.08</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.1216810756328518</v>
+        <v>0.4193</v>
       </c>
       <c r="J252" t="n">
-        <v>-1.581853983227074</v>
+        <v>5.4509</v>
       </c>
     </row>
     <row r="253">
@@ -12481,10 +12469,10 @@
         <v>0.47</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.7626164885662444</v>
+        <v>-0.6852</v>
       </c>
       <c r="J253" t="n">
-        <v>-9.914014351361178</v>
+        <v>-8.9076</v>
       </c>
     </row>
     <row r="254">
@@ -12521,10 +12509,10 @@
         <v>0.47</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.7626164885662444</v>
+        <v>-0.6852</v>
       </c>
       <c r="J254" t="n">
-        <v>-9.914014351361178</v>
+        <v>-8.9076</v>
       </c>
     </row>
     <row r="255">
@@ -12561,10 +12549,10 @@
         <v>0.35</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.8898111119763896</v>
+        <v>-0.858</v>
       </c>
       <c r="J255" t="n">
-        <v>-11.56754445569307</v>
+        <v>-11.154</v>
       </c>
     </row>
     <row r="256">
@@ -12601,10 +12589,10 @@
         <v>0.25</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.9954722218325454</v>
+        <v>-0.9881</v>
       </c>
       <c r="J256" t="n">
-        <v>-12.94113888382309</v>
+        <v>-12.8453</v>
       </c>
     </row>
     <row r="257">
@@ -12641,10 +12629,10 @@
         <v>2.4</v>
       </c>
       <c r="I257" t="n">
-        <v>1.364320715495895</v>
+        <v>1.4398</v>
       </c>
       <c r="J257" t="n">
-        <v>17.73616930144663</v>
+        <v>18.7174</v>
       </c>
     </row>
     <row r="258">
@@ -12681,10 +12669,10 @@
         <v>2.12</v>
       </c>
       <c r="I258" t="n">
-        <v>1.071817261884415</v>
+        <v>1.1898</v>
       </c>
       <c r="J258" t="n">
-        <v>13.93362440449739</v>
+        <v>15.4674</v>
       </c>
     </row>
     <row r="259">
@@ -12721,10 +12709,10 @@
         <v>1.89</v>
       </c>
       <c r="I259" t="n">
-        <v>0.8141505449046668</v>
+        <v>0.9637</v>
       </c>
       <c r="J259" t="n">
-        <v>10.58395708376067</v>
+        <v>12.5281</v>
       </c>
     </row>
     <row r="260">
@@ -12761,10 +12749,10 @@
         <v>1.83</v>
       </c>
       <c r="I260" t="n">
-        <v>0.7535959036005118</v>
+        <v>0.893</v>
       </c>
       <c r="J260" t="n">
-        <v>9.796746746806653</v>
+        <v>11.609</v>
       </c>
     </row>
     <row r="261">
@@ -12801,10 +12789,10 @@
         <v>0.91</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.1931364696586361</v>
+        <v>-0.3219</v>
       </c>
       <c r="J261" t="n">
-        <v>-2.510774105562269</v>
+        <v>-4.1847</v>
       </c>
     </row>
     <row r="262">
@@ -12841,10 +12829,10 @@
         <v>2.39</v>
       </c>
       <c r="I262" t="n">
-        <v>1.199134302213687</v>
+        <v>2.0593</v>
       </c>
       <c r="J262" t="n">
-        <v>22.78355174206006</v>
+        <v>39.1267</v>
       </c>
     </row>
     <row r="263">
@@ -12881,10 +12869,10 @@
         <v>1.38</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3398956421248946</v>
+        <v>0.9172</v>
       </c>
       <c r="J263" t="n">
-        <v>6.458017200372997</v>
+        <v>17.4268</v>
       </c>
     </row>
     <row r="264">
@@ -12921,10 +12909,10 @@
         <v>0.96</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.08284080188811943</v>
+        <v>-0.3261</v>
       </c>
       <c r="J264" t="n">
-        <v>-1.573975235874269</v>
+        <v>-6.1959</v>
       </c>
     </row>
     <row r="265">
@@ -12961,10 +12949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1059273199676759</v>
+        <v>-0.3892</v>
       </c>
       <c r="J265" t="n">
-        <v>-2.012619079385842</v>
+        <v>-7.3948</v>
       </c>
     </row>
     <row r="266">
@@ -13001,10 +12989,10 @@
         <v>0.84</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2149139290776375</v>
+        <v>-0.6571</v>
       </c>
       <c r="J266" t="n">
-        <v>-4.083364652475113</v>
+        <v>-12.4849</v>
       </c>
     </row>
     <row r="267">
@@ -13041,10 +13029,10 @@
         <v>1.41</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3052102024715984</v>
+        <v>0.7003</v>
       </c>
       <c r="J267" t="n">
-        <v>5.798993846960369</v>
+        <v>13.3057</v>
       </c>
     </row>
     <row r="268">
@@ -13081,10 +13069,10 @@
         <v>0.99</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1552586186370932</v>
+        <v>0.0257</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.94991375410477</v>
+        <v>0.4883</v>
       </c>
     </row>
     <row r="269">
@@ -13121,10 +13109,10 @@
         <v>0.8</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3199633504218776</v>
+        <v>-0.3494</v>
       </c>
       <c r="J269" t="n">
-        <v>-6.079303658015675</v>
+        <v>-6.6386</v>
       </c>
     </row>
     <row r="270">
@@ -13161,10 +13149,10 @@
         <v>0.68</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4299527157067123</v>
+        <v>-0.5219</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.169101598427533</v>
+        <v>-9.9161</v>
       </c>
     </row>
     <row r="271">
@@ -13201,10 +13189,10 @@
         <v>0.53</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5636521284333311</v>
+        <v>-0.7125</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.70939044023329</v>
+        <v>-13.5375</v>
       </c>
     </row>
     <row r="272">
@@ -13241,10 +13229,10 @@
         <v>2</v>
       </c>
       <c r="I272" t="n">
-        <v>0.9047708608127326</v>
+        <v>2.0155</v>
       </c>
       <c r="J272" t="n">
-        <v>17.19064635544192</v>
+        <v>38.2945</v>
       </c>
     </row>
     <row r="273">
@@ -13281,10 +13269,10 @@
         <v>1.2</v>
       </c>
       <c r="I273" t="n">
-        <v>0.1675092003780901</v>
+        <v>0.467</v>
       </c>
       <c r="J273" t="n">
-        <v>3.182674807183712</v>
+        <v>8.872999999999999</v>
       </c>
     </row>
     <row r="274">
@@ -13321,10 +13309,10 @@
         <v>1.16</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1269658171943733</v>
+        <v>0.3641</v>
       </c>
       <c r="J274" t="n">
-        <v>2.412350526693093</v>
+        <v>6.9179</v>
       </c>
     </row>
     <row r="275">
@@ -13361,10 +13349,10 @@
         <v>1.1</v>
       </c>
       <c r="I275" t="n">
-        <v>0.06543309436823111</v>
+        <v>0.2027</v>
       </c>
       <c r="J275" t="n">
-        <v>1.243228792996391</v>
+        <v>3.8513</v>
       </c>
     </row>
     <row r="276">
@@ -13401,10 +13389,10 @@
         <v>0.93</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.119669403465409</v>
+        <v>-0.4128</v>
       </c>
       <c r="J276" t="n">
-        <v>-2.273718665842771</v>
+        <v>-7.8432</v>
       </c>
     </row>
     <row r="277">
@@ -13441,10 +13429,10 @@
         <v>1.44</v>
       </c>
       <c r="I277" t="n">
-        <v>0.2905451170984661</v>
+        <v>0.7089</v>
       </c>
       <c r="J277" t="n">
-        <v>5.520357224870856</v>
+        <v>13.4691</v>
       </c>
     </row>
     <row r="278">
@@ -13481,10 +13469,10 @@
         <v>1.26</v>
       </c>
       <c r="I278" t="n">
-        <v>0.07614755048265039</v>
+        <v>0.4824</v>
       </c>
       <c r="J278" t="n">
-        <v>1.446803459170357</v>
+        <v>9.1656</v>
       </c>
     </row>
     <row r="279">
@@ -13521,10 +13509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.235571770621626</v>
+        <v>-0.1348</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.475863641810895</v>
+        <v>-2.5612</v>
       </c>
     </row>
     <row r="280">
@@ -13561,10 +13549,10 @@
         <v>0.74</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4183421529926594</v>
+        <v>-0.4578</v>
       </c>
       <c r="J280" t="n">
-        <v>-7.948500906860529</v>
+        <v>-8.6982</v>
       </c>
     </row>
     <row r="281">
@@ -13601,10 +13589,10 @@
         <v>0.4</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.7125491302487598</v>
+        <v>-0.872</v>
       </c>
       <c r="J281" t="n">
-        <v>-13.53843347472644</v>
+        <v>-16.568</v>
       </c>
     </row>
     <row r="282">
@@ -13641,10 +13629,10 @@
         <v>1.31</v>
       </c>
       <c r="I282" t="n">
-        <v>0.3029925680959115</v>
+        <v>0.8255</v>
       </c>
       <c r="J282" t="n">
-        <v>8.786784474781435</v>
+        <v>23.9395</v>
       </c>
     </row>
     <row r="283">
@@ -13681,10 +13669,10 @@
         <v>1.29</v>
       </c>
       <c r="I283" t="n">
-        <v>0.2814680235683866</v>
+        <v>0.7788</v>
       </c>
       <c r="J283" t="n">
-        <v>8.162572683483212</v>
+        <v>22.5852</v>
       </c>
     </row>
     <row r="284">
@@ -13721,10 +13709,10 @@
         <v>1.15</v>
       </c>
       <c r="I284" t="n">
-        <v>0.1419094104083057</v>
+        <v>0.39</v>
       </c>
       <c r="J284" t="n">
-        <v>4.115372901840865</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="285">
@@ -13761,10 +13749,10 @@
         <v>1.11</v>
       </c>
       <c r="I285" t="n">
-        <v>0.09988652733697848</v>
+        <v>0.2747</v>
       </c>
       <c r="J285" t="n">
-        <v>2.896709292772376</v>
+        <v>7.9663</v>
       </c>
     </row>
     <row r="286">
@@ -13801,10 +13789,10 @@
         <v>1.05</v>
       </c>
       <c r="I286" t="n">
-        <v>0.03424951619553404</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="J286" t="n">
-        <v>0.9932359696704872</v>
+        <v>2.6477</v>
       </c>
     </row>
     <row r="287">
@@ -13841,10 +13829,10 @@
         <v>1.14</v>
       </c>
       <c r="I287" t="n">
-        <v>0.1435092977959085</v>
+        <v>0.348</v>
       </c>
       <c r="J287" t="n">
-        <v>4.161769636081345</v>
+        <v>10.092</v>
       </c>
     </row>
     <row r="288">
@@ -13881,10 +13869,10 @@
         <v>0.87</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1499541508242998</v>
+        <v>-0.2036</v>
       </c>
       <c r="J288" t="n">
-        <v>-4.348670373904693</v>
+        <v>-5.9044</v>
       </c>
     </row>
     <row r="289">
@@ -13921,10 +13909,10 @@
         <v>0.85</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1662169232498175</v>
+        <v>-0.2488</v>
       </c>
       <c r="J289" t="n">
-        <v>-4.820290774244707</v>
+        <v>-7.2152</v>
       </c>
     </row>
     <row r="290">
@@ -13961,10 +13949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.203146648393137</v>
+        <v>-0.3217</v>
       </c>
       <c r="J290" t="n">
-        <v>-5.891252803400973</v>
+        <v>-9.3293</v>
       </c>
     </row>
     <row r="291">
@@ -14001,10 +13989,10 @@
         <v>0.6</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4160971906566599</v>
+        <v>-0.6203</v>
       </c>
       <c r="J291" t="n">
-        <v>-12.06681852904314</v>
+        <v>-17.9887</v>
       </c>
     </row>
     <row r="292">
@@ -14041,10 +14029,10 @@
         <v>1.62</v>
       </c>
       <c r="I292" t="n">
-        <v>0.616354397323696</v>
+        <v>1.521</v>
       </c>
       <c r="J292" t="n">
-        <v>14.7925055357687</v>
+        <v>36.504</v>
       </c>
     </row>
     <row r="293">
@@ -14081,10 +14069,10 @@
         <v>1.46</v>
       </c>
       <c r="I293" t="n">
-        <v>0.4546954129752318</v>
+        <v>1.2076</v>
       </c>
       <c r="J293" t="n">
-        <v>10.91268991140556</v>
+        <v>28.9824</v>
       </c>
     </row>
     <row r="294">
@@ -14121,10 +14109,10 @@
         <v>1.02</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.00620118149128732</v>
+        <v>0.0408</v>
       </c>
       <c r="J294" t="n">
-        <v>-0.1488283557908957</v>
+        <v>0.9792</v>
       </c>
     </row>
     <row r="295">
@@ -14161,10 +14149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.3703137086397078</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="J295" t="n">
-        <v>-8.887529007352988</v>
+        <v>-22.7544</v>
       </c>
     </row>
     <row r="296">
@@ -14201,10 +14189,10 @@
         <v>0.57</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4946756866779806</v>
+        <v>-1.2019</v>
       </c>
       <c r="J296" t="n">
-        <v>-11.87221648027153</v>
+        <v>-28.8456</v>
       </c>
     </row>
     <row r="297">
@@ -14241,10 +14229,10 @@
         <v>1.5</v>
       </c>
       <c r="I297" t="n">
-        <v>0.430217843538803</v>
+        <v>0.7379</v>
       </c>
       <c r="J297" t="n">
-        <v>10.32522824493127</v>
+        <v>17.7096</v>
       </c>
     </row>
     <row r="298">
@@ -14281,10 +14269,10 @@
         <v>1.31</v>
       </c>
       <c r="I298" t="n">
-        <v>0.2144295400239258</v>
+        <v>0.507</v>
       </c>
       <c r="J298" t="n">
-        <v>5.14630896057422</v>
+        <v>12.168</v>
       </c>
     </row>
     <row r="299">
@@ -14321,10 +14309,10 @@
         <v>1.03</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.0839506316791704</v>
+        <v>0.0434</v>
       </c>
       <c r="J299" t="n">
-        <v>-2.01481516030009</v>
+        <v>1.0416</v>
       </c>
     </row>
     <row r="300">
@@ -14361,10 +14349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3126741608229667</v>
+        <v>-0.3861</v>
       </c>
       <c r="J300" t="n">
-        <v>-7.504179859751201</v>
+        <v>-9.266400000000001</v>
       </c>
     </row>
     <row r="301">
@@ -14401,10 +14389,10 @@
         <v>0.75</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3741288876027826</v>
+        <v>-0.4684</v>
       </c>
       <c r="J301" t="n">
-        <v>-8.979093302466781</v>
+        <v>-11.2416</v>
       </c>
     </row>
     <row r="302">
@@ -14441,10 +14429,10 @@
         <v>1.22</v>
       </c>
       <c r="I302" t="n">
-        <v>0.03319299054916976</v>
+        <v>0.4368</v>
       </c>
       <c r="J302" t="n">
-        <v>0.6306668204342254</v>
+        <v>8.299200000000001</v>
       </c>
     </row>
     <row r="303">
@@ -14481,10 +14469,10 @@
         <v>1.16</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.02947109306674738</v>
+        <v>0.3497</v>
       </c>
       <c r="J303" t="n">
-        <v>-0.5599507682682002</v>
+        <v>6.6443</v>
       </c>
     </row>
     <row r="304">
@@ -14521,10 +14509,10 @@
         <v>0.93</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.3252449212769588</v>
+        <v>-0.1364</v>
       </c>
       <c r="J304" t="n">
-        <v>-6.179653504262216</v>
+        <v>-2.5916</v>
       </c>
     </row>
     <row r="305">
@@ -14561,10 +14549,10 @@
         <v>0.87</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3956120643213203</v>
+        <v>-0.2541</v>
       </c>
       <c r="J305" t="n">
-        <v>-7.516629222105086</v>
+        <v>-4.8279</v>
       </c>
     </row>
     <row r="306">
@@ -14601,10 +14589,10 @@
         <v>0.47</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.8956230409051962</v>
+        <v>-0.7901</v>
       </c>
       <c r="J306" t="n">
-        <v>-17.01683777719873</v>
+        <v>-15.0119</v>
       </c>
     </row>
     <row r="307">
@@ -14641,10 +14629,10 @@
         <v>2.1</v>
       </c>
       <c r="I307" t="n">
-        <v>1.285884094395939</v>
+        <v>2.0593</v>
       </c>
       <c r="J307" t="n">
-        <v>24.43179779352285</v>
+        <v>39.1267</v>
       </c>
     </row>
     <row r="308">
@@ -14681,10 +14669,10 @@
         <v>1.73</v>
       </c>
       <c r="I308" t="n">
-        <v>0.8804726209905398</v>
+        <v>1.6176</v>
       </c>
       <c r="J308" t="n">
-        <v>16.72897979882026</v>
+        <v>30.7344</v>
       </c>
     </row>
     <row r="309">
@@ -14721,10 +14709,10 @@
         <v>0.95</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.07210396357448536</v>
+        <v>-0.3541</v>
       </c>
       <c r="J309" t="n">
-        <v>-1.369975307915222</v>
+        <v>-6.7279</v>
       </c>
     </row>
     <row r="310">
@@ -14761,10 +14749,10 @@
         <v>0.87</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1370738371437212</v>
+        <v>-0.5785</v>
       </c>
       <c r="J310" t="n">
-        <v>-2.604402905730703</v>
+        <v>-10.9915</v>
       </c>
     </row>
     <row r="311">
@@ -14801,10 +14789,10 @@
         <v>0.78</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.2122826421491986</v>
+        <v>-0.7952</v>
       </c>
       <c r="J311" t="n">
-        <v>-4.033370200834773</v>
+        <v>-15.1088</v>
       </c>
     </row>
     <row r="312">
@@ -14841,10 +14829,10 @@
         <v>1.7</v>
       </c>
       <c r="I312" t="n">
-        <v>0.4258343013053486</v>
+        <v>1.0193</v>
       </c>
       <c r="J312" t="n">
-        <v>8.090851724801622</v>
+        <v>19.3667</v>
       </c>
     </row>
     <row r="313">
@@ -14881,10 +14869,10 @@
         <v>1.03</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.1954958855883125</v>
+        <v>0.1339</v>
       </c>
       <c r="J313" t="n">
-        <v>-3.714421826177938</v>
+        <v>2.5441</v>
       </c>
     </row>
     <row r="314">
@@ -14921,10 +14909,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.6178646089925526</v>
+        <v>-0.5137</v>
       </c>
       <c r="J314" t="n">
-        <v>-11.7394275708585</v>
+        <v>-9.760300000000001</v>
       </c>
     </row>
     <row r="315">
@@ -14961,10 +14949,10 @@
         <v>0.63</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.6933477994021569</v>
+        <v>-0.5923</v>
       </c>
       <c r="J315" t="n">
-        <v>-13.17360818864098</v>
+        <v>-11.2537</v>
       </c>
     </row>
     <row r="316">
@@ -15001,10 +14989,10 @@
         <v>0.47</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.8870341264422512</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="J316" t="n">
-        <v>-16.85364840240277</v>
+        <v>-14.9492</v>
       </c>
     </row>
     <row r="317">
@@ -15041,10 +15029,10 @@
         <v>2.22</v>
       </c>
       <c r="I317" t="n">
-        <v>1.380342144859858</v>
+        <v>2.0593</v>
       </c>
       <c r="J317" t="n">
-        <v>26.22650075233729</v>
+        <v>39.1267</v>
       </c>
     </row>
     <row r="318">
@@ -15081,10 +15069,10 @@
         <v>1.3</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3198374649136421</v>
+        <v>0.6878</v>
       </c>
       <c r="J318" t="n">
-        <v>6.076911833359199</v>
+        <v>13.0682</v>
       </c>
     </row>
     <row r="319">
@@ -15121,10 +15109,10 @@
         <v>1.25</v>
       </c>
       <c r="I319" t="n">
-        <v>0.2567443823549744</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="J319" t="n">
-        <v>4.878143264744513</v>
+        <v>10.735</v>
       </c>
     </row>
     <row r="320">
@@ -15161,10 +15149,10 @@
         <v>1.07</v>
       </c>
       <c r="I320" t="n">
-        <v>0.0178569675072076</v>
+        <v>0.0989</v>
       </c>
       <c r="J320" t="n">
-        <v>0.3392823826369443</v>
+        <v>1.8791</v>
       </c>
     </row>
     <row r="321">
@@ -15201,10 +15189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.2051916011648005</v>
+        <v>-0.7344000000000001</v>
       </c>
       <c r="J321" t="n">
-        <v>-3.89864042213121</v>
+        <v>-13.9536</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7557/event_7557_evp_summary.xlsx
+++ b/database/event/7557/event_7557_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>8.591799999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3.9036</v>
       </c>
       <c r="D2" t="n">
         <v>3.0495</v>
@@ -545,7 +545,7 @@
         <v>6.7059</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3.0467</v>
       </c>
       <c r="D3" t="n">
         <v>2.2877</v>
@@ -591,7 +591,7 @@
         <v>6.1346</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2.7872</v>
       </c>
       <c r="D4" t="n">
         <v>2.0569</v>
@@ -637,7 +637,7 @@
         <v>5.5449</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.5192</v>
       </c>
       <c r="D5" t="n">
         <v>1.8187</v>
@@ -683,7 +683,7 @@
         <v>4.2196</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1.9171</v>
       </c>
       <c r="D6" t="n">
         <v>1.2833</v>
@@ -729,7 +729,7 @@
         <v>4.0996</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.8626</v>
       </c>
       <c r="D7" t="n">
         <v>1.2348</v>
@@ -775,7 +775,7 @@
         <v>3.557</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1.6161</v>
       </c>
       <c r="D8" t="n">
         <v>1.0156</v>
@@ -821,7 +821,7 @@
         <v>3.5033</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1.5917</v>
       </c>
       <c r="D9" t="n">
         <v>0.9939</v>
@@ -867,7 +867,7 @@
         <v>3.4395</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1.5627</v>
       </c>
       <c r="D10" t="n">
         <v>0.9681</v>
@@ -913,7 +913,7 @@
         <v>3.0832</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.4008</v>
       </c>
       <c r="D11" t="n">
         <v>0.8242</v>
@@ -959,7 +959,7 @@
         <v>2.517</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.1436</v>
       </c>
       <c r="D12" t="n">
         <v>0.5954</v>
@@ -1005,7 +1005,7 @@
         <v>2.2692</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.031</v>
       </c>
       <c r="D13" t="n">
         <v>0.4953</v>
@@ -1051,7 +1051,7 @@
         <v>2.0421</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="D14" t="n">
         <v>0.4036</v>
@@ -1097,7 +1097,7 @@
         <v>1.9614</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.8911</v>
       </c>
       <c r="D15" t="n">
         <v>0.371</v>
@@ -1143,7 +1143,7 @@
         <v>1.9007</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.8636</v>
       </c>
       <c r="D16" t="n">
         <v>0.3465</v>
@@ -1189,7 +1189,7 @@
         <v>1.7801</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.8088</v>
       </c>
       <c r="D17" t="n">
         <v>0.2978</v>
@@ -1235,7 +1235,7 @@
         <v>1.5134</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.6876</v>
       </c>
       <c r="D18" t="n">
         <v>0.19</v>
@@ -1281,7 +1281,7 @@
         <v>1.2997</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.5905</v>
       </c>
       <c r="D19" t="n">
         <v>0.1037</v>
@@ -1327,7 +1327,7 @@
         <v>1.2004</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.5454</v>
       </c>
       <c r="D20" t="n">
         <v>0.0636</v>
@@ -1373,7 +1373,7 @@
         <v>1.0946</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.4973</v>
       </c>
       <c r="D21" t="n">
         <v>0.0208</v>
@@ -1419,7 +1419,7 @@
         <v>0.9623</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.4372</v>
       </c>
       <c r="D22" t="n">
         <v>-0.0326</v>
@@ -1465,7 +1465,7 @@
         <v>0.8855</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.4023</v>
       </c>
       <c r="D23" t="n">
         <v>-0.0636</v>
@@ -1511,7 +1511,7 @@
         <v>0.5413</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.2459</v>
       </c>
       <c r="D24" t="n">
         <v>-0.2027</v>
@@ -1557,7 +1557,7 @@
         <v>0.3202</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.1455</v>
       </c>
       <c r="D25" t="n">
         <v>-0.292</v>
@@ -1603,7 +1603,7 @@
         <v>0.2431</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.1104</v>
       </c>
       <c r="D26" t="n">
         <v>-0.3232</v>
@@ -1649,7 +1649,7 @@
         <v>-0.0636</v>
       </c>
       <c r="C27" t="n">
-        <v>-0</v>
+        <v>-0.0289</v>
       </c>
       <c r="D27" t="n">
         <v>-0.4471</v>
@@ -1695,7 +1695,7 @@
         <v>-0.204</v>
       </c>
       <c r="C28" t="n">
-        <v>-0</v>
+        <v>-0.0927</v>
       </c>
       <c r="D28" t="n">
         <v>-0.5038</v>
@@ -1741,7 +1741,7 @@
         <v>-0.2858</v>
       </c>
       <c r="C29" t="n">
-        <v>-0</v>
+        <v>-0.1298</v>
       </c>
       <c r="D29" t="n">
         <v>-0.5368000000000001</v>
@@ -1787,7 +1787,7 @@
         <v>-0.4115</v>
       </c>
       <c r="C30" t="n">
-        <v>-0</v>
+        <v>-0.187</v>
       </c>
       <c r="D30" t="n">
         <v>-0.5876</v>
@@ -1833,7 +1833,7 @@
         <v>-0.6786</v>
       </c>
       <c r="C31" t="n">
-        <v>-0</v>
+        <v>-0.3083</v>
       </c>
       <c r="D31" t="n">
         <v>-0.6955</v>
@@ -1879,7 +1879,7 @@
         <v>-0.9315</v>
       </c>
       <c r="C32" t="n">
-        <v>-0</v>
+        <v>-0.4232</v>
       </c>
       <c r="D32" t="n">
         <v>-0.7977</v>
@@ -1925,7 +1925,7 @@
         <v>-1.0009</v>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>-0.4547</v>
       </c>
       <c r="D33" t="n">
         <v>-0.8257</v>
@@ -1971,7 +1971,7 @@
         <v>-1.0025</v>
       </c>
       <c r="C34" t="n">
-        <v>-0</v>
+        <v>-0.4555</v>
       </c>
       <c r="D34" t="n">
         <v>-0.8264</v>
@@ -2017,7 +2017,7 @@
         <v>-1.1192</v>
       </c>
       <c r="C35" t="n">
-        <v>-0</v>
+        <v>-0.5085</v>
       </c>
       <c r="D35" t="n">
         <v>-0.8735000000000001</v>
@@ -2063,7 +2063,7 @@
         <v>-1.2644</v>
       </c>
       <c r="C36" t="n">
-        <v>-0</v>
+        <v>-0.5745</v>
       </c>
       <c r="D36" t="n">
         <v>-0.9322</v>
@@ -2109,7 +2109,7 @@
         <v>-1.6564</v>
       </c>
       <c r="C37" t="n">
-        <v>-0</v>
+        <v>-0.7526</v>
       </c>
       <c r="D37" t="n">
         <v>-1.0905</v>
@@ -2155,7 +2155,7 @@
         <v>-2.4414</v>
       </c>
       <c r="C38" t="n">
-        <v>-0</v>
+        <v>-1.1092</v>
       </c>
       <c r="D38" t="n">
         <v>-1.4076</v>
@@ -2201,7 +2201,7 @@
         <v>-2.4801</v>
       </c>
       <c r="C39" t="n">
-        <v>-0</v>
+        <v>-1.1268</v>
       </c>
       <c r="D39" t="n">
         <v>-1.4233</v>
@@ -2247,7 +2247,7 @@
         <v>-2.9542</v>
       </c>
       <c r="C40" t="n">
-        <v>-0</v>
+        <v>-1.3422</v>
       </c>
       <c r="D40" t="n">
         <v>-1.6148</v>
@@ -2293,7 +2293,7 @@
         <v>-3.0362</v>
       </c>
       <c r="C41" t="n">
-        <v>-0</v>
+        <v>-1.3795</v>
       </c>
       <c r="D41" t="n">
         <v>-1.6479</v>

--- a/database/event/7557/event_7557_evp_summary.xlsx
+++ b/database/event/7557/event_7557_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>3.9036</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0495</v>
+        <v>2.9791</v>
       </c>
       <c r="E2" t="n">
         <v>8.591799999999999</v>
@@ -548,7 +548,7 @@
         <v>3.0467</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2877</v>
+        <v>2.2277</v>
       </c>
       <c r="E3" t="n">
         <v>6.7059</v>
@@ -594,7 +594,7 @@
         <v>2.7872</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0569</v>
+        <v>2.0001</v>
       </c>
       <c r="E4" t="n">
         <v>6.1346</v>
@@ -640,7 +640,7 @@
         <v>2.5192</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8187</v>
+        <v>1.7652</v>
       </c>
       <c r="E5" t="n">
         <v>5.5449</v>
@@ -686,7 +686,7 @@
         <v>1.9171</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2833</v>
+        <v>1.2372</v>
       </c>
       <c r="E6" t="n">
         <v>4.2196</v>
@@ -732,7 +732,7 @@
         <v>1.8626</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2348</v>
+        <v>1.1894</v>
       </c>
       <c r="E7" t="n">
         <v>4.0996</v>
@@ -778,7 +778,7 @@
         <v>1.6161</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0156</v>
+        <v>0.9732</v>
       </c>
       <c r="E8" t="n">
         <v>3.557</v>
@@ -824,7 +824,7 @@
         <v>1.5917</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9939</v>
+        <v>0.9518</v>
       </c>
       <c r="E9" t="n">
         <v>3.5033</v>
@@ -870,7 +870,7 @@
         <v>1.5627</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9681</v>
+        <v>0.9264</v>
       </c>
       <c r="E10" t="n">
         <v>3.4395</v>
@@ -916,7 +916,7 @@
         <v>1.4008</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8242</v>
+        <v>0.7844</v>
       </c>
       <c r="E11" t="n">
         <v>3.0832</v>
@@ -962,7 +962,7 @@
         <v>1.1436</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5954</v>
+        <v>0.5589</v>
       </c>
       <c r="E12" t="n">
         <v>2.517</v>
@@ -1008,7 +1008,7 @@
         <v>1.031</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4953</v>
+        <v>0.4601</v>
       </c>
       <c r="E13" t="n">
         <v>2.2692</v>
@@ -1054,7 +1054,7 @@
         <v>0.9278</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4036</v>
+        <v>0.3697</v>
       </c>
       <c r="E14" t="n">
         <v>2.0421</v>
@@ -1100,7 +1100,7 @@
         <v>0.8911</v>
       </c>
       <c r="D15" t="n">
-        <v>0.371</v>
+        <v>0.3375</v>
       </c>
       <c r="E15" t="n">
         <v>1.9614</v>
@@ -1146,7 +1146,7 @@
         <v>0.8636</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3465</v>
+        <v>0.3133</v>
       </c>
       <c r="E16" t="n">
         <v>1.9007</v>
@@ -1192,7 +1192,7 @@
         <v>0.8088</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2978</v>
+        <v>0.2653</v>
       </c>
       <c r="E17" t="n">
         <v>1.7801</v>
@@ -1238,7 +1238,7 @@
         <v>0.6876</v>
       </c>
       <c r="D18" t="n">
-        <v>0.19</v>
+        <v>0.159</v>
       </c>
       <c r="E18" t="n">
         <v>1.5134</v>
@@ -1284,7 +1284,7 @@
         <v>0.5905</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1037</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="E19" t="n">
         <v>1.2997</v>
@@ -1330,7 +1330,7 @@
         <v>0.5454</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0636</v>
+        <v>0.0343</v>
       </c>
       <c r="E20" t="n">
         <v>1.2004</v>
@@ -1376,7 +1376,7 @@
         <v>0.4973</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0208</v>
+        <v>-0.0078</v>
       </c>
       <c r="E21" t="n">
         <v>1.0946</v>
@@ -1422,7 +1422,7 @@
         <v>0.4372</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0326</v>
+        <v>-0.0605</v>
       </c>
       <c r="E22" t="n">
         <v>0.9623</v>
@@ -1468,7 +1468,7 @@
         <v>0.4023</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0636</v>
+        <v>-0.0911</v>
       </c>
       <c r="E23" t="n">
         <v>0.8855</v>
@@ -1514,7 +1514,7 @@
         <v>0.2459</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2027</v>
+        <v>-0.2283</v>
       </c>
       <c r="E24" t="n">
         <v>0.5413</v>
@@ -1560,7 +1560,7 @@
         <v>0.1455</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.292</v>
+        <v>-0.3163</v>
       </c>
       <c r="E25" t="n">
         <v>0.3202</v>
@@ -1606,7 +1606,7 @@
         <v>0.1104</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3232</v>
+        <v>-0.3471</v>
       </c>
       <c r="E26" t="n">
         <v>0.2431</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0289</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4471</v>
+        <v>-0.4692</v>
       </c>
       <c r="E27" t="n">
         <v>-0.0636</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0927</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5038</v>
+        <v>-0.5252</v>
       </c>
       <c r="E28" t="n">
         <v>-0.204</v>
@@ -1744,7 +1744,7 @@
         <v>-0.1298</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.5578</v>
       </c>
       <c r="E29" t="n">
         <v>-0.2858</v>
@@ -1790,7 +1790,7 @@
         <v>-0.187</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5876</v>
+        <v>-0.6079</v>
       </c>
       <c r="E30" t="n">
         <v>-0.4115</v>
@@ -1836,7 +1836,7 @@
         <v>-0.3083</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6955</v>
+        <v>-0.7143</v>
       </c>
       <c r="E31" t="n">
         <v>-0.6786</v>
@@ -1882,7 +1882,7 @@
         <v>-0.4232</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7977</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="E32" t="n">
         <v>-0.9315</v>
@@ -1928,7 +1928,7 @@
         <v>-0.4547</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8257</v>
+        <v>-0.8427</v>
       </c>
       <c r="E33" t="n">
         <v>-1.0009</v>
@@ -1974,7 +1974,7 @@
         <v>-0.4555</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8264</v>
+        <v>-0.8433</v>
       </c>
       <c r="E34" t="n">
         <v>-1.0025</v>
@@ -2020,7 +2020,7 @@
         <v>-0.5085</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.8898</v>
       </c>
       <c r="E35" t="n">
         <v>-1.1192</v>
@@ -2066,7 +2066,7 @@
         <v>-0.5745</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9322</v>
+        <v>-0.9476</v>
       </c>
       <c r="E36" t="n">
         <v>-1.2644</v>
@@ -2112,7 +2112,7 @@
         <v>-0.7526</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0905</v>
+        <v>-1.1038</v>
       </c>
       <c r="E37" t="n">
         <v>-1.6564</v>
@@ -2158,7 +2158,7 @@
         <v>-1.1092</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.4076</v>
+        <v>-1.4166</v>
       </c>
       <c r="E38" t="n">
         <v>-2.4414</v>
@@ -2204,7 +2204,7 @@
         <v>-1.1268</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.4233</v>
+        <v>-1.432</v>
       </c>
       <c r="E39" t="n">
         <v>-2.4801</v>
@@ -2250,7 +2250,7 @@
         <v>-1.3422</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6148</v>
+        <v>-1.6209</v>
       </c>
       <c r="E40" t="n">
         <v>-2.9542</v>
@@ -2296,7 +2296,7 @@
         <v>-1.3795</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6479</v>
+        <v>-1.6535</v>
       </c>
       <c r="E41" t="n">
         <v>-3.0362</v>

--- a/database/event/7557/event_7557_evp_summary.xlsx
+++ b/database/event/7557/event_7557_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.591799999999999</v>
+        <v>8.1119</v>
       </c>
       <c r="C2" t="n">
-        <v>3.9036</v>
+        <v>3.6855</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9791</v>
+        <v>3.0241</v>
       </c>
       <c r="E2" t="n">
-        <v>8.591799999999999</v>
+        <v>8.1119</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1935</v>
+        <v>2.9824</v>
       </c>
       <c r="G2" t="n">
-        <v>5.3983</v>
+        <v>5.1295</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1935</v>
+        <v>5.0218</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5884</v>
+        <v>2.6111</v>
       </c>
       <c r="J2" t="n">
-        <v>5.3983</v>
+        <v>5.1295</v>
       </c>
       <c r="K2" t="n">
         <v>103</v>
@@ -529,7 +529,7 @@
         <v>122</v>
       </c>
       <c r="M2" t="n">
-        <v>7.9867</v>
+        <v>7.740600000000001</v>
       </c>
       <c r="N2" t="n">
         <v>225</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.7059</v>
+        <v>6.2944</v>
       </c>
       <c r="C3" t="n">
-        <v>3.0467</v>
+        <v>2.8598</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2277</v>
+        <v>2.2036</v>
       </c>
       <c r="E3" t="n">
-        <v>6.7059</v>
+        <v>6.2944</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0515</v>
+        <v>3.3882</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6543</v>
+        <v>2.9062</v>
       </c>
       <c r="H3" t="n">
-        <v>3.0515</v>
+        <v>4.0801</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0515</v>
+        <v>4.0801</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6543</v>
+        <v>2.9062</v>
       </c>
       <c r="K3" t="n">
         <v>109</v>
@@ -575,7 +575,7 @@
         <v>102</v>
       </c>
       <c r="M3" t="n">
-        <v>6.7058</v>
+        <v>6.9863</v>
       </c>
       <c r="N3" t="n">
         <v>211</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.1346</v>
+        <v>6.2435</v>
       </c>
       <c r="C4" t="n">
-        <v>2.7872</v>
+        <v>2.8366</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0001</v>
+        <v>2.1806</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1346</v>
+        <v>6.2435</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5166</v>
+        <v>2.7924</v>
       </c>
       <c r="G4" t="n">
-        <v>3.618</v>
+        <v>3.4511</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5166</v>
+        <v>2.7924</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5166</v>
+        <v>2.7924</v>
       </c>
       <c r="J4" t="n">
-        <v>3.618</v>
+        <v>3.4511</v>
       </c>
       <c r="K4" t="n">
         <v>98</v>
@@ -621,7 +621,7 @@
         <v>169</v>
       </c>
       <c r="M4" t="n">
-        <v>6.1346</v>
+        <v>6.2435</v>
       </c>
       <c r="N4" t="n">
         <v>267</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.5449</v>
+        <v>5.1459</v>
       </c>
       <c r="C5" t="n">
-        <v>2.5192</v>
+        <v>2.338</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7652</v>
+        <v>1.6851</v>
       </c>
       <c r="E5" t="n">
-        <v>5.5449</v>
+        <v>5.1459</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0604</v>
+        <v>3.0112</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4845</v>
+        <v>2.1347</v>
       </c>
       <c r="H5" t="n">
-        <v>3.0604</v>
+        <v>5.1233</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4805</v>
+        <v>2.6639</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4845</v>
+        <v>2.1347</v>
       </c>
       <c r="K5" t="n">
         <v>103</v>
@@ -667,7 +667,7 @@
         <v>122</v>
       </c>
       <c r="M5" t="n">
-        <v>4.965</v>
+        <v>4.7986</v>
       </c>
       <c r="N5" t="n">
         <v>225</v>
@@ -676,219 +676,219 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2196</v>
+        <v>4.5623</v>
       </c>
       <c r="C6" t="n">
-        <v>1.9171</v>
+        <v>2.0728</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2372</v>
+        <v>1.4216</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2196</v>
+        <v>4.5623</v>
       </c>
       <c r="F6" t="n">
-        <v>4.2064</v>
+        <v>2.7384</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0132</v>
+        <v>1.8239</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3627</v>
+        <v>4.1621</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5361</v>
+        <v>2.1641</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0132</v>
+        <v>1.8239</v>
       </c>
       <c r="K6" t="n">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="L6" t="n">
-        <v>52</v>
+        <v>122</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5493</v>
+        <v>3.988</v>
       </c>
       <c r="N6" t="n">
-        <v>132</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0996</v>
+        <v>3.7615</v>
       </c>
       <c r="C7" t="n">
-        <v>1.8626</v>
+        <v>1.709</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1894</v>
+        <v>1.0601</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0996</v>
+        <v>3.7615</v>
       </c>
       <c r="F7" t="n">
-        <v>1.505</v>
+        <v>2.7935</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5946</v>
+        <v>0.968</v>
       </c>
       <c r="H7" t="n">
-        <v>1.505</v>
+        <v>4.3562</v>
       </c>
       <c r="I7" t="n">
-        <v>1.505</v>
+        <v>2.265</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5946</v>
+        <v>0.968</v>
       </c>
       <c r="K7" t="n">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="L7" t="n">
-        <v>169</v>
+        <v>52</v>
       </c>
       <c r="M7" t="n">
-        <v>4.0996</v>
+        <v>3.233</v>
       </c>
       <c r="N7" t="n">
-        <v>267</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.557</v>
+        <v>3.4958</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6161</v>
+        <v>1.5883</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9732</v>
+        <v>0.9402</v>
       </c>
       <c r="E8" t="n">
-        <v>3.557</v>
+        <v>3.4958</v>
       </c>
       <c r="F8" t="n">
-        <v>2.169</v>
+        <v>3.4801</v>
       </c>
       <c r="G8" t="n">
-        <v>1.388</v>
+        <v>0.0157</v>
       </c>
       <c r="H8" t="n">
-        <v>2.169</v>
+        <v>6.7754</v>
       </c>
       <c r="I8" t="n">
-        <v>1.758</v>
+        <v>3.5229</v>
       </c>
       <c r="J8" t="n">
-        <v>1.388</v>
+        <v>0.0157</v>
       </c>
       <c r="K8" t="n">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="L8" t="n">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="M8" t="n">
-        <v>3.146</v>
+        <v>3.5386</v>
       </c>
       <c r="N8" t="n">
-        <v>225</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5033</v>
+        <v>3.4419</v>
       </c>
       <c r="C9" t="n">
-        <v>1.5917</v>
+        <v>1.5638</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9518</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5033</v>
+        <v>3.4419</v>
       </c>
       <c r="F9" t="n">
-        <v>3.516</v>
+        <v>1.5522</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0127</v>
+        <v>1.8897</v>
       </c>
       <c r="H9" t="n">
-        <v>3.516</v>
+        <v>1.5522</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8498</v>
+        <v>1.5522</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0127</v>
+        <v>1.8897</v>
       </c>
       <c r="K9" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="L9" t="n">
-        <v>52</v>
+        <v>169</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8371</v>
+        <v>3.4419</v>
       </c>
       <c r="N9" t="n">
-        <v>132</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4395</v>
+        <v>3.2421</v>
       </c>
       <c r="C10" t="n">
-        <v>1.5627</v>
+        <v>1.473</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9264</v>
+        <v>0.8256</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4395</v>
+        <v>3.2421</v>
       </c>
       <c r="F10" t="n">
-        <v>2.175</v>
+        <v>3.0691</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2645</v>
+        <v>0.173</v>
       </c>
       <c r="H10" t="n">
-        <v>2.175</v>
+        <v>5.3272</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7629</v>
+        <v>2.7699</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2645</v>
+        <v>0.173</v>
       </c>
       <c r="K10" t="n">
         <v>80</v>
@@ -897,7 +897,7 @@
         <v>52</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0274</v>
+        <v>2.9429</v>
       </c>
       <c r="N10" t="n">
         <v>132</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0832</v>
+        <v>3.11</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4008</v>
+        <v>1.413</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7844</v>
+        <v>0.766</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0832</v>
+        <v>3.11</v>
       </c>
       <c r="F11" t="n">
-        <v>3.0832</v>
+        <v>3.11</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.0832</v>
+        <v>3.4693</v>
       </c>
       <c r="I11" t="n">
-        <v>3.0832</v>
+        <v>3.4693</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0832</v>
+        <v>3.4693</v>
       </c>
       <c r="N11" t="n">
         <v>97</v>
@@ -952,185 +952,185 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.517</v>
+        <v>2.9318</v>
       </c>
       <c r="C12" t="n">
-        <v>1.1436</v>
+        <v>1.332</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5589</v>
+        <v>0.6855</v>
       </c>
       <c r="E12" t="n">
-        <v>2.517</v>
+        <v>2.9318</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6238</v>
+        <v>1.0953</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1068</v>
+        <v>1.8365</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6238</v>
+        <v>1.0953</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6238</v>
+        <v>0.5695</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1068</v>
+        <v>1.8365</v>
       </c>
       <c r="K12" t="n">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="L12" t="n">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="M12" t="n">
-        <v>2.517</v>
+        <v>2.406</v>
       </c>
       <c r="N12" t="n">
-        <v>171</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2692</v>
+        <v>2.9208</v>
       </c>
       <c r="C13" t="n">
-        <v>1.031</v>
+        <v>1.327</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4601</v>
+        <v>0.6806</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2692</v>
+        <v>2.9208</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1574</v>
+        <v>2.9208</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1118</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1574</v>
+        <v>3.0539</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1574</v>
+        <v>3.0539</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1118</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="L13" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2692</v>
+        <v>3.0539</v>
       </c>
       <c r="N13" t="n">
-        <v>211</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0421</v>
+        <v>2.7895</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9278</v>
+        <v>1.2674</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3697</v>
+        <v>0.6213</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0421</v>
+        <v>2.7895</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7327</v>
+        <v>2.8454</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7748</v>
+        <v>-0.0559</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7327</v>
+        <v>2.8883</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7327</v>
+        <v>2.8883</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7748</v>
+        <v>-0.0559</v>
       </c>
       <c r="K14" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L14" t="n">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0421</v>
+        <v>2.8324</v>
       </c>
       <c r="N14" t="n">
-        <v>211</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9614</v>
+        <v>2.7681</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8911</v>
+        <v>1.2576</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3375</v>
+        <v>0.6116</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9614</v>
+        <v>2.7681</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9614</v>
+        <v>1.8089</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9614</v>
+        <v>1.8089</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9614</v>
+        <v>1.8089</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9614</v>
+        <v>2.7681</v>
       </c>
       <c r="N15" t="n">
-        <v>114</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9007</v>
+        <v>2.0829</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8636</v>
+        <v>0.9463</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3133</v>
+        <v>0.3023</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9007</v>
+        <v>2.0829</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9007</v>
+        <v>2.0829</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9007</v>
+        <v>2.0829</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9007</v>
+        <v>2.0829</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9007</v>
+        <v>2.0829</v>
       </c>
       <c r="N16" t="n">
         <v>114</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7801</v>
+        <v>2.0757</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8088</v>
+        <v>0.9431</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2653</v>
+        <v>0.2991</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7801</v>
+        <v>2.0757</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1191</v>
+        <v>2.168</v>
       </c>
       <c r="G17" t="n">
-        <v>1.661</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1191</v>
+        <v>2.168</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0965</v>
+        <v>2.168</v>
       </c>
       <c r="J17" t="n">
-        <v>1.661</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="L17" t="n">
-        <v>122</v>
+        <v>38</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7575</v>
+        <v>2.0757</v>
       </c>
       <c r="N17" t="n">
-        <v>225</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5134</v>
+        <v>1.9248</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6876</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>0.159</v>
+        <v>0.2309</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5134</v>
+        <v>1.9248</v>
       </c>
       <c r="F18" t="n">
-        <v>1.681</v>
+        <v>-0.3803</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1676</v>
+        <v>2.3051</v>
       </c>
       <c r="H18" t="n">
-        <v>1.681</v>
+        <v>-0.3803</v>
       </c>
       <c r="I18" t="n">
-        <v>1.681</v>
+        <v>-0.3803</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1676</v>
+        <v>2.3051</v>
       </c>
       <c r="K18" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="L18" t="n">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5134</v>
+        <v>1.9248</v>
       </c>
       <c r="N18" t="n">
-        <v>133</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2997</v>
+        <v>1.8653</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5905</v>
+        <v>0.8475</v>
       </c>
       <c r="D19" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.2041</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2997</v>
+        <v>1.8653</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9772999999999999</v>
+        <v>1.4677</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3224</v>
+        <v>0.3976</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9772999999999999</v>
+        <v>1.4677</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9772999999999999</v>
+        <v>1.4677</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3224</v>
+        <v>0.3976</v>
       </c>
       <c r="K19" t="n">
         <v>112</v>
@@ -1311,7 +1311,7 @@
         <v>59</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2997</v>
+        <v>1.8653</v>
       </c>
       <c r="N19" t="n">
         <v>171</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2004</v>
+        <v>1.5435</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5454</v>
+        <v>0.7013</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0343</v>
+        <v>0.0588</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2004</v>
+        <v>1.5435</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2004</v>
+        <v>1.5435</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2004</v>
+        <v>1.5435</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2004</v>
+        <v>1.5435</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2004</v>
+        <v>1.5435</v>
       </c>
       <c r="N20" t="n">
         <v>114</v>
@@ -1366,127 +1366,127 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0946</v>
+        <v>1.3054</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4973</v>
+        <v>0.5931</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0078</v>
+        <v>-0.0487</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0946</v>
+        <v>1.3054</v>
       </c>
       <c r="F21" t="n">
-        <v>0.22</v>
+        <v>1.4134</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8746</v>
+        <v>-0.108</v>
       </c>
       <c r="H21" t="n">
-        <v>0.22</v>
+        <v>1.4134</v>
       </c>
       <c r="I21" t="n">
-        <v>0.22</v>
+        <v>0.7349</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8746</v>
+        <v>-0.108</v>
       </c>
       <c r="K21" t="n">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="L21" t="n">
-        <v>169</v>
+        <v>52</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0946</v>
+        <v>0.6269</v>
       </c>
       <c r="N21" t="n">
-        <v>267</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9623</v>
+        <v>1.219</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4372</v>
+        <v>0.5538</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0605</v>
+        <v>-0.0877</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9623</v>
+        <v>1.219</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1693</v>
+        <v>1.3978</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.207</v>
+        <v>-0.1788</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1693</v>
+        <v>1.3978</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1693</v>
+        <v>1.3978</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.207</v>
+        <v>-0.1788</v>
       </c>
       <c r="K22" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="L22" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9623</v>
+        <v>1.219</v>
       </c>
       <c r="N22" t="n">
-        <v>133</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8855</v>
+        <v>1.2097</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4023</v>
+        <v>0.5496</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0911</v>
+        <v>-0.0919</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8855</v>
+        <v>1.2097</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5506</v>
+        <v>1.2155</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3349</v>
+        <v>-0.0058</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5506</v>
+        <v>1.2155</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5506</v>
+        <v>1.2155</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3349</v>
+        <v>-0.0058</v>
       </c>
       <c r="K23" t="n">
         <v>95</v>
@@ -1495,7 +1495,7 @@
         <v>38</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8855</v>
+        <v>1.2097</v>
       </c>
       <c r="N23" t="n">
         <v>133</v>
@@ -1504,81 +1504,81 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5413</v>
+        <v>1.0239</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2459</v>
+        <v>0.4652</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2283</v>
+        <v>-0.1758</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5413</v>
+        <v>1.0239</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9825</v>
+        <v>0.665</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4412</v>
+        <v>0.3589</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9825</v>
+        <v>0.665</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9825</v>
+        <v>0.665</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4412</v>
+        <v>0.3589</v>
       </c>
       <c r="K24" t="n">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="L24" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5413000000000001</v>
+        <v>1.0239</v>
       </c>
       <c r="N24" t="n">
-        <v>171</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3202</v>
+        <v>1.0117</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1455</v>
+        <v>0.4597</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3163</v>
+        <v>-0.1813</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3202</v>
+        <v>1.0117</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4371</v>
+        <v>0.3694</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7573</v>
+        <v>0.6423</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4371</v>
+        <v>0.3694</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4371</v>
+        <v>0.3694</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7573</v>
+        <v>0.6423</v>
       </c>
       <c r="K25" t="n">
         <v>98</v>
@@ -1587,7 +1587,7 @@
         <v>169</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3202</v>
+        <v>1.0117</v>
       </c>
       <c r="N25" t="n">
         <v>267</v>
@@ -1596,185 +1596,185 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2431</v>
+        <v>0.3345</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1104</v>
+        <v>0.152</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3471</v>
+        <v>-0.487</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2431</v>
+        <v>0.3345</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5855</v>
+        <v>0.3345</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.3424</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5855</v>
+        <v>0.3345</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4746</v>
+        <v>0.3345</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3424</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="L26" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1322</v>
+        <v>0.3345</v>
       </c>
       <c r="N26" t="n">
-        <v>132</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0636</v>
+        <v>0.2512</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0289</v>
+        <v>0.1141</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4692</v>
+        <v>-0.5246</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0636</v>
+        <v>0.2512</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0636</v>
+        <v>-0.4193</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.6705</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0636</v>
+        <v>-0.4193</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0636</v>
+        <v>-0.4193</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.6705</v>
       </c>
       <c r="K27" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0636</v>
+        <v>0.2512</v>
       </c>
       <c r="N27" t="n">
-        <v>97</v>
+        <v>267</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.204</v>
+        <v>0.1572</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0927</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5252</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.204</v>
+        <v>0.1572</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.7369</v>
+        <v>0.1886</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5329</v>
+        <v>-0.0314</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.7369</v>
+        <v>0.1886</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.7369</v>
+        <v>0.1886</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5329</v>
+        <v>-0.0314</v>
       </c>
       <c r="K28" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="L28" t="n">
-        <v>169</v>
+        <v>59</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.204</v>
+        <v>0.1572</v>
       </c>
       <c r="N28" t="n">
-        <v>267</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2858</v>
+        <v>0.1301</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1298</v>
+        <v>0.0591</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5578</v>
+        <v>-0.5793</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2858</v>
+        <v>0.1301</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1751</v>
+        <v>-0.1606</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.1107</v>
+        <v>0.2907</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1751</v>
+        <v>-0.1606</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1751</v>
+        <v>-0.1606</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.1107</v>
+        <v>0.2907</v>
       </c>
       <c r="K29" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="L29" t="n">
-        <v>59</v>
+        <v>169</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2858</v>
+        <v>0.1301</v>
       </c>
       <c r="N29" t="n">
-        <v>171</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30">
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4115</v>
+        <v>0.0318</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.187</v>
+        <v>0.0144</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6079</v>
+        <v>-0.6237</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4115</v>
+        <v>0.0318</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.7056</v>
+        <v>-0.1235</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2941</v>
+        <v>0.1553</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7056</v>
+        <v>-0.1235</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7056</v>
+        <v>-0.1235</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2941</v>
+        <v>0.1553</v>
       </c>
       <c r="K30" t="n">
         <v>109</v>
@@ -1817,7 +1817,7 @@
         <v>102</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4115</v>
+        <v>0.03179999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>211</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6786</v>
+        <v>-0.1488</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3083</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7143</v>
+        <v>-0.7052</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6786</v>
+        <v>-0.1488</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.6786</v>
+        <v>-0.1488</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.6786</v>
+        <v>-0.1488</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6786</v>
+        <v>-0.1488</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.6786</v>
+        <v>-0.1488</v>
       </c>
       <c r="N31" t="n">
         <v>114</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.9315</v>
+        <v>-0.5093</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.4232</v>
+        <v>-0.2314</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8149999999999999</v>
+        <v>-0.8679</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.9315</v>
+        <v>-0.5093</v>
       </c>
       <c r="F32" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.2563</v>
       </c>
       <c r="G32" t="n">
-        <v>-1</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.2563</v>
       </c>
       <c r="I32" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.2563</v>
       </c>
       <c r="J32" t="n">
-        <v>-1</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="K32" t="n">
         <v>95</v>
@@ -1909,7 +1909,7 @@
         <v>38</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.9315</v>
+        <v>-0.5093</v>
       </c>
       <c r="N32" t="n">
         <v>133</v>
@@ -1918,78 +1918,78 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.0009</v>
+        <v>-0.5924</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.4547</v>
+        <v>-0.2691</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8427</v>
+        <v>-0.9055</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0009</v>
+        <v>-0.5924</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.0009</v>
+        <v>-0.6039</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.0115</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.0009</v>
+        <v>-0.6039</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.0009</v>
+        <v>-0.6039</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.0115</v>
       </c>
       <c r="K33" t="n">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.0009</v>
+        <v>-0.5924</v>
       </c>
       <c r="N33" t="n">
-        <v>97</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0025</v>
+        <v>-0.6471</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4555</v>
+        <v>-0.294</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8433</v>
+        <v>-0.9301</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0025</v>
+        <v>-0.6471</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.0025</v>
+        <v>-0.6471</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.0025</v>
+        <v>-0.6471</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.0025</v>
+        <v>-0.6471</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.0025</v>
+        <v>-0.6471</v>
       </c>
       <c r="N34" t="n">
         <v>97</v>
@@ -2010,78 +2010,78 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1192</v>
+        <v>-0.6621</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.5085</v>
+        <v>-0.3008</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8898</v>
+        <v>-0.9369</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1192</v>
+        <v>-0.6621</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.0649</v>
+        <v>-0.6621</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0543</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.0649</v>
+        <v>-0.6621</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.0649</v>
+        <v>-0.6621</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.0543</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="L35" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1192</v>
+        <v>-0.6621</v>
       </c>
       <c r="N35" t="n">
-        <v>171</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2644</v>
+        <v>-0.7961</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.5745</v>
+        <v>-0.3617</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9476</v>
+        <v>-0.9974</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2644</v>
+        <v>-0.7961</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.2644</v>
+        <v>-0.7961</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2644</v>
+        <v>-0.7961</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.2644</v>
+        <v>-0.7961</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.2644</v>
+        <v>-0.7961</v>
       </c>
       <c r="N36" t="n">
         <v>97</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.6564</v>
+        <v>-1.3718</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.7526</v>
+        <v>-0.6233</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1038</v>
+        <v>-1.2573</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.6564</v>
+        <v>-1.3718</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.6564</v>
+        <v>-1.3718</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.6564</v>
+        <v>-1.3718</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.6564</v>
+        <v>-1.3718</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.6564</v>
+        <v>-1.3718</v>
       </c>
       <c r="N37" t="n">
         <v>114</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.4414</v>
+        <v>-2.0373</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.1092</v>
+        <v>-0.9256</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.4166</v>
+        <v>-1.5578</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.4414</v>
+        <v>-2.0373</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.4414</v>
+        <v>-1.1874</v>
       </c>
       <c r="G38" t="n">
-        <v>-1</v>
+        <v>-0.8499</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.4414</v>
+        <v>-1.1874</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.4414</v>
+        <v>-1.1874</v>
       </c>
       <c r="J38" t="n">
-        <v>-1</v>
+        <v>-0.8499</v>
       </c>
       <c r="K38" t="n">
         <v>95</v>
@@ -2185,7 +2185,7 @@
         <v>38</v>
       </c>
       <c r="M38" t="n">
-        <v>-2.4414</v>
+        <v>-2.0373</v>
       </c>
       <c r="N38" t="n">
         <v>133</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.4801</v>
+        <v>-2.2997</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.1268</v>
+        <v>-1.0448</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.432</v>
+        <v>-1.6762</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.4801</v>
+        <v>-2.2997</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5202</v>
+        <v>-0.9312</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.9599</v>
+        <v>-1.3685</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5202</v>
+        <v>-0.9312</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2322</v>
+        <v>-0.9312</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.9599</v>
+        <v>-1.3685</v>
       </c>
       <c r="K39" t="n">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="L39" t="n">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.1921</v>
+        <v>-2.2997</v>
       </c>
       <c r="N39" t="n">
-        <v>132</v>
+        <v>211</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.9542</v>
+        <v>-2.3795</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.3422</v>
+        <v>-1.0811</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6209</v>
+        <v>-1.7122</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.9542</v>
+        <v>-2.3795</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3329</v>
+        <v>-1.8423</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.6213</v>
+        <v>-0.5372</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3329</v>
+        <v>-1.8423</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3329</v>
+        <v>-0.9579</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.6213</v>
+        <v>-0.5372</v>
       </c>
       <c r="K40" t="n">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="L40" t="n">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.9542</v>
+        <v>-1.4951</v>
       </c>
       <c r="N40" t="n">
-        <v>211</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.0362</v>
+        <v>-3.5594</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.3795</v>
+        <v>-1.6172</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6535</v>
+        <v>-2.2449</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.0362</v>
+        <v>-3.5594</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.0826</v>
+        <v>-3.9225</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0464</v>
+        <v>0.3631</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.0826</v>
+        <v>-3.9225</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.4985</v>
+        <v>-2.0395</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0464</v>
+        <v>0.3631</v>
       </c>
       <c r="K41" t="n">
         <v>103</v>
@@ -2323,7 +2323,7 @@
         <v>122</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.4521</v>
+        <v>-1.6764</v>
       </c>
       <c r="N41" t="n">
         <v>225</v>
@@ -2429,10 +2429,10 @@
         <v>1.43</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0668</v>
+        <v>1.045</v>
       </c>
       <c r="J2" t="n">
-        <v>21.336</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.43</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0668</v>
+        <v>1.045</v>
       </c>
       <c r="J3" t="n">
-        <v>21.336</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.39</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9815</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>19.63</v>
+        <v>19.628</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0737</v>
+        <v>0.1464</v>
       </c>
       <c r="J5" t="n">
-        <v>1.474</v>
+        <v>2.928</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6879</v>
+        <v>-0.6288</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.758</v>
+        <v>-12.576</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.24</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4667</v>
+        <v>0.5411</v>
       </c>
       <c r="J7" t="n">
-        <v>9.334</v>
+        <v>10.822</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.03</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1258</v>
+        <v>0.1093</v>
       </c>
       <c r="J8" t="n">
-        <v>2.516</v>
+        <v>2.186</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2342</v>
+        <v>-0.1476</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.684</v>
+        <v>-2.952</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.84</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3014</v>
+        <v>-0.1894</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.028</v>
+        <v>-3.788</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.63</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5961</v>
+        <v>-0.3931</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.922</v>
+        <v>-7.862</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>2.02</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0114</v>
+        <v>1.7115</v>
       </c>
       <c r="J12" t="n">
-        <v>36.2052</v>
+        <v>30.807</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.31</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6748</v>
+        <v>0.7792</v>
       </c>
       <c r="J13" t="n">
-        <v>12.1464</v>
+        <v>14.0256</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.28</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6056</v>
+        <v>0.7113</v>
       </c>
       <c r="J14" t="n">
-        <v>10.9008</v>
+        <v>12.8034</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.23</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4892</v>
+        <v>0.594</v>
       </c>
       <c r="J15" t="n">
-        <v>8.8056</v>
+        <v>10.692</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.14</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2697</v>
+        <v>0.3673</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8546</v>
+        <v>6.6114</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.28</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5454</v>
+        <v>0.6484</v>
       </c>
       <c r="J17" t="n">
-        <v>9.8172</v>
+        <v>11.6712</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.27</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5321</v>
+        <v>0.6298</v>
       </c>
       <c r="J18" t="n">
-        <v>9.5778</v>
+        <v>11.3364</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.68</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5158</v>
+        <v>-0.3376</v>
       </c>
       <c r="J19" t="n">
-        <v>-9.2844</v>
+        <v>-6.0768</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.59</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6339</v>
+        <v>-0.422</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.4102</v>
+        <v>-7.596</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.47</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7804</v>
+        <v>-0.5319</v>
       </c>
       <c r="J21" t="n">
-        <v>-14.0472</v>
+        <v>-9.574199999999999</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>2.28</v>
       </c>
       <c r="I22" t="n">
-        <v>2.2791</v>
+        <v>1.8681</v>
       </c>
       <c r="J22" t="n">
-        <v>45.582</v>
+        <v>37.362</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.35</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8856000000000001</v>
+        <v>0.8962</v>
       </c>
       <c r="J23" t="n">
-        <v>17.712</v>
+        <v>17.924</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.08</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1608</v>
+        <v>0.2357</v>
       </c>
       <c r="J24" t="n">
-        <v>3.216</v>
+        <v>4.714</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.91</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4593</v>
+        <v>-0.3836</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.186</v>
+        <v>-7.672</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.57</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.2297</v>
+        <v>-1.2377</v>
       </c>
       <c r="J26" t="n">
-        <v>-24.594</v>
+        <v>-24.754</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.66</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9733000000000001</v>
+        <v>1.1585</v>
       </c>
       <c r="J27" t="n">
-        <v>19.466</v>
+        <v>23.17</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.96</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0582</v>
+        <v>-0.0556</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.164</v>
+        <v>-1.112</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.78</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3896</v>
+        <v>-0.2482</v>
       </c>
       <c r="J29" t="n">
-        <v>-7.792</v>
+        <v>-4.964</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.73</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4611</v>
+        <v>-0.297</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.222</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.43</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8337</v>
+        <v>-0.5735</v>
       </c>
       <c r="J31" t="n">
-        <v>-16.674</v>
+        <v>-11.47</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.19</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4331</v>
+        <v>0.428</v>
       </c>
       <c r="J32" t="n">
-        <v>7.7958</v>
+        <v>7.704</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.86</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2061</v>
+        <v>-0.1593</v>
       </c>
       <c r="J33" t="n">
-        <v>-3.7098</v>
+        <v>-2.8674</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.8</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3253</v>
+        <v>-0.2181</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.8554</v>
+        <v>-3.9258</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.67</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5212</v>
+        <v>-0.343</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.381600000000001</v>
+        <v>-6.174</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.62</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5884</v>
+        <v>-0.39</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.5912</v>
+        <v>-7.02</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.74</v>
       </c>
       <c r="I37" t="n">
-        <v>1.5968</v>
+        <v>1.121</v>
       </c>
       <c r="J37" t="n">
-        <v>28.7424</v>
+        <v>20.178</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.7</v>
       </c>
       <c r="I38" t="n">
-        <v>1.5241</v>
+        <v>1.0739</v>
       </c>
       <c r="J38" t="n">
-        <v>27.4338</v>
+        <v>19.3302</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.36</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8071</v>
+        <v>0.6626</v>
       </c>
       <c r="J39" t="n">
-        <v>14.5278</v>
+        <v>11.9268</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.19</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4014</v>
+        <v>0.4323</v>
       </c>
       <c r="J40" t="n">
-        <v>7.2252</v>
+        <v>7.7814</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.88</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5717</v>
+        <v>-0.4996</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.2906</v>
+        <v>-8.992800000000001</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.32</v>
       </c>
       <c r="I42" t="n">
-        <v>1.4473</v>
+        <v>0.9495</v>
       </c>
       <c r="J42" t="n">
-        <v>23.1568</v>
+        <v>15.192</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>2.01</v>
       </c>
       <c r="I43" t="n">
-        <v>1.165</v>
+        <v>0.7778</v>
       </c>
       <c r="J43" t="n">
-        <v>18.64</v>
+        <v>12.4448</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.19</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2155</v>
+        <v>0.2431</v>
       </c>
       <c r="J44" t="n">
-        <v>3.448</v>
+        <v>3.8896</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1884</v>
+        <v>-0.0921</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.0144</v>
+        <v>-1.4736</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.79</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4608</v>
+        <v>-0.2896</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.3728</v>
+        <v>-4.6336</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.98</v>
       </c>
       <c r="I47" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0122</v>
       </c>
       <c r="J47" t="n">
-        <v>1.0032</v>
+        <v>0.1952</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.243</v>
+        <v>-0.1973</v>
       </c>
       <c r="J48" t="n">
-        <v>-3.888</v>
+        <v>-3.1568</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.75</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3455</v>
+        <v>-0.2563</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.528</v>
+        <v>-4.1008</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.6</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5898</v>
+        <v>-0.3954</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.4368</v>
+        <v>-6.3264</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.55</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.657</v>
+        <v>-0.4421</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.512</v>
+        <v>-7.0736</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.24</v>
       </c>
       <c r="I52" t="n">
-        <v>0.501</v>
+        <v>0.4832</v>
       </c>
       <c r="J52" t="n">
-        <v>9.018000000000001</v>
+        <v>8.6976</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.12</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3245</v>
+        <v>0.3409</v>
       </c>
       <c r="J53" t="n">
-        <v>5.841</v>
+        <v>6.1362</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.64</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.5634</v>
+        <v>-0.3721</v>
       </c>
       <c r="J54" t="n">
-        <v>-10.1412</v>
+        <v>-6.6978</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.6</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.6159</v>
+        <v>-0.4095</v>
       </c>
       <c r="J55" t="n">
-        <v>-11.0862</v>
+        <v>-7.371</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.57</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6542</v>
+        <v>-0.4373</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.7756</v>
+        <v>-7.8714</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.74</v>
       </c>
       <c r="I57" t="n">
-        <v>1.5857</v>
+        <v>1.1155</v>
       </c>
       <c r="J57" t="n">
-        <v>28.5426</v>
+        <v>20.079</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.55</v>
       </c>
       <c r="I58" t="n">
-        <v>1.2263</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>22.0734</v>
+        <v>16.0308</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.5</v>
       </c>
       <c r="I59" t="n">
-        <v>1.1242</v>
+        <v>0.8303</v>
       </c>
       <c r="J59" t="n">
-        <v>20.2356</v>
+        <v>14.9454</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.27</v>
       </c>
       <c r="I60" t="n">
-        <v>0.5809</v>
+        <v>0.5422</v>
       </c>
       <c r="J60" t="n">
-        <v>10.4562</v>
+        <v>9.759600000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.412</v>
+        <v>-0.3282</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.416</v>
+        <v>-5.9076</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>2.26</v>
       </c>
       <c r="I62" t="n">
-        <v>2.1469</v>
+        <v>1.7427</v>
       </c>
       <c r="J62" t="n">
-        <v>49.3787</v>
+        <v>40.0821</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.08</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1386</v>
+        <v>0.2215</v>
       </c>
       <c r="J63" t="n">
-        <v>3.1878</v>
+        <v>5.0945</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.08</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1386</v>
+        <v>0.2215</v>
       </c>
       <c r="J64" t="n">
-        <v>3.1878</v>
+        <v>5.0945</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.05</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0477</v>
+        <v>0.1287</v>
       </c>
       <c r="J65" t="n">
-        <v>1.0971</v>
+        <v>2.9601</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.02</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.0561</v>
+        <v>0.0236</v>
       </c>
       <c r="J66" t="n">
-        <v>-1.2903</v>
+        <v>0.5427999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.7</v>
       </c>
       <c r="I67" t="n">
-        <v>0.9899</v>
+        <v>0.8942</v>
       </c>
       <c r="J67" t="n">
-        <v>22.7677</v>
+        <v>20.5666</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.35</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="J68" t="n">
-        <v>13.5746</v>
+        <v>12.788</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.65</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5812</v>
+        <v>-0.3812</v>
       </c>
       <c r="J69" t="n">
-        <v>-13.3676</v>
+        <v>-8.7676</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.62</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6186</v>
+        <v>-0.409</v>
       </c>
       <c r="J70" t="n">
-        <v>-14.2278</v>
+        <v>-9.407</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.59</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6553</v>
+        <v>-0.4365</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.0719</v>
+        <v>-10.0395</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.2</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4483</v>
+        <v>0.3691</v>
       </c>
       <c r="J72" t="n">
-        <v>8.965999999999999</v>
+        <v>7.382</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.04</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1865</v>
+        <v>0.1298</v>
       </c>
       <c r="J73" t="n">
-        <v>3.73</v>
+        <v>2.596</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.78</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3578</v>
+        <v>-0.2373</v>
       </c>
       <c r="J74" t="n">
-        <v>-7.156</v>
+        <v>-4.746</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.7</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4786</v>
+        <v>-0.3142</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.571999999999999</v>
+        <v>-6.284</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.41</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.846</v>
+        <v>-0.5827</v>
       </c>
       <c r="J76" t="n">
-        <v>-16.92</v>
+        <v>-11.654</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.57</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7537</v>
+        <v>0.5372</v>
       </c>
       <c r="J77" t="n">
-        <v>15.074</v>
+        <v>10.744</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.5</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.4937</v>
       </c>
       <c r="J78" t="n">
-        <v>13.478</v>
+        <v>9.874000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.46</v>
       </c>
       <c r="I79" t="n">
-        <v>0.6267</v>
+        <v>0.4685</v>
       </c>
       <c r="J79" t="n">
-        <v>12.534</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.26</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3479</v>
+        <v>0.3381</v>
       </c>
       <c r="J80" t="n">
-        <v>6.958</v>
+        <v>6.762</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.72</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5351</v>
+        <v>-0.3452</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.702</v>
+        <v>-6.904</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.37</v>
       </c>
       <c r="I82" t="n">
-        <v>0.976</v>
+        <v>0.7086</v>
       </c>
       <c r="J82" t="n">
-        <v>20.496</v>
+        <v>14.8806</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.23</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6504</v>
+        <v>0.5154</v>
       </c>
       <c r="J83" t="n">
-        <v>13.6584</v>
+        <v>10.8234</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2629</v>
+        <v>0.3129</v>
       </c>
       <c r="J84" t="n">
-        <v>5.5209</v>
+        <v>6.5709</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.07</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1704</v>
+        <v>0.2265</v>
       </c>
       <c r="J85" t="n">
-        <v>3.5784</v>
+        <v>4.7565</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.99</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1632</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>-3.4272</v>
+        <v>-1.9173</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.11</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2879</v>
+        <v>0.3036</v>
       </c>
       <c r="J87" t="n">
-        <v>6.0459</v>
+        <v>6.3756</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.05</v>
       </c>
       <c r="I88" t="n">
-        <v>0.182</v>
+        <v>0.1707</v>
       </c>
       <c r="J88" t="n">
-        <v>3.822</v>
+        <v>3.5847</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.0775</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.8249</v>
+        <v>-1.6275</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.77</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3963</v>
+        <v>-0.2547</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.3223</v>
+        <v>-5.3487</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6766</v>
+        <v>-0.4532</v>
       </c>
       <c r="J91" t="n">
-        <v>-14.2086</v>
+        <v>-9.517200000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.36</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.5737</v>
       </c>
       <c r="J92" t="n">
-        <v>14.0852</v>
+        <v>13.1951</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.03</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1133</v>
+        <v>0.1015</v>
       </c>
       <c r="J93" t="n">
-        <v>2.6059</v>
+        <v>2.3345</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.93</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1545</v>
+        <v>-0.0954</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.5535</v>
+        <v>-2.1942</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.92</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1743</v>
+        <v>-0.1069</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.0089</v>
+        <v>-2.4587</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.53</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.7232</v>
+        <v>-0.488</v>
       </c>
       <c r="J96" t="n">
-        <v>-16.6336</v>
+        <v>-11.224</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.44</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1274</v>
+        <v>0.8033</v>
       </c>
       <c r="J97" t="n">
-        <v>25.9302</v>
+        <v>18.4759</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.32</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8683999999999999</v>
+        <v>0.642</v>
       </c>
       <c r="J98" t="n">
-        <v>19.9732</v>
+        <v>14.766</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.24</v>
       </c>
       <c r="I99" t="n">
-        <v>0.6792</v>
+        <v>0.5306</v>
       </c>
       <c r="J99" t="n">
-        <v>15.6216</v>
+        <v>12.2038</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.93</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.372</v>
+        <v>-0.3</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.555999999999999</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.8</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.7159</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="J101" t="n">
-        <v>-16.4657</v>
+        <v>-15.2214</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.13</v>
       </c>
       <c r="I102" t="n">
-        <v>0.282</v>
+        <v>0.3092</v>
       </c>
       <c r="J102" t="n">
-        <v>10.152</v>
+        <v>11.1312</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.04</v>
       </c>
       <c r="I103" t="n">
-        <v>0.12</v>
+        <v>0.1184</v>
       </c>
       <c r="J103" t="n">
-        <v>4.32</v>
+        <v>4.2624</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.01</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0477</v>
+        <v>0.0395</v>
       </c>
       <c r="J104" t="n">
-        <v>1.7172</v>
+        <v>1.422</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.9</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.224</v>
+        <v>-0.1329</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.064</v>
+        <v>-4.7844</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.86</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.29</v>
+        <v>-0.1761</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.44</v>
+        <v>-6.3396</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.34</v>
       </c>
       <c r="I107" t="n">
-        <v>0.923</v>
+        <v>0.6734</v>
       </c>
       <c r="J107" t="n">
-        <v>33.228</v>
+        <v>24.2424</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.27</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7625999999999999</v>
+        <v>0.5763</v>
       </c>
       <c r="J108" t="n">
-        <v>27.4536</v>
+        <v>20.7468</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.16</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4792</v>
+        <v>0.4169</v>
       </c>
       <c r="J109" t="n">
-        <v>17.2512</v>
+        <v>15.0084</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.02</v>
       </c>
       <c r="I110" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="J110" t="n">
-        <v>0.3168</v>
+        <v>2.3616</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.85</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5868</v>
+        <v>-0.5248</v>
       </c>
       <c r="J111" t="n">
-        <v>-21.1248</v>
+        <v>-18.8928</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.14</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3624</v>
+        <v>0.3717</v>
       </c>
       <c r="J112" t="n">
-        <v>6.8856</v>
+        <v>7.0623</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.85</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2184</v>
+        <v>-0.1684</v>
       </c>
       <c r="J113" t="n">
-        <v>-4.1496</v>
+        <v>-3.1996</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.8</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3193</v>
+        <v>-0.2171</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.0667</v>
+        <v>-4.1249</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.68</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5043</v>
+        <v>-0.3321</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.5817</v>
+        <v>-6.3099</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.62</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5859</v>
+        <v>-0.3886</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.1321</v>
+        <v>-7.3834</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.58</v>
       </c>
       <c r="I117" t="n">
-        <v>1.3541</v>
+        <v>0.956</v>
       </c>
       <c r="J117" t="n">
-        <v>25.7279</v>
+        <v>18.164</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.57</v>
       </c>
       <c r="I118" t="n">
-        <v>1.3348</v>
+        <v>0.9435</v>
       </c>
       <c r="J118" t="n">
-        <v>25.3612</v>
+        <v>17.9265</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.51</v>
       </c>
       <c r="I119" t="n">
-        <v>1.2168</v>
+        <v>0.8683999999999999</v>
       </c>
       <c r="J119" t="n">
-        <v>23.1192</v>
+        <v>16.4996</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.98</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2408</v>
+        <v>-0.1576</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.5752</v>
+        <v>-2.9944</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.62</v>
       </c>
       <c r="I121" t="n">
-        <v>-1.1318</v>
+        <v>-1.1249</v>
       </c>
       <c r="J121" t="n">
-        <v>-21.5042</v>
+        <v>-21.3731</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.27</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5533</v>
+        <v>0.5273</v>
       </c>
       <c r="J122" t="n">
-        <v>10.5127</v>
+        <v>10.0187</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.02</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1517</v>
+        <v>0.1248</v>
       </c>
       <c r="J123" t="n">
-        <v>2.8823</v>
+        <v>2.3712</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.63</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.5694</v>
+        <v>-0.3775</v>
       </c>
       <c r="J124" t="n">
-        <v>-10.8186</v>
+        <v>-7.1725</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.57</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.6481</v>
+        <v>-0.4335</v>
       </c>
       <c r="J125" t="n">
-        <v>-12.3139</v>
+        <v>-8.236499999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.54</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6861</v>
+        <v>-0.4613</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.0359</v>
+        <v>-8.764699999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.61</v>
       </c>
       <c r="I127" t="n">
-        <v>1.4039</v>
+        <v>0.9892</v>
       </c>
       <c r="J127" t="n">
-        <v>26.6741</v>
+        <v>18.7948</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.52</v>
       </c>
       <c r="I128" t="n">
-        <v>1.2291</v>
+        <v>0.8776</v>
       </c>
       <c r="J128" t="n">
-        <v>23.3529</v>
+        <v>16.6744</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.33</v>
       </c>
       <c r="I129" t="n">
-        <v>0.8219</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="J129" t="n">
-        <v>15.6161</v>
+        <v>12.0574</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.03</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0097</v>
+        <v>0.0679</v>
       </c>
       <c r="J130" t="n">
-        <v>-0.1843</v>
+        <v>1.2901</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.85</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6248</v>
+        <v>-0.5591</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.8712</v>
+        <v>-10.6229</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.34</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9184</v>
       </c>
       <c r="J132" t="n">
-        <v>27.115</v>
+        <v>26.6336</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.18</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5503</v>
+        <v>0.5309</v>
       </c>
       <c r="J133" t="n">
-        <v>15.9587</v>
+        <v>15.3961</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.01</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0231</v>
+        <v>0.0303</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.6699000000000001</v>
+        <v>0.8787</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.01</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0231</v>
+        <v>0.0303</v>
       </c>
       <c r="J135" t="n">
-        <v>-0.6699000000000001</v>
+        <v>0.8787</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.99</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.1424</v>
+        <v>-0.0793</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.1296</v>
+        <v>-2.2997</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.5</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7692</v>
+        <v>0.9575</v>
       </c>
       <c r="J137" t="n">
-        <v>22.3068</v>
+        <v>27.7675</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.05</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1424</v>
+        <v>0.1427</v>
       </c>
       <c r="J138" t="n">
-        <v>4.1296</v>
+        <v>4.1383</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.96</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1069</v>
+        <v>-0.0618</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.1001</v>
+        <v>-1.7922</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3652</v>
+        <v>-0.2271</v>
       </c>
       <c r="J140" t="n">
-        <v>-10.5908</v>
+        <v>-6.5859</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.6</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6435</v>
+        <v>-0.4276</v>
       </c>
       <c r="J141" t="n">
-        <v>-18.6615</v>
+        <v>-12.4004</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.36</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9489</v>
+        <v>0.9412</v>
       </c>
       <c r="J142" t="n">
-        <v>21.8247</v>
+        <v>21.6476</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.31</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8367</v>
+        <v>0.8282</v>
       </c>
       <c r="J143" t="n">
-        <v>19.2441</v>
+        <v>19.0486</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.26</v>
       </c>
       <c r="I144" t="n">
-        <v>0.7187</v>
+        <v>0.7108</v>
       </c>
       <c r="J144" t="n">
-        <v>16.5301</v>
+        <v>16.3484</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.08</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1961</v>
+        <v>0.2539</v>
       </c>
       <c r="J145" t="n">
-        <v>4.5103</v>
+        <v>5.8397</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.8</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.6659</v>
       </c>
       <c r="J146" t="n">
-        <v>-16.5669</v>
+        <v>-15.3157</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.28</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4866</v>
+        <v>0.5743</v>
       </c>
       <c r="J147" t="n">
-        <v>11.1918</v>
+        <v>13.2089</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.12</v>
       </c>
       <c r="I148" t="n">
-        <v>0.253</v>
+        <v>0.281</v>
       </c>
       <c r="J148" t="n">
-        <v>5.819</v>
+        <v>6.463</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.1</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2192</v>
+        <v>0.2412</v>
       </c>
       <c r="J149" t="n">
-        <v>5.0416</v>
+        <v>5.5476</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.09</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2017</v>
+        <v>0.2208</v>
       </c>
       <c r="J150" t="n">
-        <v>4.6391</v>
+        <v>5.0784</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.52</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7432</v>
+        <v>-0.5036</v>
       </c>
       <c r="J151" t="n">
-        <v>-17.0936</v>
+        <v>-11.5828</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.47</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6881</v>
+        <v>0.6061</v>
       </c>
       <c r="J152" t="n">
-        <v>15.8263</v>
+        <v>13.9403</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.12</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1968</v>
+        <v>0.1871</v>
       </c>
       <c r="J153" t="n">
-        <v>4.5264</v>
+        <v>4.3033</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.08</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1236</v>
+        <v>0.1314</v>
       </c>
       <c r="J154" t="n">
-        <v>2.8428</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.01</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0202</v>
+        <v>0.0121</v>
       </c>
       <c r="J155" t="n">
-        <v>-0.4646</v>
+        <v>0.2783</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.97</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1346</v>
+        <v>-0.0631</v>
       </c>
       <c r="J156" t="n">
-        <v>-3.0958</v>
+        <v>-1.4513</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.66</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9356</v>
+        <v>0.9185</v>
       </c>
       <c r="J157" t="n">
-        <v>21.5188</v>
+        <v>21.1255</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.97</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0994</v>
+        <v>-0.0515</v>
       </c>
       <c r="J158" t="n">
-        <v>-2.2862</v>
+        <v>-1.1845</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1611</v>
+        <v>-0.0898</v>
       </c>
       <c r="J159" t="n">
-        <v>-3.7053</v>
+        <v>-2.0654</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.76</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4432</v>
+        <v>-0.2804</v>
       </c>
       <c r="J160" t="n">
-        <v>-10.1936</v>
+        <v>-6.4492</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.75</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4568</v>
+        <v>-0.2901</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.5064</v>
+        <v>-6.6723</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.08</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3016</v>
+        <v>0.3172</v>
       </c>
       <c r="J162" t="n">
-        <v>4.8256</v>
+        <v>5.0752</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.77</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.3061</v>
+        <v>-0.2365</v>
       </c>
       <c r="J163" t="n">
-        <v>-4.8976</v>
+        <v>-3.784</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.7</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.4391</v>
+        <v>-0.301</v>
       </c>
       <c r="J164" t="n">
-        <v>-7.0256</v>
+        <v>-4.816</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.57</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.6287</v>
+        <v>-0.4225</v>
       </c>
       <c r="J165" t="n">
-        <v>-10.0592</v>
+        <v>-6.76</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.54</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6685</v>
+        <v>-0.4505</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.696</v>
+        <v>-7.208</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.69</v>
       </c>
       <c r="I167" t="n">
-        <v>1.5154</v>
+        <v>1.3405</v>
       </c>
       <c r="J167" t="n">
-        <v>24.2464</v>
+        <v>21.448</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.37</v>
       </c>
       <c r="I168" t="n">
-        <v>0.8609</v>
+        <v>0.9146</v>
       </c>
       <c r="J168" t="n">
-        <v>13.7744</v>
+        <v>14.6336</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.36</v>
       </c>
       <c r="I169" t="n">
-        <v>0.8347</v>
+        <v>0.894</v>
       </c>
       <c r="J169" t="n">
-        <v>13.3552</v>
+        <v>14.304</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.3</v>
       </c>
       <c r="I170" t="n">
-        <v>0.6741</v>
+        <v>0.7651</v>
       </c>
       <c r="J170" t="n">
-        <v>10.7856</v>
+        <v>12.2416</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.04</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0008</v>
+        <v>0.0833</v>
       </c>
       <c r="J171" t="n">
-        <v>-0.0128</v>
+        <v>1.3328</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.46</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6916</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="J172" t="n">
-        <v>16.5984</v>
+        <v>20.4792</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.23</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3989</v>
+        <v>0.4695</v>
       </c>
       <c r="J173" t="n">
-        <v>9.573600000000001</v>
+        <v>11.268</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.1</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1934</v>
+        <v>0.2304</v>
       </c>
       <c r="J174" t="n">
-        <v>4.6416</v>
+        <v>5.5296</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.82</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3718</v>
+        <v>-0.2278</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.9232</v>
+        <v>-5.4672</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.79</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4141</v>
+        <v>-0.2579</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.9384</v>
+        <v>-6.1896</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.74</v>
       </c>
       <c r="I177" t="n">
-        <v>1.756</v>
+        <v>1.5017</v>
       </c>
       <c r="J177" t="n">
-        <v>42.144</v>
+        <v>36.0408</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.32</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9226</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="J178" t="n">
-        <v>22.1424</v>
+        <v>21.5448</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.98</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1541</v>
+        <v>-0.1051</v>
       </c>
       <c r="J179" t="n">
-        <v>-3.6984</v>
+        <v>-2.5224</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.7</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.9195</v>
+        <v>-0.8873</v>
       </c>
       <c r="J180" t="n">
-        <v>-22.068</v>
+        <v>-21.2952</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.5</v>
       </c>
       <c r="I181" t="n">
-        <v>-1.3378</v>
+        <v>-1.3606</v>
       </c>
       <c r="J181" t="n">
-        <v>-32.1072</v>
+        <v>-32.6544</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.62</v>
       </c>
       <c r="I182" t="n">
-        <v>1.4561</v>
+        <v>1.2938</v>
       </c>
       <c r="J182" t="n">
-        <v>29.122</v>
+        <v>25.876</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.41</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0379</v>
+        <v>1.0219</v>
       </c>
       <c r="J183" t="n">
-        <v>20.758</v>
+        <v>20.438</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.09</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2079</v>
+        <v>0.2745</v>
       </c>
       <c r="J184" t="n">
-        <v>4.158</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.04</v>
       </c>
       <c r="I185" t="n">
-        <v>0.0509</v>
+        <v>0.1197</v>
       </c>
       <c r="J185" t="n">
-        <v>1.018</v>
+        <v>2.394</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.83</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6571</v>
+        <v>-0.5962</v>
       </c>
       <c r="J186" t="n">
-        <v>-13.142</v>
+        <v>-11.924</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.13</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3071</v>
+        <v>0.3318</v>
       </c>
       <c r="J187" t="n">
-        <v>6.142</v>
+        <v>6.636</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.95</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0837</v>
+        <v>-0.0692</v>
       </c>
       <c r="J188" t="n">
-        <v>-1.674</v>
+        <v>-1.384</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.95</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0837</v>
+        <v>-0.0692</v>
       </c>
       <c r="J189" t="n">
-        <v>-1.674</v>
+        <v>-1.384</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.87</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2499</v>
+        <v>-0.1578</v>
       </c>
       <c r="J190" t="n">
-        <v>-4.998</v>
+        <v>-3.156</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.7</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.504</v>
+        <v>-0.3267</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.08</v>
+        <v>-6.534</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.45</v>
       </c>
       <c r="I192" t="n">
-        <v>1.1429</v>
+        <v>1.0877</v>
       </c>
       <c r="J192" t="n">
-        <v>25.1438</v>
+        <v>23.9294</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.34</v>
       </c>
       <c r="I193" t="n">
-        <v>0.9079</v>
+        <v>0.8995</v>
       </c>
       <c r="J193" t="n">
-        <v>19.9738</v>
+        <v>19.789</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.23</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6479</v>
+        <v>0.6408</v>
       </c>
       <c r="J194" t="n">
-        <v>14.2538</v>
+        <v>14.0976</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3449</v>
+        <v>-0.2714</v>
       </c>
       <c r="J195" t="n">
-        <v>-7.5878</v>
+        <v>-5.9708</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.82</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6703</v>
+        <v>-0.6122</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.7466</v>
+        <v>-13.4684</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.26</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4679</v>
+        <v>0.5476</v>
       </c>
       <c r="J197" t="n">
-        <v>10.2938</v>
+        <v>12.0472</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.22</v>
       </c>
       <c r="I198" t="n">
-        <v>0.4128</v>
+        <v>0.4759</v>
       </c>
       <c r="J198" t="n">
-        <v>9.0816</v>
+        <v>10.4698</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1</v>
       </c>
       <c r="I199" t="n">
-        <v>0.0029</v>
+        <v>0.0001</v>
       </c>
       <c r="J199" t="n">
-        <v>0.0638</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.83</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.339</v>
+        <v>-0.2084</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.458</v>
+        <v>-4.5848</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.68</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5458</v>
+        <v>-0.3549</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.0076</v>
+        <v>-7.8078</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>2.21</v>
       </c>
       <c r="I202" t="n">
-        <v>1.3556</v>
+        <v>1.1667</v>
       </c>
       <c r="J202" t="n">
-        <v>25.7564</v>
+        <v>22.1673</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.69</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8515</v>
+        <v>0.7804</v>
       </c>
       <c r="J203" t="n">
-        <v>16.1785</v>
+        <v>14.8276</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.36</v>
       </c>
       <c r="I204" t="n">
-        <v>0.444</v>
+        <v>0.4439</v>
       </c>
       <c r="J204" t="n">
-        <v>8.436</v>
+        <v>8.434100000000001</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.11</v>
       </c>
       <c r="I205" t="n">
-        <v>0.1046</v>
+        <v>0.14</v>
       </c>
       <c r="J205" t="n">
-        <v>1.9874</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.78</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4714</v>
+        <v>-0.2975</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.9566</v>
+        <v>-5.6525</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.26</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5654</v>
+        <v>0.5246</v>
       </c>
       <c r="J207" t="n">
-        <v>10.7426</v>
+        <v>9.9674</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.65</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.5229</v>
+        <v>-0.35</v>
       </c>
       <c r="J208" t="n">
-        <v>-9.9351</v>
+        <v>-6.65</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.64</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.5372</v>
+        <v>-0.3594</v>
       </c>
       <c r="J209" t="n">
-        <v>-10.2068</v>
+        <v>-6.8286</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.6</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.593</v>
+        <v>-0.3969</v>
       </c>
       <c r="J210" t="n">
-        <v>-11.267</v>
+        <v>-7.5411</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.59</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6065</v>
+        <v>-0.4063</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.5235</v>
+        <v>-7.7197</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.15</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3457</v>
+        <v>0.3796</v>
       </c>
       <c r="J212" t="n">
-        <v>7.2597</v>
+        <v>7.9716</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.13</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3146</v>
+        <v>0.3394</v>
       </c>
       <c r="J213" t="n">
-        <v>6.6066</v>
+        <v>7.1274</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.83</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3086</v>
+        <v>-0.1967</v>
       </c>
       <c r="J214" t="n">
-        <v>-6.4806</v>
+        <v>-4.1307</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.77</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4007</v>
+        <v>-0.2565</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.4147</v>
+        <v>-5.3865</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.62</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6042</v>
+        <v>-0.3994</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.6882</v>
+        <v>-8.3874</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.54</v>
       </c>
       <c r="I217" t="n">
-        <v>1.2811</v>
+        <v>1.1821</v>
       </c>
       <c r="J217" t="n">
-        <v>26.9031</v>
+        <v>24.8241</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.46</v>
       </c>
       <c r="I218" t="n">
-        <v>1.1202</v>
+        <v>1.0809</v>
       </c>
       <c r="J218" t="n">
-        <v>23.5242</v>
+        <v>22.6989</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.22</v>
       </c>
       <c r="I219" t="n">
-        <v>0.5419</v>
+        <v>0.6012</v>
       </c>
       <c r="J219" t="n">
-        <v>11.3799</v>
+        <v>12.6252</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.2</v>
       </c>
       <c r="I220" t="n">
-        <v>0.4877</v>
+        <v>0.5535</v>
       </c>
       <c r="J220" t="n">
-        <v>10.2417</v>
+        <v>11.6235</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.79</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.763</v>
+        <v>-0.7105</v>
       </c>
       <c r="J221" t="n">
-        <v>-16.023</v>
+        <v>-14.9205</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.12</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3134</v>
+        <v>0.3347</v>
       </c>
       <c r="J222" t="n">
-        <v>5.9546</v>
+        <v>6.3593</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.91</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.1328</v>
+        <v>-0.1095</v>
       </c>
       <c r="J223" t="n">
-        <v>-2.5232</v>
+        <v>-2.0805</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.9</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1516</v>
+        <v>-0.1207</v>
       </c>
       <c r="J224" t="n">
-        <v>-2.8804</v>
+        <v>-2.2933</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.72</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4613</v>
+        <v>-0.3</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.764699999999999</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.66</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5438</v>
+        <v>-0.3571</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.3322</v>
+        <v>-6.7849</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.73</v>
       </c>
       <c r="I227" t="n">
-        <v>1.605</v>
+        <v>1.397</v>
       </c>
       <c r="J227" t="n">
-        <v>30.495</v>
+        <v>26.543</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.61</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3827</v>
+        <v>1.2525</v>
       </c>
       <c r="J228" t="n">
-        <v>26.2713</v>
+        <v>23.7975</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.22</v>
       </c>
       <c r="I229" t="n">
-        <v>0.4993</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="J229" t="n">
-        <v>9.486700000000001</v>
+        <v>11.1568</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.05</v>
       </c>
       <c r="I230" t="n">
-        <v>0.0427</v>
+        <v>0.125</v>
       </c>
       <c r="J230" t="n">
-        <v>0.8113</v>
+        <v>2.375</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.96</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3293</v>
+        <v>-0.2443</v>
       </c>
       <c r="J231" t="n">
-        <v>-6.2567</v>
+        <v>-4.6417</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.41</v>
       </c>
       <c r="I232" t="n">
-        <v>0.6681</v>
+        <v>0.8186</v>
       </c>
       <c r="J232" t="n">
-        <v>14.6982</v>
+        <v>18.0092</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.96</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.0987</v>
+        <v>-0.0606</v>
       </c>
       <c r="J233" t="n">
-        <v>-2.1714</v>
+        <v>-1.3332</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.92</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1814</v>
+        <v>-0.1085</v>
       </c>
       <c r="J234" t="n">
-        <v>-3.9908</v>
+        <v>-2.387</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1998</v>
+        <v>-0.1198</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.3956</v>
+        <v>-2.6356</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.65</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.3798</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.7402</v>
+        <v>-8.355600000000001</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.43</v>
       </c>
       <c r="I237" t="n">
-        <v>1.1255</v>
+        <v>1.0735</v>
       </c>
       <c r="J237" t="n">
-        <v>24.761</v>
+        <v>23.617</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.21</v>
       </c>
       <c r="I238" t="n">
-        <v>0.626</v>
+        <v>0.605</v>
       </c>
       <c r="J238" t="n">
-        <v>13.772</v>
+        <v>13.31</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.11</v>
       </c>
       <c r="I239" t="n">
-        <v>0.3345</v>
+        <v>0.3485</v>
       </c>
       <c r="J239" t="n">
-        <v>7.359</v>
+        <v>7.667</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.98</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1872</v>
+        <v>-0.1214</v>
       </c>
       <c r="J240" t="n">
-        <v>-4.1184</v>
+        <v>-2.6708</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.82</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6567</v>
+        <v>-0.6002</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.4474</v>
+        <v>-13.2044</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.36</v>
       </c>
       <c r="I242" t="n">
-        <v>0.6246</v>
+        <v>0.758</v>
       </c>
       <c r="J242" t="n">
-        <v>14.9904</v>
+        <v>18.192</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.07</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2061</v>
+        <v>0.2053</v>
       </c>
       <c r="J243" t="n">
-        <v>4.9464</v>
+        <v>4.9272</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.82</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.3316</v>
+        <v>-0.2093</v>
       </c>
       <c r="J244" t="n">
-        <v>-7.9584</v>
+        <v>-5.0232</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.71</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4905</v>
+        <v>-0.3172</v>
       </c>
       <c r="J245" t="n">
-        <v>-11.772</v>
+        <v>-7.6128</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.64</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5826</v>
+        <v>-0.3833</v>
       </c>
       <c r="J246" t="n">
-        <v>-13.9824</v>
+        <v>-9.199199999999999</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.34</v>
       </c>
       <c r="I247" t="n">
-        <v>0.9263</v>
+        <v>0.9121</v>
       </c>
       <c r="J247" t="n">
-        <v>22.2312</v>
+        <v>21.8904</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.22</v>
       </c>
       <c r="I248" t="n">
-        <v>0.6439</v>
+        <v>0.626</v>
       </c>
       <c r="J248" t="n">
-        <v>15.4536</v>
+        <v>15.024</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.1</v>
       </c>
       <c r="I249" t="n">
-        <v>0.2847</v>
+        <v>0.3197</v>
       </c>
       <c r="J249" t="n">
-        <v>6.8328</v>
+        <v>7.6728</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.02</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0118</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="J250" t="n">
-        <v>0.2832</v>
+        <v>1.6104</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.93</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3629</v>
+        <v>-0.2936</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.7096</v>
+        <v>-7.0464</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.08</v>
       </c>
       <c r="I252" t="n">
-        <v>0.4193</v>
+        <v>0.4077</v>
       </c>
       <c r="J252" t="n">
-        <v>5.4509</v>
+        <v>5.3001</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.47</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.6852</v>
+        <v>-0.4777</v>
       </c>
       <c r="J253" t="n">
-        <v>-8.9076</v>
+        <v>-6.2101</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.47</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.6852</v>
+        <v>-0.4777</v>
       </c>
       <c r="J254" t="n">
-        <v>-8.9076</v>
+        <v>-6.2101</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.35</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.858</v>
+        <v>-0.5936</v>
       </c>
       <c r="J255" t="n">
-        <v>-11.154</v>
+        <v>-7.7168</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.25</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.9881</v>
+        <v>-0.6931</v>
       </c>
       <c r="J256" t="n">
-        <v>-12.8453</v>
+        <v>-9.010300000000001</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>2.4</v>
       </c>
       <c r="I257" t="n">
-        <v>1.4398</v>
+        <v>1.2204</v>
       </c>
       <c r="J257" t="n">
-        <v>18.7174</v>
+        <v>15.8652</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>2.12</v>
       </c>
       <c r="I258" t="n">
-        <v>1.1898</v>
+        <v>1.0763</v>
       </c>
       <c r="J258" t="n">
-        <v>15.4674</v>
+        <v>13.9919</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.89</v>
       </c>
       <c r="I259" t="n">
-        <v>0.9637</v>
+        <v>0.9241</v>
       </c>
       <c r="J259" t="n">
-        <v>12.5281</v>
+        <v>12.0133</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.83</v>
       </c>
       <c r="I260" t="n">
-        <v>0.893</v>
+        <v>0.8721</v>
       </c>
       <c r="J260" t="n">
-        <v>11.609</v>
+        <v>11.3373</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.91</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3219</v>
+        <v>-0.188</v>
       </c>
       <c r="J261" t="n">
-        <v>-4.1847</v>
+        <v>-2.444</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>2.39</v>
       </c>
       <c r="I262" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J262" t="n">
-        <v>39.1267</v>
+        <v>34.8422</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.38</v>
       </c>
       <c r="I263" t="n">
-        <v>0.9172</v>
+        <v>0.9438</v>
       </c>
       <c r="J263" t="n">
-        <v>17.4268</v>
+        <v>17.9322</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.96</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.3261</v>
+        <v>-0.2416</v>
       </c>
       <c r="J264" t="n">
-        <v>-6.1959</v>
+        <v>-4.5904</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3892</v>
+        <v>-0.3071</v>
       </c>
       <c r="J265" t="n">
-        <v>-7.3948</v>
+        <v>-5.8349</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.84</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.6571</v>
+        <v>-0.5934</v>
       </c>
       <c r="J266" t="n">
-        <v>-12.4849</v>
+        <v>-11.2746</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.41</v>
       </c>
       <c r="I267" t="n">
-        <v>0.7003</v>
+        <v>0.8675</v>
       </c>
       <c r="J267" t="n">
-        <v>13.3057</v>
+        <v>16.4825</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.99</v>
       </c>
       <c r="I268" t="n">
-        <v>0.0257</v>
+        <v>-0.0072</v>
       </c>
       <c r="J268" t="n">
-        <v>0.4883</v>
+        <v>-0.1368</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.8</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3494</v>
+        <v>-0.2246</v>
       </c>
       <c r="J269" t="n">
-        <v>-6.6386</v>
+        <v>-4.2674</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.68</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5219</v>
+        <v>-0.3408</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.9161</v>
+        <v>-6.4752</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.53</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.7125</v>
+        <v>-0.4801</v>
       </c>
       <c r="J271" t="n">
-        <v>-13.5375</v>
+        <v>-9.1219</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2</v>
       </c>
       <c r="I272" t="n">
-        <v>2.0155</v>
+        <v>1.7257</v>
       </c>
       <c r="J272" t="n">
-        <v>38.2945</v>
+        <v>32.7883</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.2</v>
       </c>
       <c r="I273" t="n">
-        <v>0.467</v>
+        <v>0.5462</v>
       </c>
       <c r="J273" t="n">
-        <v>8.872999999999999</v>
+        <v>10.3778</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.16</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3641</v>
+        <v>0.4459</v>
       </c>
       <c r="J274" t="n">
-        <v>6.9179</v>
+        <v>8.472099999999999</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.1</v>
       </c>
       <c r="I275" t="n">
-        <v>0.2027</v>
+        <v>0.2842</v>
       </c>
       <c r="J275" t="n">
-        <v>3.8513</v>
+        <v>5.3998</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.93</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4128</v>
+        <v>-0.3328</v>
       </c>
       <c r="J276" t="n">
-        <v>-7.8432</v>
+        <v>-6.3232</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.44</v>
       </c>
       <c r="I277" t="n">
-        <v>0.7089</v>
+        <v>0.8763</v>
       </c>
       <c r="J277" t="n">
-        <v>13.4691</v>
+        <v>16.6497</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.26</v>
       </c>
       <c r="I278" t="n">
-        <v>0.4824</v>
+        <v>0.5638</v>
       </c>
       <c r="J278" t="n">
-        <v>9.1656</v>
+        <v>10.7122</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1348</v>
+        <v>-0.0839</v>
       </c>
       <c r="J279" t="n">
-        <v>-2.5612</v>
+        <v>-1.5941</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.74</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4578</v>
+        <v>-0.2928</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.6982</v>
+        <v>-5.5632</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.4</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.872</v>
+        <v>-0.604</v>
       </c>
       <c r="J281" t="n">
-        <v>-16.568</v>
+        <v>-11.476</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.31</v>
       </c>
       <c r="I282" t="n">
-        <v>0.8255</v>
+        <v>0.8218</v>
       </c>
       <c r="J282" t="n">
-        <v>23.9395</v>
+        <v>23.8322</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.29</v>
       </c>
       <c r="I283" t="n">
-        <v>0.7788</v>
+        <v>0.7755</v>
       </c>
       <c r="J283" t="n">
-        <v>22.5852</v>
+        <v>22.4895</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.15</v>
       </c>
       <c r="I284" t="n">
-        <v>0.39</v>
+        <v>0.4407</v>
       </c>
       <c r="J284" t="n">
-        <v>11.31</v>
+        <v>12.7803</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.11</v>
       </c>
       <c r="I285" t="n">
-        <v>0.2747</v>
+        <v>0.3345</v>
       </c>
       <c r="J285" t="n">
-        <v>7.9663</v>
+        <v>9.7005</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.05</v>
       </c>
       <c r="I286" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.1567</v>
       </c>
       <c r="J286" t="n">
-        <v>2.6477</v>
+        <v>4.5443</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.14</v>
       </c>
       <c r="I287" t="n">
-        <v>0.348</v>
+        <v>0.3797</v>
       </c>
       <c r="J287" t="n">
-        <v>10.092</v>
+        <v>11.0113</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.87</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.2036</v>
+        <v>-0.1519</v>
       </c>
       <c r="J288" t="n">
-        <v>-5.9044</v>
+        <v>-4.4051</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.85</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2488</v>
+        <v>-0.1718</v>
       </c>
       <c r="J289" t="n">
-        <v>-7.2152</v>
+        <v>-4.9822</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3217</v>
+        <v>-0.2113</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.3293</v>
+        <v>-6.1277</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.6</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6203</v>
+        <v>-0.4122</v>
       </c>
       <c r="J291" t="n">
-        <v>-17.9887</v>
+        <v>-11.9538</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.62</v>
       </c>
       <c r="I292" t="n">
-        <v>1.521</v>
+        <v>1.3364</v>
       </c>
       <c r="J292" t="n">
-        <v>36.504</v>
+        <v>32.0736</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.46</v>
       </c>
       <c r="I293" t="n">
-        <v>1.2076</v>
+        <v>1.1253</v>
       </c>
       <c r="J293" t="n">
-        <v>28.9824</v>
+        <v>27.0072</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.02</v>
       </c>
       <c r="I294" t="n">
-        <v>0.0408</v>
+        <v>0.0795</v>
       </c>
       <c r="J294" t="n">
-        <v>0.9792</v>
+        <v>1.908</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-0.9182</v>
       </c>
       <c r="J295" t="n">
-        <v>-22.7544</v>
+        <v>-22.0368</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.57</v>
       </c>
       <c r="I296" t="n">
-        <v>-1.2019</v>
+        <v>-1.204</v>
       </c>
       <c r="J296" t="n">
-        <v>-28.8456</v>
+        <v>-28.896</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.5</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7379</v>
+        <v>0.9167</v>
       </c>
       <c r="J297" t="n">
-        <v>17.7096</v>
+        <v>22.0008</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.31</v>
       </c>
       <c r="I298" t="n">
-        <v>0.507</v>
+        <v>0.6069</v>
       </c>
       <c r="J298" t="n">
-        <v>12.168</v>
+        <v>14.5656</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.03</v>
       </c>
       <c r="I299" t="n">
-        <v>0.0434</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="J299" t="n">
-        <v>1.0416</v>
+        <v>1.9368</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3861</v>
+        <v>-0.2379</v>
       </c>
       <c r="J300" t="n">
-        <v>-9.266400000000001</v>
+        <v>-5.7096</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.75</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4684</v>
+        <v>-0.297</v>
       </c>
       <c r="J301" t="n">
-        <v>-11.2416</v>
+        <v>-7.128</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.22</v>
       </c>
       <c r="I302" t="n">
-        <v>0.4368</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="J302" t="n">
-        <v>8.299200000000001</v>
+        <v>9.528499999999999</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.16</v>
       </c>
       <c r="I303" t="n">
-        <v>0.3497</v>
+        <v>0.3874</v>
       </c>
       <c r="J303" t="n">
-        <v>6.6443</v>
+        <v>7.3606</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.93</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1364</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="J304" t="n">
-        <v>-2.5916</v>
+        <v>-1.7803</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.87</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2541</v>
+        <v>-0.1589</v>
       </c>
       <c r="J305" t="n">
-        <v>-4.8279</v>
+        <v>-3.0191</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.47</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.7901</v>
+        <v>-0.5395</v>
       </c>
       <c r="J306" t="n">
-        <v>-15.0119</v>
+        <v>-10.2505</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>2.1</v>
       </c>
       <c r="I307" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J307" t="n">
-        <v>39.1267</v>
+        <v>34.8422</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.73</v>
       </c>
       <c r="I308" t="n">
-        <v>1.6176</v>
+        <v>1.4042</v>
       </c>
       <c r="J308" t="n">
-        <v>30.7344</v>
+        <v>26.6798</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.95</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.3541</v>
+        <v>-0.2713</v>
       </c>
       <c r="J309" t="n">
-        <v>-6.7279</v>
+        <v>-5.1547</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.87</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.5785</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="J310" t="n">
-        <v>-10.9915</v>
+        <v>-9.663399999999999</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.78</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.7952</v>
+        <v>-0.7454</v>
       </c>
       <c r="J311" t="n">
-        <v>-15.1088</v>
+        <v>-14.1626</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.7</v>
       </c>
       <c r="I312" t="n">
-        <v>1.0193</v>
+        <v>1.2009</v>
       </c>
       <c r="J312" t="n">
-        <v>19.3667</v>
+        <v>22.8171</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.03</v>
       </c>
       <c r="I313" t="n">
-        <v>0.1339</v>
+        <v>0.1152</v>
       </c>
       <c r="J313" t="n">
-        <v>2.5441</v>
+        <v>2.1888</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.5137</v>
+        <v>-0.3342</v>
       </c>
       <c r="J314" t="n">
-        <v>-9.760300000000001</v>
+        <v>-6.3498</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.63</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.5923</v>
+        <v>-0.3906</v>
       </c>
       <c r="J315" t="n">
-        <v>-11.2537</v>
+        <v>-7.4214</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.47</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.5369</v>
       </c>
       <c r="J316" t="n">
-        <v>-14.9492</v>
+        <v>-10.2011</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>2.22</v>
       </c>
       <c r="I317" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J317" t="n">
-        <v>39.1267</v>
+        <v>34.8422</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.3</v>
       </c>
       <c r="I318" t="n">
-        <v>0.6878</v>
+        <v>0.7689</v>
       </c>
       <c r="J318" t="n">
-        <v>13.0682</v>
+        <v>14.6091</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.25</v>
       </c>
       <c r="I319" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.6551</v>
       </c>
       <c r="J319" t="n">
-        <v>10.735</v>
+        <v>12.4469</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.07</v>
       </c>
       <c r="I320" t="n">
-        <v>0.0989</v>
+        <v>0.1841</v>
       </c>
       <c r="J320" t="n">
-        <v>1.8791</v>
+        <v>3.4979</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="J321" t="n">
-        <v>-13.9536</v>
+        <v>-12.8801</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7557/event_7557_evp_summary.xlsx
+++ b/database/event/7557/event_7557_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.1119</v>
+        <v>8.190200000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>3.6855</v>
+        <v>3.7211</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0241</v>
+        <v>3.1041</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1119</v>
+        <v>8.190200000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9824</v>
+        <v>2.9277</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1295</v>
+        <v>5.2624</v>
       </c>
       <c r="H2" t="n">
-        <v>5.0218</v>
+        <v>4.7654</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6111</v>
+        <v>2.5733</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1295</v>
+        <v>5.2624</v>
       </c>
       <c r="K2" t="n">
         <v>103</v>
@@ -529,7 +529,7 @@
         <v>122</v>
       </c>
       <c r="M2" t="n">
-        <v>7.740600000000001</v>
+        <v>7.835700000000001</v>
       </c>
       <c r="N2" t="n">
         <v>225</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.2944</v>
+        <v>6.2544</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8598</v>
+        <v>2.8416</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2036</v>
+        <v>2.2229</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2944</v>
+        <v>6.2544</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3882</v>
+        <v>3.0542</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9062</v>
+        <v>3.2002</v>
       </c>
       <c r="H3" t="n">
-        <v>4.0801</v>
+        <v>3.9598</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0801</v>
+        <v>3.9598</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9062</v>
+        <v>3.2002</v>
       </c>
       <c r="K3" t="n">
         <v>109</v>
@@ -575,7 +575,7 @@
         <v>102</v>
       </c>
       <c r="M3" t="n">
-        <v>6.9863</v>
+        <v>7.16</v>
       </c>
       <c r="N3" t="n">
         <v>211</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.2435</v>
+        <v>6.134</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8366</v>
+        <v>2.7869</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1806</v>
+        <v>2.1681</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2435</v>
+        <v>6.134</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7924</v>
+        <v>2.4626</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4511</v>
+        <v>3.6714</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7924</v>
+        <v>2.6649</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7924</v>
+        <v>2.6649</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4511</v>
+        <v>3.6714</v>
       </c>
       <c r="K4" t="n">
         <v>98</v>
@@ -621,7 +621,7 @@
         <v>169</v>
       </c>
       <c r="M4" t="n">
-        <v>6.2435</v>
+        <v>6.3363</v>
       </c>
       <c r="N4" t="n">
         <v>267</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1459</v>
+        <v>5.4205</v>
       </c>
       <c r="C5" t="n">
-        <v>2.338</v>
+        <v>2.4627</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6851</v>
+        <v>1.8433</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1459</v>
+        <v>5.4205</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0112</v>
+        <v>2.9951</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1347</v>
+        <v>2.4254</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1233</v>
+        <v>4.9877</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6639</v>
+        <v>2.6933</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1347</v>
+        <v>2.4254</v>
       </c>
       <c r="K5" t="n">
         <v>103</v>
@@ -667,7 +667,7 @@
         <v>122</v>
       </c>
       <c r="M5" t="n">
-        <v>4.7986</v>
+        <v>5.1187</v>
       </c>
       <c r="N5" t="n">
         <v>225</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5623</v>
+        <v>4.4157</v>
       </c>
       <c r="C6" t="n">
-        <v>2.0728</v>
+        <v>2.0062</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4216</v>
+        <v>1.3859</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5623</v>
+        <v>4.4157</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7384</v>
+        <v>2.624</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8239</v>
+        <v>1.7917</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1621</v>
+        <v>3.7634</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1641</v>
+        <v>2.0322</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8239</v>
+        <v>1.7917</v>
       </c>
       <c r="K6" t="n">
         <v>103</v>
@@ -713,7 +713,7 @@
         <v>122</v>
       </c>
       <c r="M6" t="n">
-        <v>3.988</v>
+        <v>3.8239</v>
       </c>
       <c r="N6" t="n">
         <v>225</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7615</v>
+        <v>3.9007</v>
       </c>
       <c r="C7" t="n">
-        <v>1.709</v>
+        <v>1.7722</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0601</v>
+        <v>1.1515</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7615</v>
+        <v>3.9007</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7935</v>
+        <v>2.7689</v>
       </c>
       <c r="G7" t="n">
-        <v>0.968</v>
+        <v>1.1318</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3562</v>
+        <v>4.2415</v>
       </c>
       <c r="I7" t="n">
-        <v>2.265</v>
+        <v>2.2904</v>
       </c>
       <c r="J7" t="n">
-        <v>0.968</v>
+        <v>1.1318</v>
       </c>
       <c r="K7" t="n">
         <v>80</v>
@@ -759,7 +759,7 @@
         <v>52</v>
       </c>
       <c r="M7" t="n">
-        <v>3.233</v>
+        <v>3.4222</v>
       </c>
       <c r="N7" t="n">
         <v>132</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4958</v>
+        <v>3.6665</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5883</v>
+        <v>1.6658</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9402</v>
+        <v>1.0449</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4958</v>
+        <v>3.6665</v>
       </c>
       <c r="F8" t="n">
-        <v>3.4801</v>
+        <v>1.5033</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0157</v>
+        <v>2.1632</v>
       </c>
       <c r="H8" t="n">
-        <v>6.7754</v>
+        <v>1.5033</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5229</v>
+        <v>1.5033</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0157</v>
+        <v>2.1632</v>
       </c>
       <c r="K8" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="L8" t="n">
-        <v>52</v>
+        <v>169</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5386</v>
+        <v>3.6665</v>
       </c>
       <c r="N8" t="n">
-        <v>132</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4419</v>
+        <v>3.5434</v>
       </c>
       <c r="C9" t="n">
-        <v>1.5638</v>
+        <v>1.6099</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.9888</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4419</v>
+        <v>3.5434</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5522</v>
+        <v>3.4351</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8897</v>
+        <v>0.1083</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5522</v>
+        <v>6.4395</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5522</v>
+        <v>3.4773</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8897</v>
+        <v>0.1083</v>
       </c>
       <c r="K9" t="n">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="L9" t="n">
-        <v>169</v>
+        <v>52</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4419</v>
+        <v>3.5856</v>
       </c>
       <c r="N9" t="n">
-        <v>267</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2421</v>
+        <v>3.2908</v>
       </c>
       <c r="C10" t="n">
-        <v>1.473</v>
+        <v>1.4951</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8256</v>
+        <v>0.8738</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2421</v>
+        <v>3.2908</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0691</v>
+        <v>3.0921</v>
       </c>
       <c r="G10" t="n">
-        <v>0.173</v>
+        <v>0.1987</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3272</v>
+        <v>5.3079</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7699</v>
+        <v>2.8662</v>
       </c>
       <c r="J10" t="n">
-        <v>0.173</v>
+        <v>0.1987</v>
       </c>
       <c r="K10" t="n">
         <v>80</v>
@@ -897,7 +897,7 @@
         <v>52</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9429</v>
+        <v>3.0649</v>
       </c>
       <c r="N10" t="n">
         <v>132</v>
@@ -906,369 +906,369 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.11</v>
+        <v>2.8662</v>
       </c>
       <c r="C11" t="n">
-        <v>1.413</v>
+        <v>1.3022</v>
       </c>
       <c r="D11" t="n">
-        <v>0.766</v>
+        <v>0.6805</v>
       </c>
       <c r="E11" t="n">
-        <v>3.11</v>
+        <v>2.8662</v>
       </c>
       <c r="F11" t="n">
-        <v>3.11</v>
+        <v>0.9928</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.8734</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4693</v>
+        <v>0.9928</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4693</v>
+        <v>0.5361</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1.8734</v>
       </c>
       <c r="K11" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4693</v>
+        <v>2.4095</v>
       </c>
       <c r="N11" t="n">
-        <v>97</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9318</v>
+        <v>2.8097</v>
       </c>
       <c r="C12" t="n">
-        <v>1.332</v>
+        <v>1.2765</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6855</v>
+        <v>0.6548</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9318</v>
+        <v>2.8097</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0953</v>
+        <v>2.8097</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8365</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0953</v>
+        <v>3.4246</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5695</v>
+        <v>3.4246</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8365</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L12" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.406</v>
+        <v>3.4246</v>
       </c>
       <c r="N12" t="n">
-        <v>225</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9208</v>
+        <v>2.7834</v>
       </c>
       <c r="C13" t="n">
-        <v>1.327</v>
+        <v>1.2646</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6806</v>
+        <v>0.6429</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9208</v>
+        <v>2.7834</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9208</v>
+        <v>1.6964</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.087</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0539</v>
+        <v>1.6964</v>
       </c>
       <c r="I13" t="n">
-        <v>3.0539</v>
+        <v>1.6964</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1.087</v>
       </c>
       <c r="K13" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0539</v>
+        <v>2.7834</v>
       </c>
       <c r="N13" t="n">
-        <v>114</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7895</v>
+        <v>2.5893</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2674</v>
+        <v>1.1764</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6213</v>
+        <v>0.5545</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7895</v>
+        <v>2.5893</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8454</v>
+        <v>2.5893</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0559</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8883</v>
+        <v>2.9422</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8883</v>
+        <v>2.9422</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0559</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L14" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8324</v>
+        <v>2.9422</v>
       </c>
       <c r="N14" t="n">
-        <v>171</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.7681</v>
+        <v>2.4535</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2576</v>
+        <v>1.1147</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6116</v>
+        <v>0.4927</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7681</v>
+        <v>2.4535</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8089</v>
+        <v>2.5169</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9592000000000001</v>
+        <v>-0.0634</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8089</v>
+        <v>2.7838</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8089</v>
+        <v>2.7838</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9592000000000001</v>
+        <v>-0.0634</v>
       </c>
       <c r="K15" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L15" t="n">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7681</v>
+        <v>2.7204</v>
       </c>
       <c r="N15" t="n">
-        <v>211</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0829</v>
+        <v>2.1752</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9463</v>
+        <v>0.9883</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3023</v>
+        <v>0.366</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0829</v>
+        <v>2.1752</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0829</v>
+        <v>-0.3989</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2.5741</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0829</v>
+        <v>-0.3989</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0829</v>
+        <v>-0.3989</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2.5741</v>
       </c>
       <c r="K16" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0829</v>
+        <v>2.1752</v>
       </c>
       <c r="N16" t="n">
-        <v>114</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0757</v>
+        <v>2.0153</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9431</v>
+        <v>0.9156</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2991</v>
+        <v>0.2932</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0757</v>
+        <v>2.0153</v>
       </c>
       <c r="F17" t="n">
-        <v>2.168</v>
+        <v>2.0153</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.09229999999999999</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.168</v>
+        <v>2.0153</v>
       </c>
       <c r="I17" t="n">
-        <v>2.168</v>
+        <v>2.0153</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.09229999999999999</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="L17" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0757</v>
+        <v>2.0153</v>
       </c>
       <c r="N17" t="n">
-        <v>133</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9248</v>
+        <v>1.9312</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.8774</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2309</v>
+        <v>0.2549</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9248</v>
+        <v>1.9312</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3803</v>
+        <v>2.0505</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3051</v>
+        <v>-0.1193</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3803</v>
+        <v>2.0505</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3803</v>
+        <v>2.0505</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3051</v>
+        <v>-0.1193</v>
       </c>
       <c r="K18" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="L18" t="n">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9248</v>
+        <v>1.9312</v>
       </c>
       <c r="N18" t="n">
-        <v>211</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8653</v>
+        <v>1.805</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8475</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2041</v>
+        <v>0.1975</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8653</v>
+        <v>1.805</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4677</v>
+        <v>1.3586</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3976</v>
+        <v>0.4464</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4677</v>
+        <v>1.3586</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4677</v>
+        <v>1.3586</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3976</v>
+        <v>0.4464</v>
       </c>
       <c r="K19" t="n">
         <v>112</v>
@@ -1311,7 +1311,7 @@
         <v>59</v>
       </c>
       <c r="M19" t="n">
-        <v>1.8653</v>
+        <v>1.805</v>
       </c>
       <c r="N19" t="n">
         <v>171</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5435</v>
+        <v>1.5092</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7013</v>
+        <v>0.6857</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0588</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5435</v>
+        <v>1.5092</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5435</v>
+        <v>1.5092</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5435</v>
+        <v>1.5092</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5435</v>
+        <v>1.5092</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5435</v>
+        <v>1.5092</v>
       </c>
       <c r="N20" t="n">
         <v>114</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3054</v>
+        <v>1.1907</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5931</v>
+        <v>0.541</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0487</v>
+        <v>-0.0822</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3054</v>
+        <v>1.1907</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4134</v>
+        <v>1.3261</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.108</v>
+        <v>-0.1354</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4134</v>
+        <v>1.3261</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7349</v>
+        <v>0.7161</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.108</v>
+        <v>-0.1354</v>
       </c>
       <c r="K21" t="n">
         <v>80</v>
@@ -1403,7 +1403,7 @@
         <v>52</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6269</v>
+        <v>0.5807</v>
       </c>
       <c r="N21" t="n">
         <v>132</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.219</v>
+        <v>1.1763</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5538</v>
+        <v>0.5344</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0877</v>
+        <v>-0.0887</v>
       </c>
       <c r="E22" t="n">
-        <v>1.219</v>
+        <v>1.1763</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3978</v>
+        <v>1.3583</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1788</v>
+        <v>-0.182</v>
       </c>
       <c r="H22" t="n">
-        <v>1.3978</v>
+        <v>1.3583</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3978</v>
+        <v>1.3583</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1788</v>
+        <v>-0.182</v>
       </c>
       <c r="K22" t="n">
         <v>112</v>
@@ -1449,7 +1449,7 @@
         <v>59</v>
       </c>
       <c r="M22" t="n">
-        <v>1.219</v>
+        <v>1.1763</v>
       </c>
       <c r="N22" t="n">
         <v>171</v>
@@ -1458,81 +1458,81 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.2097</v>
+        <v>1.1636</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5496</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0919</v>
+        <v>-0.0945</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2097</v>
+        <v>1.1636</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2155</v>
+        <v>0.4</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0058</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2155</v>
+        <v>0.4</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2155</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0058</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L23" t="n">
-        <v>38</v>
+        <v>169</v>
       </c>
       <c r="M23" t="n">
-        <v>1.2097</v>
+        <v>1.1636</v>
       </c>
       <c r="N23" t="n">
-        <v>133</v>
+        <v>267</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0239</v>
+        <v>1.1633</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4652</v>
+        <v>0.5285</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1758</v>
+        <v>-0.0946</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0239</v>
+        <v>1.1633</v>
       </c>
       <c r="F24" t="n">
-        <v>0.665</v>
+        <v>1.1741</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3589</v>
+        <v>-0.0108</v>
       </c>
       <c r="H24" t="n">
-        <v>0.665</v>
+        <v>1.1741</v>
       </c>
       <c r="I24" t="n">
-        <v>0.665</v>
+        <v>1.1741</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3589</v>
+        <v>-0.0108</v>
       </c>
       <c r="K24" t="n">
         <v>95</v>
@@ -1541,7 +1541,7 @@
         <v>38</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0239</v>
+        <v>1.1633</v>
       </c>
       <c r="N24" t="n">
         <v>133</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0117</v>
+        <v>1.0753</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4597</v>
+        <v>0.4885</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1813</v>
+        <v>-0.1347</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0117</v>
+        <v>1.0753</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3694</v>
+        <v>0.6879</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6423</v>
+        <v>0.3874</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3694</v>
+        <v>0.6879</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3694</v>
+        <v>0.6879</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6423</v>
+        <v>0.3874</v>
       </c>
       <c r="K25" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L25" t="n">
-        <v>169</v>
+        <v>38</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0117</v>
+        <v>1.0753</v>
       </c>
       <c r="N25" t="n">
-        <v>267</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3345</v>
+        <v>0.3481</v>
       </c>
       <c r="C26" t="n">
-        <v>0.152</v>
+        <v>0.1582</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.487</v>
+        <v>-0.4657</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3345</v>
+        <v>0.3481</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3345</v>
+        <v>-0.1495</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.4976</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3345</v>
+        <v>-0.1495</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3345</v>
+        <v>-0.1495</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.4976</v>
       </c>
       <c r="K26" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3345</v>
+        <v>0.3481</v>
       </c>
       <c r="N26" t="n">
-        <v>97</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27">
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2512</v>
+        <v>0.3447</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1141</v>
+        <v>0.1566</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5246</v>
+        <v>-0.4673</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2512</v>
+        <v>0.3447</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4193</v>
+        <v>-0.4504</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6705</v>
+        <v>0.7951</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.4193</v>
+        <v>-0.4504</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.4193</v>
+        <v>-0.4504</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6705</v>
+        <v>0.7951</v>
       </c>
       <c r="K27" t="n">
         <v>98</v>
@@ -1679,7 +1679,7 @@
         <v>169</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2512</v>
+        <v>0.3447</v>
       </c>
       <c r="N27" t="n">
         <v>267</v>
@@ -1688,139 +1688,139 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1572</v>
+        <v>0.3191</v>
       </c>
       <c r="C28" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.145</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.4789</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1572</v>
+        <v>0.3191</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1886</v>
+        <v>0.3191</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0314</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1886</v>
+        <v>0.3191</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1886</v>
+        <v>0.3191</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.0314</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="L28" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1572</v>
+        <v>0.3191</v>
       </c>
       <c r="N28" t="n">
-        <v>171</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1301</v>
+        <v>0.1491</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0591</v>
+        <v>0.0677</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5793</v>
+        <v>-0.5563</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1301</v>
+        <v>0.1491</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1606</v>
+        <v>-0.1941</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2907</v>
+        <v>0.3432</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1606</v>
+        <v>-0.1941</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1606</v>
+        <v>-0.1941</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2907</v>
+        <v>0.3432</v>
       </c>
       <c r="K29" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="L29" t="n">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1301</v>
+        <v>0.1491</v>
       </c>
       <c r="N29" t="n">
-        <v>267</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0318</v>
+        <v>0.0921</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0144</v>
+        <v>0.0418</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6237</v>
+        <v>-0.5823</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0318</v>
+        <v>0.0921</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1235</v>
+        <v>0.1311</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1553</v>
+        <v>-0.039</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1235</v>
+        <v>0.1311</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1235</v>
+        <v>0.1311</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1553</v>
+        <v>-0.039</v>
       </c>
       <c r="K30" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L30" t="n">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="M30" t="n">
-        <v>0.03179999999999999</v>
+        <v>0.09209999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>211</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1488</v>
+        <v>-0.19</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0863</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7052</v>
+        <v>-0.7107</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1488</v>
+        <v>-0.19</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1488</v>
+        <v>-0.19</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1488</v>
+        <v>-0.19</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1488</v>
+        <v>-0.19</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1488</v>
+        <v>-0.19</v>
       </c>
       <c r="N31" t="n">
         <v>114</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5093</v>
+        <v>-0.5374</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2314</v>
+        <v>-0.2442</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8679</v>
+        <v>-0.8688</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5093</v>
+        <v>-0.5374</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2563</v>
+        <v>0.2556</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.793</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2563</v>
+        <v>0.2556</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2563</v>
+        <v>0.2556</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.793</v>
       </c>
       <c r="K32" t="n">
         <v>95</v>
@@ -1909,7 +1909,7 @@
         <v>38</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5093</v>
+        <v>-0.5374000000000001</v>
       </c>
       <c r="N32" t="n">
         <v>133</v>
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5924</v>
+        <v>-0.5785</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2691</v>
+        <v>-0.2628</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9055</v>
+        <v>-0.8875</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5924</v>
+        <v>-0.5785</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6039</v>
+        <v>-0.5848</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0115</v>
+        <v>0.0063</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6039</v>
+        <v>-0.5848</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6039</v>
+        <v>-0.5848</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0115</v>
+        <v>0.0063</v>
       </c>
       <c r="K33" t="n">
         <v>112</v>
@@ -1955,7 +1955,7 @@
         <v>59</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5924</v>
+        <v>-0.5785</v>
       </c>
       <c r="N33" t="n">
         <v>171</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6471</v>
+        <v>-0.6973</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.294</v>
+        <v>-0.3168</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9301</v>
+        <v>-0.9416</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6471</v>
+        <v>-0.6973</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6471</v>
+        <v>-0.6973</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6471</v>
+        <v>-0.6973</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6471</v>
+        <v>-0.6973</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6471</v>
+        <v>-0.6973</v>
       </c>
       <c r="N34" t="n">
         <v>97</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6621</v>
+        <v>-0.7032</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3008</v>
+        <v>-0.3195</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9369</v>
+        <v>-0.9443</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6621</v>
+        <v>-0.7032</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6621</v>
+        <v>-0.7032</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6621</v>
+        <v>-0.7032</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6621</v>
+        <v>-0.7032</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6621</v>
+        <v>-0.7032</v>
       </c>
       <c r="N35" t="n">
         <v>97</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7961</v>
+        <v>-0.8395</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3617</v>
+        <v>-0.3814</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9974</v>
+        <v>-1.0064</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7961</v>
+        <v>-0.8395</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7961</v>
+        <v>-0.8395</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7961</v>
+        <v>-0.8395</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7961</v>
+        <v>-0.8395</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7961</v>
+        <v>-0.8395</v>
       </c>
       <c r="N36" t="n">
         <v>97</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3718</v>
+        <v>-1.386</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.6233</v>
+        <v>-0.6297</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2573</v>
+        <v>-1.2551</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3718</v>
+        <v>-1.386</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.3718</v>
+        <v>-1.386</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.3718</v>
+        <v>-1.386</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.3718</v>
+        <v>-1.386</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.3718</v>
+        <v>-1.386</v>
       </c>
       <c r="N37" t="n">
         <v>114</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.0373</v>
+        <v>-1.9749</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.9256</v>
+        <v>-0.8973</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.5578</v>
+        <v>-1.5232</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.0373</v>
+        <v>-1.9749</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.1874</v>
+        <v>-1.1014</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.8499</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.1874</v>
+        <v>-1.1014</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.1874</v>
+        <v>-1.1014</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.8499</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="K38" t="n">
         <v>95</v>
@@ -2185,7 +2185,7 @@
         <v>38</v>
       </c>
       <c r="M38" t="n">
-        <v>-2.0373</v>
+        <v>-1.9749</v>
       </c>
       <c r="N38" t="n">
         <v>133</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.2997</v>
+        <v>-2.1012</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.0448</v>
+        <v>-0.9546</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.6762</v>
+        <v>-1.5807</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.2997</v>
+        <v>-2.1012</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9312</v>
+        <v>-0.8625</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.3685</v>
+        <v>-1.2387</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9312</v>
+        <v>-0.8625</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9312</v>
+        <v>-0.8625</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.3685</v>
+        <v>-1.2387</v>
       </c>
       <c r="K39" t="n">
         <v>109</v>
@@ -2231,7 +2231,7 @@
         <v>102</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.2997</v>
+        <v>-2.1012</v>
       </c>
       <c r="N39" t="n">
         <v>211</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.3795</v>
+        <v>-2.139</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.0811</v>
+        <v>-0.9718</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.7122</v>
+        <v>-1.5979</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.3795</v>
+        <v>-2.139</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.8423</v>
+        <v>-1.6</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.5372</v>
+        <v>-0.539</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.8423</v>
+        <v>-1.6</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9579</v>
+        <v>-0.864</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.5372</v>
+        <v>-0.539</v>
       </c>
       <c r="K40" t="n">
         <v>80</v>
@@ -2277,7 +2277,7 @@
         <v>52</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4951</v>
+        <v>-1.403</v>
       </c>
       <c r="N40" t="n">
         <v>132</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.5594</v>
+        <v>-3.1401</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.6172</v>
+        <v>-1.4267</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.2449</v>
+        <v>-2.0536</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.5594</v>
+        <v>-3.1401</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.9225</v>
+        <v>-3.5714</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3631</v>
+        <v>0.4313</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.9225</v>
+        <v>-3.5714</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.0395</v>
+        <v>-1.9285</v>
       </c>
       <c r="J41" t="n">
-        <v>0.3631</v>
+        <v>0.4313</v>
       </c>
       <c r="K41" t="n">
         <v>103</v>
@@ -2323,7 +2323,7 @@
         <v>122</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.6764</v>
+        <v>-1.4972</v>
       </c>
       <c r="N41" t="n">
         <v>225</v>
@@ -2429,10 +2429,10 @@
         <v>1.43</v>
       </c>
       <c r="I2" t="n">
-        <v>1.045</v>
+        <v>1.0018</v>
       </c>
       <c r="J2" t="n">
-        <v>20.9</v>
+        <v>20.036</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.43</v>
       </c>
       <c r="I3" t="n">
-        <v>1.045</v>
+        <v>1.0018</v>
       </c>
       <c r="J3" t="n">
-        <v>20.9</v>
+        <v>20.036</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.39</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9254</v>
       </c>
       <c r="J4" t="n">
-        <v>19.628</v>
+        <v>18.508</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1464</v>
+        <v>0.1654</v>
       </c>
       <c r="J5" t="n">
-        <v>2.928</v>
+        <v>3.308</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6288</v>
+        <v>-0.583</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.576</v>
+        <v>-11.66</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.24</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5411</v>
+        <v>0.5226</v>
       </c>
       <c r="J7" t="n">
-        <v>10.822</v>
+        <v>10.452</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.03</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1093</v>
+        <v>0.1126</v>
       </c>
       <c r="J8" t="n">
-        <v>2.186</v>
+        <v>2.252</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1476</v>
+        <v>-0.1627</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.952</v>
+        <v>-3.254</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.84</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1894</v>
+        <v>-0.2049</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.788</v>
+        <v>-4.098</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.63</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3931</v>
+        <v>-0.404</v>
       </c>
       <c r="J11" t="n">
-        <v>-7.862</v>
+        <v>-8.08</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>2.02</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7115</v>
+        <v>1.8453</v>
       </c>
       <c r="J12" t="n">
-        <v>30.807</v>
+        <v>33.2154</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.31</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7792</v>
+        <v>0.7477</v>
       </c>
       <c r="J13" t="n">
-        <v>14.0256</v>
+        <v>13.4586</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.28</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7113</v>
+        <v>0.6877</v>
       </c>
       <c r="J14" t="n">
-        <v>12.8034</v>
+        <v>12.3786</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.23</v>
       </c>
       <c r="I15" t="n">
-        <v>0.594</v>
+        <v>0.5835</v>
       </c>
       <c r="J15" t="n">
-        <v>10.692</v>
+        <v>10.503</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.14</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3673</v>
+        <v>0.3795</v>
       </c>
       <c r="J16" t="n">
-        <v>6.6114</v>
+        <v>6.831</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.28</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6484</v>
+        <v>0.6145</v>
       </c>
       <c r="J17" t="n">
-        <v>11.6712</v>
+        <v>11.061</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.27</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6298</v>
+        <v>0.5977</v>
       </c>
       <c r="J18" t="n">
-        <v>11.3364</v>
+        <v>10.7586</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.68</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3376</v>
+        <v>-0.3522</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.0768</v>
+        <v>-6.3396</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.59</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.422</v>
+        <v>-0.433</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.596</v>
+        <v>-7.794</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.47</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5319</v>
+        <v>-0.5369</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.574199999999999</v>
+        <v>-9.664199999999999</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>2.28</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8681</v>
+        <v>1.8453</v>
       </c>
       <c r="J22" t="n">
-        <v>37.362</v>
+        <v>36.906</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.35</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8962</v>
+        <v>0.845</v>
       </c>
       <c r="J23" t="n">
-        <v>17.924</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.08</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2357</v>
+        <v>0.2503</v>
       </c>
       <c r="J24" t="n">
-        <v>4.714</v>
+        <v>5.006</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.91</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3836</v>
+        <v>-0.3597</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.672</v>
+        <v>-7.194</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.57</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.2377</v>
+        <v>-1.1145</v>
       </c>
       <c r="J26" t="n">
-        <v>-24.754</v>
+        <v>-22.29</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.66</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1585</v>
+        <v>1.1684</v>
       </c>
       <c r="J27" t="n">
-        <v>23.17</v>
+        <v>23.368</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.96</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0556</v>
+        <v>-0.0667</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.112</v>
+        <v>-1.334</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.78</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2482</v>
+        <v>-0.2637</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.964</v>
+        <v>-5.274</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.73</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.297</v>
+        <v>-0.3115</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.94</v>
+        <v>-6.23</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.43</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5735</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.47</v>
+        <v>-11.502</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.19</v>
       </c>
       <c r="I32" t="n">
-        <v>0.428</v>
+        <v>0.4619</v>
       </c>
       <c r="J32" t="n">
-        <v>7.704</v>
+        <v>8.3142</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.86</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1593</v>
+        <v>-0.177</v>
       </c>
       <c r="J33" t="n">
-        <v>-2.8674</v>
+        <v>-3.186</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.8</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2181</v>
+        <v>-0.2362</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.9258</v>
+        <v>-4.2516</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.67</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.343</v>
+        <v>-0.3581</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.174</v>
+        <v>-6.4458</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.62</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.39</v>
+        <v>-0.4032</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.02</v>
+        <v>-7.2576</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.74</v>
       </c>
       <c r="I37" t="n">
-        <v>1.121</v>
+        <v>1.2342</v>
       </c>
       <c r="J37" t="n">
-        <v>20.178</v>
+        <v>22.2156</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.7</v>
       </c>
       <c r="I38" t="n">
-        <v>1.0739</v>
+        <v>1.1842</v>
       </c>
       <c r="J38" t="n">
-        <v>19.3302</v>
+        <v>21.3156</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.36</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6626</v>
+        <v>0.7399</v>
       </c>
       <c r="J39" t="n">
-        <v>11.9268</v>
+        <v>13.3182</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.19</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4323</v>
+        <v>0.4834</v>
       </c>
       <c r="J40" t="n">
-        <v>7.7814</v>
+        <v>8.7012</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.88</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4996</v>
+        <v>-0.4599</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.992800000000001</v>
+        <v>-8.2782</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.32</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9495</v>
+        <v>1.0916</v>
       </c>
       <c r="J42" t="n">
-        <v>15.192</v>
+        <v>17.4656</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>2.01</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7778</v>
+        <v>0.8974</v>
       </c>
       <c r="J43" t="n">
-        <v>12.4448</v>
+        <v>14.3584</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.19</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2431</v>
+        <v>0.2672</v>
       </c>
       <c r="J44" t="n">
-        <v>3.8896</v>
+        <v>4.2752</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0921</v>
+        <v>-0.091</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.4736</v>
+        <v>-1.456</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.79</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2896</v>
+        <v>-0.2942</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.6336</v>
+        <v>-4.7072</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.98</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0122</v>
+        <v>-0.008</v>
       </c>
       <c r="J47" t="n">
-        <v>0.1952</v>
+        <v>-0.128</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1973</v>
+        <v>-0.2181</v>
       </c>
       <c r="J48" t="n">
-        <v>-3.1568</v>
+        <v>-3.4896</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.75</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2563</v>
+        <v>-0.2762</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.1008</v>
+        <v>-4.4192</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.6</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3954</v>
+        <v>-0.4106</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.3264</v>
+        <v>-6.5696</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.55</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4421</v>
+        <v>-0.4549</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.0736</v>
+        <v>-7.2784</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.24</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4832</v>
+        <v>0.5259</v>
       </c>
       <c r="J52" t="n">
-        <v>8.6976</v>
+        <v>9.466200000000001</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.12</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3409</v>
+        <v>0.3358</v>
       </c>
       <c r="J53" t="n">
-        <v>6.1362</v>
+        <v>6.0444</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.64</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3721</v>
+        <v>-0.3859</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.6978</v>
+        <v>-6.9462</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.6</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4095</v>
+        <v>-0.4217</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.371</v>
+        <v>-7.5906</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.57</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4373</v>
+        <v>-0.4481</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.8714</v>
+        <v>-8.065799999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.74</v>
       </c>
       <c r="I57" t="n">
-        <v>1.1155</v>
+        <v>1.2293</v>
       </c>
       <c r="J57" t="n">
-        <v>20.079</v>
+        <v>22.1274</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.55</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8905999999999999</v>
+        <v>0.9892</v>
       </c>
       <c r="J58" t="n">
-        <v>16.0308</v>
+        <v>17.8056</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.5</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8303</v>
+        <v>0.9242</v>
       </c>
       <c r="J59" t="n">
-        <v>14.9454</v>
+        <v>16.6356</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.27</v>
       </c>
       <c r="I60" t="n">
-        <v>0.5422</v>
+        <v>0.6072</v>
       </c>
       <c r="J60" t="n">
-        <v>9.759600000000001</v>
+        <v>10.9296</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3282</v>
+        <v>-0.2998</v>
       </c>
       <c r="J61" t="n">
-        <v>-5.9076</v>
+        <v>-5.3964</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>2.26</v>
       </c>
       <c r="I62" t="n">
-        <v>1.7427</v>
+        <v>1.8782</v>
       </c>
       <c r="J62" t="n">
-        <v>40.0821</v>
+        <v>43.1986</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.08</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2215</v>
+        <v>0.2404</v>
       </c>
       <c r="J63" t="n">
-        <v>5.0945</v>
+        <v>5.5292</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.08</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2215</v>
+        <v>0.2404</v>
       </c>
       <c r="J64" t="n">
-        <v>5.0945</v>
+        <v>5.5292</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.05</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1287</v>
+        <v>0.153</v>
       </c>
       <c r="J65" t="n">
-        <v>2.9601</v>
+        <v>3.519</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.02</v>
       </c>
       <c r="I66" t="n">
-        <v>0.0236</v>
+        <v>0.0511</v>
       </c>
       <c r="J66" t="n">
-        <v>0.5427999999999999</v>
+        <v>1.1753</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.7</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8942</v>
+        <v>0.993</v>
       </c>
       <c r="J67" t="n">
-        <v>20.5666</v>
+        <v>22.839</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.35</v>
       </c>
       <c r="I68" t="n">
-        <v>0.556</v>
+        <v>0.6178</v>
       </c>
       <c r="J68" t="n">
-        <v>12.788</v>
+        <v>14.2094</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.65</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3812</v>
+        <v>-0.3915</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.7676</v>
+        <v>-9.0045</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.62</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.409</v>
+        <v>-0.4181</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.407</v>
+        <v>-9.616300000000001</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.59</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4365</v>
+        <v>-0.4445</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.0395</v>
+        <v>-10.2235</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.2</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3691</v>
+        <v>0.3834</v>
       </c>
       <c r="J72" t="n">
-        <v>7.382</v>
+        <v>7.668</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.04</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1298</v>
+        <v>0.1281</v>
       </c>
       <c r="J73" t="n">
-        <v>2.596</v>
+        <v>2.562</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.78</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2373</v>
+        <v>-0.2553</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.746</v>
+        <v>-5.106</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.7</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3142</v>
+        <v>-0.3304</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.284</v>
+        <v>-6.608</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.41</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5827</v>
+        <v>-0.585</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.654</v>
+        <v>-11.7</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.57</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5372</v>
+        <v>0.617</v>
       </c>
       <c r="J77" t="n">
-        <v>10.744</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.5</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4937</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>9.874000000000001</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.46</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4685</v>
+        <v>0.5364</v>
       </c>
       <c r="J79" t="n">
-        <v>9.369999999999999</v>
+        <v>10.728</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.26</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3381</v>
+        <v>0.3618</v>
       </c>
       <c r="J80" t="n">
-        <v>6.762</v>
+        <v>7.236</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.72</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3452</v>
+        <v>-0.3513</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.904</v>
+        <v>-7.026</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.37</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7086</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="J82" t="n">
-        <v>14.8806</v>
+        <v>16.4388</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.23</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5154</v>
+        <v>0.57</v>
       </c>
       <c r="J83" t="n">
-        <v>10.8234</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3129</v>
+        <v>0.3178</v>
       </c>
       <c r="J84" t="n">
-        <v>6.5709</v>
+        <v>6.6738</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.07</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2265</v>
+        <v>0.2367</v>
       </c>
       <c r="J85" t="n">
-        <v>4.7565</v>
+        <v>4.9707</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.99</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.0848</v>
       </c>
       <c r="J86" t="n">
-        <v>-1.9173</v>
+        <v>-1.7808</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.11</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3036</v>
+        <v>0.299</v>
       </c>
       <c r="J87" t="n">
-        <v>6.3756</v>
+        <v>6.279</v>
       </c>
     </row>
     <row r="88">
@@ -5909,10 +5909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0775</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.6275</v>
+        <v>-1.9089</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.77</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2547</v>
+        <v>-0.2708</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.3487</v>
+        <v>-5.6868</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4532</v>
+        <v>-0.4621</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.517200000000001</v>
+        <v>-9.7041</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.36</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5737</v>
+        <v>0.6362</v>
       </c>
       <c r="J92" t="n">
-        <v>13.1951</v>
+        <v>14.6326</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.03</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1015</v>
+        <v>0.1069</v>
       </c>
       <c r="J93" t="n">
-        <v>2.3345</v>
+        <v>2.4587</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.93</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0954</v>
+        <v>-0.108</v>
       </c>
       <c r="J94" t="n">
-        <v>-2.1942</v>
+        <v>-2.484</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.92</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1069</v>
+        <v>-0.12</v>
       </c>
       <c r="J95" t="n">
-        <v>-2.4587</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.53</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.488</v>
+        <v>-0.494</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.224</v>
+        <v>-11.362</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.44</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8033</v>
+        <v>0.8851</v>
       </c>
       <c r="J97" t="n">
-        <v>18.4759</v>
+        <v>20.3573</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.32</v>
       </c>
       <c r="I98" t="n">
-        <v>0.642</v>
+        <v>0.7098</v>
       </c>
       <c r="J98" t="n">
-        <v>14.766</v>
+        <v>16.3254</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.24</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5306</v>
+        <v>0.5867</v>
       </c>
       <c r="J99" t="n">
-        <v>12.2038</v>
+        <v>13.4941</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.93</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3</v>
+        <v>-0.2874</v>
       </c>
       <c r="J100" t="n">
-        <v>-6.9</v>
+        <v>-6.6102</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.8</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.616</v>
       </c>
       <c r="J101" t="n">
-        <v>-15.2214</v>
+        <v>-14.168</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.13</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3092</v>
+        <v>0.312</v>
       </c>
       <c r="J102" t="n">
-        <v>11.1312</v>
+        <v>11.232</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.04</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1184</v>
+        <v>0.1263</v>
       </c>
       <c r="J103" t="n">
-        <v>4.2624</v>
+        <v>4.5468</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.01</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0395</v>
+        <v>0.0446</v>
       </c>
       <c r="J104" t="n">
-        <v>1.422</v>
+        <v>1.6056</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.9</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1329</v>
+        <v>-0.1459</v>
       </c>
       <c r="J105" t="n">
-        <v>-4.7844</v>
+        <v>-5.2524</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.86</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1761</v>
+        <v>-0.1898</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.3396</v>
+        <v>-6.8328</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.34</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6734</v>
+        <v>0.7433</v>
       </c>
       <c r="J107" t="n">
-        <v>24.2424</v>
+        <v>26.7588</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.27</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5763</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="J108" t="n">
-        <v>20.7468</v>
+        <v>22.9176</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.16</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4169</v>
+        <v>0.4575</v>
       </c>
       <c r="J109" t="n">
-        <v>15.0084</v>
+        <v>16.47</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.02</v>
       </c>
       <c r="I110" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0803</v>
       </c>
       <c r="J110" t="n">
-        <v>2.3616</v>
+        <v>2.8908</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.85</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5248</v>
+        <v>-0.4943</v>
       </c>
       <c r="J111" t="n">
-        <v>-18.8928</v>
+        <v>-17.7948</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.14</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3717</v>
+        <v>0.381</v>
       </c>
       <c r="J112" t="n">
-        <v>7.0623</v>
+        <v>7.239</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.85</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1684</v>
+        <v>-0.1865</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.1996</v>
+        <v>-3.5435</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.8</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2171</v>
+        <v>-0.2354</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.1249</v>
+        <v>-4.4726</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.68</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3321</v>
+        <v>-0.3479</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.3099</v>
+        <v>-6.6101</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.62</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3886</v>
+        <v>-0.4021</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.3834</v>
+        <v>-7.6399</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.58</v>
       </c>
       <c r="I117" t="n">
-        <v>0.956</v>
+        <v>1.0537</v>
       </c>
       <c r="J117" t="n">
-        <v>18.164</v>
+        <v>20.0203</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.57</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9435</v>
+        <v>1.0405</v>
       </c>
       <c r="J118" t="n">
-        <v>17.9265</v>
+        <v>19.7695</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.51</v>
       </c>
       <c r="I119" t="n">
-        <v>0.8683999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="J119" t="n">
-        <v>16.4996</v>
+        <v>18.24</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.98</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1576</v>
+        <v>-0.1439</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.9944</v>
+        <v>-2.7341</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.62</v>
       </c>
       <c r="I121" t="n">
-        <v>-1.1249</v>
+        <v>-1.0171</v>
       </c>
       <c r="J121" t="n">
-        <v>-21.3731</v>
+        <v>-19.3249</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.27</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5273</v>
+        <v>0.5739</v>
       </c>
       <c r="J122" t="n">
-        <v>10.0187</v>
+        <v>10.9041</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.02</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1248</v>
+        <v>0.1161</v>
       </c>
       <c r="J123" t="n">
-        <v>2.3712</v>
+        <v>2.2059</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.63</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3775</v>
+        <v>-0.3918</v>
       </c>
       <c r="J124" t="n">
-        <v>-7.1725</v>
+        <v>-7.4442</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.57</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4335</v>
+        <v>-0.4451</v>
       </c>
       <c r="J125" t="n">
-        <v>-8.236499999999999</v>
+        <v>-8.456899999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.54</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4613</v>
+        <v>-0.4714</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.764699999999999</v>
+        <v>-8.9566</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.61</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9892</v>
+        <v>1.0899</v>
       </c>
       <c r="J127" t="n">
-        <v>18.7948</v>
+        <v>20.7081</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.52</v>
       </c>
       <c r="I128" t="n">
-        <v>0.8776</v>
+        <v>0.9705</v>
       </c>
       <c r="J128" t="n">
-        <v>16.6744</v>
+        <v>18.4395</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.33</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.7065</v>
       </c>
       <c r="J129" t="n">
-        <v>12.0574</v>
+        <v>13.4235</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.03</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0679</v>
+        <v>0.0926</v>
       </c>
       <c r="J130" t="n">
-        <v>1.2901</v>
+        <v>1.7594</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.85</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5591</v>
+        <v>-0.5185</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.6229</v>
+        <v>-9.8515</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.34</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9184</v>
+        <v>0.8569</v>
       </c>
       <c r="J132" t="n">
-        <v>26.6336</v>
+        <v>24.8501</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.18</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5309</v>
+        <v>0.5145</v>
       </c>
       <c r="J133" t="n">
-        <v>15.3961</v>
+        <v>14.9205</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.01</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0303</v>
+        <v>0.0429</v>
       </c>
       <c r="J134" t="n">
-        <v>0.8787</v>
+        <v>1.2441</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.01</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0303</v>
+        <v>0.0429</v>
       </c>
       <c r="J135" t="n">
-        <v>0.8787</v>
+        <v>1.2441</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.99</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.0793</v>
+        <v>-0.0765</v>
       </c>
       <c r="J136" t="n">
-        <v>-2.2997</v>
+        <v>-2.2185</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.5</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9575</v>
+        <v>0.9045</v>
       </c>
       <c r="J137" t="n">
-        <v>27.7675</v>
+        <v>26.2305</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.05</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1427</v>
+        <v>0.1503</v>
       </c>
       <c r="J138" t="n">
-        <v>4.1383</v>
+        <v>4.3587</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.96</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0618</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="J139" t="n">
-        <v>-1.7922</v>
+        <v>-2.0706</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2271</v>
+        <v>-0.241</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.5859</v>
+        <v>-6.989</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.6</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4276</v>
+        <v>-0.4359</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.4004</v>
+        <v>-12.6411</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.36</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9412</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="J142" t="n">
-        <v>21.6476</v>
+        <v>20.2768</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.31</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8282</v>
+        <v>0.7812</v>
       </c>
       <c r="J143" t="n">
-        <v>19.0486</v>
+        <v>17.9676</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.26</v>
       </c>
       <c r="I144" t="n">
-        <v>0.7108</v>
+        <v>0.678</v>
       </c>
       <c r="J144" t="n">
-        <v>16.3484</v>
+        <v>15.594</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.08</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2539</v>
+        <v>0.2629</v>
       </c>
       <c r="J145" t="n">
-        <v>5.8397</v>
+        <v>6.0467</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.8</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6659</v>
+        <v>-0.6188</v>
       </c>
       <c r="J146" t="n">
-        <v>-15.3157</v>
+        <v>-14.2324</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.28</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5743</v>
+        <v>0.5598</v>
       </c>
       <c r="J147" t="n">
-        <v>13.2089</v>
+        <v>12.8754</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.12</v>
       </c>
       <c r="I148" t="n">
-        <v>0.281</v>
+        <v>0.2869</v>
       </c>
       <c r="J148" t="n">
-        <v>6.463</v>
+        <v>6.5987</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.1</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2412</v>
+        <v>0.2487</v>
       </c>
       <c r="J149" t="n">
-        <v>5.5476</v>
+        <v>5.7201</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.09</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2208</v>
+        <v>0.2291</v>
       </c>
       <c r="J150" t="n">
-        <v>5.0784</v>
+        <v>5.2693</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.52</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5036</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.5828</v>
+        <v>-11.6748</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.47</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6061</v>
+        <v>0.6062</v>
       </c>
       <c r="J152" t="n">
-        <v>13.9403</v>
+        <v>13.9426</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.12</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1871</v>
+        <v>0.2035</v>
       </c>
       <c r="J153" t="n">
-        <v>4.3033</v>
+        <v>4.6805</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.08</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1314</v>
+        <v>0.147</v>
       </c>
       <c r="J154" t="n">
-        <v>3.0222</v>
+        <v>3.381</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.01</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0121</v>
+        <v>0.0212</v>
       </c>
       <c r="J155" t="n">
-        <v>0.2783</v>
+        <v>0.4876</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.97</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.0631</v>
+        <v>-0.0683</v>
       </c>
       <c r="J156" t="n">
-        <v>-1.4513</v>
+        <v>-1.5709</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.66</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9185</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="J157" t="n">
-        <v>21.1255</v>
+        <v>20.1365</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.97</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0515</v>
+        <v>-0.0593</v>
       </c>
       <c r="J158" t="n">
-        <v>-1.1845</v>
+        <v>-1.3639</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0898</v>
+        <v>-0.1003</v>
       </c>
       <c r="J159" t="n">
-        <v>-2.0654</v>
+        <v>-2.3069</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.76</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2804</v>
+        <v>-0.2928</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.4492</v>
+        <v>-6.7344</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.75</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2901</v>
+        <v>-0.3024</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.6723</v>
+        <v>-6.9552</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.08</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3172</v>
+        <v>0.2949</v>
       </c>
       <c r="J162" t="n">
-        <v>5.0752</v>
+        <v>4.7184</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.77</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.2365</v>
+        <v>-0.2568</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.784</v>
+        <v>-4.1088</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.7</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.301</v>
+        <v>-0.3202</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.816</v>
+        <v>-5.1232</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.57</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4225</v>
+        <v>-0.4365</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.76</v>
+        <v>-6.984</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.54</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4505</v>
+        <v>-0.4629</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.208</v>
+        <v>-7.4064</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.69</v>
       </c>
       <c r="I167" t="n">
-        <v>1.3405</v>
+        <v>1.3231</v>
       </c>
       <c r="J167" t="n">
-        <v>21.448</v>
+        <v>21.1696</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.37</v>
       </c>
       <c r="I168" t="n">
-        <v>0.9146</v>
+        <v>0.8661</v>
       </c>
       <c r="J168" t="n">
-        <v>14.6336</v>
+        <v>13.8576</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.36</v>
       </c>
       <c r="I169" t="n">
-        <v>0.894</v>
+        <v>0.8476</v>
       </c>
       <c r="J169" t="n">
-        <v>14.304</v>
+        <v>13.5616</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.3</v>
       </c>
       <c r="I170" t="n">
-        <v>0.7651</v>
+        <v>0.7336</v>
       </c>
       <c r="J170" t="n">
-        <v>12.2416</v>
+        <v>11.7376</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.04</v>
       </c>
       <c r="I171" t="n">
-        <v>0.0833</v>
+        <v>0.1127</v>
       </c>
       <c r="J171" t="n">
-        <v>1.3328</v>
+        <v>1.8032</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.46</v>
       </c>
       <c r="I172" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.8149</v>
       </c>
       <c r="J172" t="n">
-        <v>20.4792</v>
+        <v>19.5576</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.23</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4695</v>
+        <v>0.4667</v>
       </c>
       <c r="J173" t="n">
-        <v>11.268</v>
+        <v>11.2008</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.1</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2304</v>
+        <v>0.241</v>
       </c>
       <c r="J174" t="n">
-        <v>5.5296</v>
+        <v>5.784</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.82</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2278</v>
+        <v>-0.2394</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.4672</v>
+        <v>-5.7456</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.79</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2579</v>
+        <v>-0.2693</v>
       </c>
       <c r="J176" t="n">
-        <v>-6.1896</v>
+        <v>-6.4632</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.74</v>
       </c>
       <c r="I177" t="n">
-        <v>1.5017</v>
+        <v>1.4765</v>
       </c>
       <c r="J177" t="n">
-        <v>36.0408</v>
+        <v>35.436</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.32</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.8341</v>
       </c>
       <c r="J178" t="n">
-        <v>21.5448</v>
+        <v>20.0184</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.98</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1051</v>
+        <v>-0.1073</v>
       </c>
       <c r="J179" t="n">
-        <v>-2.5224</v>
+        <v>-2.5752</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.7</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.8873</v>
+        <v>-0.8186</v>
       </c>
       <c r="J180" t="n">
-        <v>-21.2952</v>
+        <v>-19.6464</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.5</v>
       </c>
       <c r="I181" t="n">
-        <v>-1.3606</v>
+        <v>-1.2247</v>
       </c>
       <c r="J181" t="n">
-        <v>-32.6544</v>
+        <v>-29.3928</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.62</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2938</v>
+        <v>1.2667</v>
       </c>
       <c r="J182" t="n">
-        <v>25.876</v>
+        <v>25.334</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.41</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0219</v>
+        <v>0.9673</v>
       </c>
       <c r="J183" t="n">
-        <v>20.438</v>
+        <v>19.346</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.09</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2745</v>
+        <v>0.2841</v>
       </c>
       <c r="J184" t="n">
-        <v>5.49</v>
+        <v>5.682</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.04</v>
       </c>
       <c r="I185" t="n">
-        <v>0.1197</v>
+        <v>0.1381</v>
       </c>
       <c r="J185" t="n">
-        <v>2.394</v>
+        <v>2.762</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.83</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5962</v>
+        <v>-0.555</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.924</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.13</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3318</v>
+        <v>0.3282</v>
       </c>
       <c r="J187" t="n">
-        <v>6.636</v>
+        <v>6.564</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.95</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0692</v>
+        <v>-0.081</v>
       </c>
       <c r="J188" t="n">
-        <v>-1.384</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.95</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0692</v>
+        <v>-0.081</v>
       </c>
       <c r="J189" t="n">
-        <v>-1.384</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.87</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1578</v>
+        <v>-0.1732</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.156</v>
+        <v>-3.464</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.7</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3267</v>
+        <v>-0.3402</v>
       </c>
       <c r="J191" t="n">
-        <v>-6.534</v>
+        <v>-6.804</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.45</v>
       </c>
       <c r="I192" t="n">
-        <v>1.0877</v>
+        <v>1.0428</v>
       </c>
       <c r="J192" t="n">
-        <v>23.9294</v>
+        <v>22.9416</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.34</v>
       </c>
       <c r="I193" t="n">
-        <v>0.8995</v>
+        <v>0.8433</v>
       </c>
       <c r="J193" t="n">
-        <v>19.789</v>
+        <v>18.5526</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.23</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6408</v>
+        <v>0.6156</v>
       </c>
       <c r="J194" t="n">
-        <v>14.0976</v>
+        <v>13.5432</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2714</v>
+        <v>-0.2599</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.9708</v>
+        <v>-5.7178</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.82</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6122</v>
+        <v>-0.5713</v>
       </c>
       <c r="J196" t="n">
-        <v>-13.4684</v>
+        <v>-12.5686</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.26</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5476</v>
+        <v>0.5339</v>
       </c>
       <c r="J197" t="n">
-        <v>12.0472</v>
+        <v>11.7458</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.22</v>
       </c>
       <c r="I198" t="n">
-        <v>0.4759</v>
+        <v>0.468</v>
       </c>
       <c r="J198" t="n">
-        <v>10.4698</v>
+        <v>10.296</v>
       </c>
     </row>
     <row r="199">
@@ -10349,10 +10349,10 @@
         <v>0.83</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2084</v>
+        <v>-0.222</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.5848</v>
+        <v>-4.884</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.68</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3549</v>
+        <v>-0.3658</v>
       </c>
       <c r="J201" t="n">
-        <v>-7.8078</v>
+        <v>-8.047599999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>2.21</v>
       </c>
       <c r="I202" t="n">
-        <v>1.1667</v>
+        <v>1.1746</v>
       </c>
       <c r="J202" t="n">
-        <v>22.1673</v>
+        <v>22.3174</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.69</v>
       </c>
       <c r="I203" t="n">
-        <v>0.7804</v>
+        <v>0.7774</v>
       </c>
       <c r="J203" t="n">
-        <v>14.8276</v>
+        <v>14.7706</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.36</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4439</v>
+        <v>0.4608</v>
       </c>
       <c r="J204" t="n">
-        <v>8.434100000000001</v>
+        <v>8.7552</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.11</v>
       </c>
       <c r="I205" t="n">
-        <v>0.14</v>
+        <v>0.1644</v>
       </c>
       <c r="J205" t="n">
-        <v>2.66</v>
+        <v>3.1236</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.78</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2975</v>
+        <v>-0.3025</v>
       </c>
       <c r="J206" t="n">
-        <v>-5.6525</v>
+        <v>-5.7475</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.26</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5246</v>
+        <v>0.4982</v>
       </c>
       <c r="J207" t="n">
-        <v>9.9674</v>
+        <v>9.4658</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.65</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.35</v>
+        <v>-0.3671</v>
       </c>
       <c r="J208" t="n">
-        <v>-6.65</v>
+        <v>-6.9749</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.64</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.3594</v>
+        <v>-0.3761</v>
       </c>
       <c r="J209" t="n">
-        <v>-6.8286</v>
+        <v>-7.1459</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.6</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3969</v>
+        <v>-0.4118</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.5411</v>
+        <v>-7.8242</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.59</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4063</v>
+        <v>-0.4207</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.7197</v>
+        <v>-7.9933</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.15</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3796</v>
+        <v>0.3715</v>
       </c>
       <c r="J212" t="n">
-        <v>7.9716</v>
+        <v>7.8015</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.13</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3394</v>
+        <v>0.3339</v>
       </c>
       <c r="J213" t="n">
-        <v>7.1274</v>
+        <v>7.0119</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.83</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1967</v>
+        <v>-0.213</v>
       </c>
       <c r="J214" t="n">
-        <v>-4.1307</v>
+        <v>-4.473</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.77</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2565</v>
+        <v>-0.2722</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.3865</v>
+        <v>-5.7162</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.62</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3994</v>
+        <v>-0.4106</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.3874</v>
+        <v>-8.6226</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.54</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1821</v>
+        <v>1.1498</v>
       </c>
       <c r="J217" t="n">
-        <v>24.8241</v>
+        <v>24.1458</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.46</v>
       </c>
       <c r="I218" t="n">
-        <v>1.0809</v>
+        <v>1.0392</v>
       </c>
       <c r="J218" t="n">
-        <v>22.6989</v>
+        <v>21.8232</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.22</v>
       </c>
       <c r="I219" t="n">
-        <v>0.6012</v>
+        <v>0.5836</v>
       </c>
       <c r="J219" t="n">
-        <v>12.6252</v>
+        <v>12.2556</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.2</v>
       </c>
       <c r="I220" t="n">
-        <v>0.5535</v>
+        <v>0.5407</v>
       </c>
       <c r="J220" t="n">
-        <v>11.6235</v>
+        <v>11.3547</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.79</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7105</v>
+        <v>-0.655</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.9205</v>
+        <v>-13.755</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.12</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3347</v>
+        <v>0.3262</v>
       </c>
       <c r="J222" t="n">
-        <v>6.3593</v>
+        <v>6.1978</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.91</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.1095</v>
+        <v>-0.1251</v>
       </c>
       <c r="J223" t="n">
-        <v>-2.0805</v>
+        <v>-2.3769</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.9</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1207</v>
+        <v>-0.1366</v>
       </c>
       <c r="J224" t="n">
-        <v>-2.2933</v>
+        <v>-2.5954</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.72</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3</v>
+        <v>-0.3157</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.7</v>
+        <v>-5.9983</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.66</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3571</v>
+        <v>-0.3709</v>
       </c>
       <c r="J226" t="n">
-        <v>-6.7849</v>
+        <v>-7.0471</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.73</v>
       </c>
       <c r="I227" t="n">
-        <v>1.397</v>
+        <v>1.3814</v>
       </c>
       <c r="J227" t="n">
-        <v>26.543</v>
+        <v>26.2466</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.61</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2525</v>
+        <v>1.228</v>
       </c>
       <c r="J228" t="n">
-        <v>23.7975</v>
+        <v>23.332</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.22</v>
       </c>
       <c r="I229" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.574</v>
       </c>
       <c r="J229" t="n">
-        <v>11.1568</v>
+        <v>10.906</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.05</v>
       </c>
       <c r="I230" t="n">
-        <v>0.125</v>
+        <v>0.1504</v>
       </c>
       <c r="J230" t="n">
-        <v>2.375</v>
+        <v>2.8576</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.96</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2443</v>
+        <v>-0.2245</v>
       </c>
       <c r="J231" t="n">
-        <v>-4.6417</v>
+        <v>-4.2655</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.41</v>
       </c>
       <c r="I232" t="n">
-        <v>0.8186</v>
+        <v>0.7766</v>
       </c>
       <c r="J232" t="n">
-        <v>18.0092</v>
+        <v>17.0852</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.96</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.0606</v>
+        <v>-0.0706</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.3332</v>
+        <v>-1.5532</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.92</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1085</v>
+        <v>-0.1212</v>
       </c>
       <c r="J234" t="n">
-        <v>-2.387</v>
+        <v>-2.6664</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1198</v>
+        <v>-0.1329</v>
       </c>
       <c r="J235" t="n">
-        <v>-2.6356</v>
+        <v>-2.9238</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.65</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3798</v>
+        <v>-0.3904</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.355600000000001</v>
+        <v>-8.588800000000001</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.43</v>
       </c>
       <c r="I237" t="n">
-        <v>1.0735</v>
+        <v>1.0236</v>
       </c>
       <c r="J237" t="n">
-        <v>23.617</v>
+        <v>22.5192</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.21</v>
       </c>
       <c r="I238" t="n">
-        <v>0.605</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="J238" t="n">
-        <v>13.31</v>
+        <v>12.7842</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.11</v>
       </c>
       <c r="I239" t="n">
-        <v>0.3485</v>
+        <v>0.3483</v>
       </c>
       <c r="J239" t="n">
-        <v>7.667</v>
+        <v>7.6626</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.98</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1214</v>
+        <v>-0.1186</v>
       </c>
       <c r="J240" t="n">
-        <v>-2.6708</v>
+        <v>-2.6092</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.82</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6002</v>
+        <v>-0.5628</v>
       </c>
       <c r="J241" t="n">
-        <v>-13.2044</v>
+        <v>-12.3816</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.36</v>
       </c>
       <c r="I242" t="n">
-        <v>0.758</v>
+        <v>0.7185</v>
       </c>
       <c r="J242" t="n">
-        <v>18.192</v>
+        <v>17.244</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.07</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2053</v>
+        <v>0.2074</v>
       </c>
       <c r="J243" t="n">
-        <v>4.9272</v>
+        <v>4.9776</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.82</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2093</v>
+        <v>-0.2249</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.0232</v>
+        <v>-5.3976</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.71</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3172</v>
+        <v>-0.3309</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.6128</v>
+        <v>-7.9416</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.64</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3833</v>
+        <v>-0.3947</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.199199999999999</v>
+        <v>-9.472799999999999</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.34</v>
       </c>
       <c r="I247" t="n">
-        <v>0.9121</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="J247" t="n">
-        <v>21.8904</v>
+        <v>20.4552</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.22</v>
       </c>
       <c r="I248" t="n">
-        <v>0.626</v>
+        <v>0.6005</v>
       </c>
       <c r="J248" t="n">
-        <v>15.024</v>
+        <v>14.412</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.1</v>
       </c>
       <c r="I249" t="n">
-        <v>0.3197</v>
+        <v>0.322</v>
       </c>
       <c r="J249" t="n">
-        <v>7.6728</v>
+        <v>7.728</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.02</v>
       </c>
       <c r="I250" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0814</v>
       </c>
       <c r="J250" t="n">
-        <v>1.6104</v>
+        <v>1.9536</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.93</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2936</v>
+        <v>-0.2829</v>
       </c>
       <c r="J251" t="n">
-        <v>-7.0464</v>
+        <v>-6.7896</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.08</v>
       </c>
       <c r="I252" t="n">
-        <v>0.4077</v>
+        <v>0.3569</v>
       </c>
       <c r="J252" t="n">
-        <v>5.3001</v>
+        <v>4.6397</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.47</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.4777</v>
+        <v>-0.4943</v>
       </c>
       <c r="J253" t="n">
-        <v>-6.2101</v>
+        <v>-6.4259</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.47</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.4777</v>
+        <v>-0.4943</v>
       </c>
       <c r="J254" t="n">
-        <v>-6.2101</v>
+        <v>-6.4259</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.35</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.5936</v>
+        <v>-0.6011</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.7168</v>
+        <v>-7.8143</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.25</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6931</v>
+        <v>-0.6916</v>
       </c>
       <c r="J256" t="n">
-        <v>-9.010300000000001</v>
+        <v>-8.9908</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>2.4</v>
       </c>
       <c r="I257" t="n">
-        <v>1.2204</v>
+        <v>1.2427</v>
       </c>
       <c r="J257" t="n">
-        <v>15.8652</v>
+        <v>16.1551</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>2.12</v>
       </c>
       <c r="I258" t="n">
-        <v>1.0763</v>
+        <v>1.079</v>
       </c>
       <c r="J258" t="n">
-        <v>13.9919</v>
+        <v>14.027</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.89</v>
       </c>
       <c r="I259" t="n">
-        <v>0.9241</v>
+        <v>0.918</v>
       </c>
       <c r="J259" t="n">
-        <v>12.0133</v>
+        <v>11.934</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.83</v>
       </c>
       <c r="I260" t="n">
-        <v>0.8721</v>
+        <v>0.8693</v>
       </c>
       <c r="J260" t="n">
-        <v>11.3373</v>
+        <v>11.3009</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.91</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.188</v>
+        <v>-0.1864</v>
       </c>
       <c r="J261" t="n">
-        <v>-2.444</v>
+        <v>-2.4232</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>2.39</v>
       </c>
       <c r="I262" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J262" t="n">
-        <v>34.8422</v>
+        <v>36.8068</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.38</v>
       </c>
       <c r="I263" t="n">
-        <v>0.9438</v>
+        <v>0.8914</v>
       </c>
       <c r="J263" t="n">
-        <v>17.9322</v>
+        <v>16.9366</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.96</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2416</v>
+        <v>-0.2226</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.5904</v>
+        <v>-4.2294</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3071</v>
+        <v>-0.2849</v>
       </c>
       <c r="J265" t="n">
-        <v>-5.8349</v>
+        <v>-5.4131</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.84</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5934</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="J266" t="n">
-        <v>-11.2746</v>
+        <v>-10.4101</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.41</v>
       </c>
       <c r="I267" t="n">
-        <v>0.8675</v>
+        <v>0.8129</v>
       </c>
       <c r="J267" t="n">
-        <v>16.4825</v>
+        <v>15.4451</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.99</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.0072</v>
+        <v>-0.015</v>
       </c>
       <c r="J268" t="n">
-        <v>-0.1368</v>
+        <v>-0.285</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.8</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2246</v>
+        <v>-0.2412</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.2674</v>
+        <v>-4.5828</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.68</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3408</v>
+        <v>-0.3547</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.4752</v>
+        <v>-6.7393</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.53</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4801</v>
+        <v>-0.4877</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.1219</v>
+        <v>-9.266299999999999</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2</v>
       </c>
       <c r="I272" t="n">
-        <v>1.7257</v>
+        <v>1.7239</v>
       </c>
       <c r="J272" t="n">
-        <v>32.7883</v>
+        <v>32.7541</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.2</v>
       </c>
       <c r="I273" t="n">
-        <v>0.5462</v>
+        <v>0.5357</v>
       </c>
       <c r="J273" t="n">
-        <v>10.3778</v>
+        <v>10.1783</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.16</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4459</v>
+        <v>0.4453</v>
       </c>
       <c r="J274" t="n">
-        <v>8.472099999999999</v>
+        <v>8.460699999999999</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.1</v>
       </c>
       <c r="I275" t="n">
-        <v>0.2842</v>
+        <v>0.2975</v>
       </c>
       <c r="J275" t="n">
-        <v>5.3998</v>
+        <v>5.6525</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.93</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3328</v>
+        <v>-0.3104</v>
       </c>
       <c r="J276" t="n">
-        <v>-6.3232</v>
+        <v>-5.8976</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.44</v>
       </c>
       <c r="I277" t="n">
-        <v>0.8763</v>
+        <v>0.827</v>
       </c>
       <c r="J277" t="n">
-        <v>16.6497</v>
+        <v>15.713</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.26</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5638</v>
+        <v>0.5458</v>
       </c>
       <c r="J278" t="n">
-        <v>10.7122</v>
+        <v>10.3702</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0839</v>
+        <v>-0.0958</v>
       </c>
       <c r="J279" t="n">
-        <v>-1.5941</v>
+        <v>-1.8202</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.74</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2928</v>
+        <v>-0.3063</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.5632</v>
+        <v>-5.8197</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.4</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.604</v>
+        <v>-0.6031</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.476</v>
+        <v>-11.4589</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.31</v>
       </c>
       <c r="I282" t="n">
-        <v>0.8218</v>
+        <v>0.7768</v>
       </c>
       <c r="J282" t="n">
-        <v>23.8322</v>
+        <v>22.5272</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.29</v>
       </c>
       <c r="I283" t="n">
-        <v>0.7755</v>
+        <v>0.7361</v>
       </c>
       <c r="J283" t="n">
-        <v>22.4895</v>
+        <v>21.3469</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.15</v>
       </c>
       <c r="I284" t="n">
-        <v>0.4407</v>
+        <v>0.436</v>
       </c>
       <c r="J284" t="n">
-        <v>12.7803</v>
+        <v>12.644</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.11</v>
       </c>
       <c r="I285" t="n">
-        <v>0.3345</v>
+        <v>0.3388</v>
       </c>
       <c r="J285" t="n">
-        <v>9.7005</v>
+        <v>9.825200000000001</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.05</v>
       </c>
       <c r="I286" t="n">
-        <v>0.1567</v>
+        <v>0.1726</v>
       </c>
       <c r="J286" t="n">
-        <v>4.5443</v>
+        <v>5.0054</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.14</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3797</v>
+        <v>0.3676</v>
       </c>
       <c r="J287" t="n">
-        <v>11.0113</v>
+        <v>10.6604</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.87</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1519</v>
+        <v>-0.1687</v>
       </c>
       <c r="J288" t="n">
-        <v>-4.4051</v>
+        <v>-4.8923</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.85</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1718</v>
+        <v>-0.189</v>
       </c>
       <c r="J289" t="n">
-        <v>-4.9822</v>
+        <v>-5.481</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2113</v>
+        <v>-0.2288</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.1277</v>
+        <v>-6.6352</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.6</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4122</v>
+        <v>-0.4238</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.9538</v>
+        <v>-12.2902</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.62</v>
       </c>
       <c r="I292" t="n">
-        <v>1.3364</v>
+        <v>1.3045</v>
       </c>
       <c r="J292" t="n">
-        <v>32.0736</v>
+        <v>31.308</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.46</v>
       </c>
       <c r="I293" t="n">
-        <v>1.1253</v>
+        <v>1.08</v>
       </c>
       <c r="J293" t="n">
-        <v>27.0072</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.02</v>
       </c>
       <c r="I294" t="n">
-        <v>0.0795</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="J294" t="n">
-        <v>1.908</v>
+        <v>2.1576</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.9182</v>
+        <v>-0.8444</v>
       </c>
       <c r="J295" t="n">
-        <v>-22.0368</v>
+        <v>-20.2656</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.57</v>
       </c>
       <c r="I296" t="n">
-        <v>-1.204</v>
+        <v>-1.0906</v>
       </c>
       <c r="J296" t="n">
-        <v>-28.896</v>
+        <v>-26.1744</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.5</v>
       </c>
       <c r="I297" t="n">
-        <v>0.9167</v>
+        <v>0.8719</v>
       </c>
       <c r="J297" t="n">
-        <v>22.0008</v>
+        <v>20.9256</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.31</v>
       </c>
       <c r="I298" t="n">
-        <v>0.6069</v>
+        <v>0.5928</v>
       </c>
       <c r="J298" t="n">
-        <v>14.5656</v>
+        <v>14.2272</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.03</v>
       </c>
       <c r="I299" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0921</v>
       </c>
       <c r="J299" t="n">
-        <v>1.9368</v>
+        <v>2.2104</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2379</v>
+        <v>-0.2494</v>
       </c>
       <c r="J300" t="n">
-        <v>-5.7096</v>
+        <v>-5.9856</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.75</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.297</v>
+        <v>-0.3078</v>
       </c>
       <c r="J301" t="n">
-        <v>-7.128</v>
+        <v>-7.3872</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.22</v>
       </c>
       <c r="I302" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.4868</v>
       </c>
       <c r="J302" t="n">
-        <v>9.528499999999999</v>
+        <v>9.2492</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.16</v>
       </c>
       <c r="I303" t="n">
-        <v>0.3874</v>
+        <v>0.3812</v>
       </c>
       <c r="J303" t="n">
-        <v>7.3606</v>
+        <v>7.2428</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.93</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.1067</v>
       </c>
       <c r="J304" t="n">
-        <v>-1.7803</v>
+        <v>-2.0273</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.87</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1589</v>
+        <v>-0.174</v>
       </c>
       <c r="J305" t="n">
-        <v>-3.0191</v>
+        <v>-3.306</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.47</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5395</v>
+        <v>-0.543</v>
       </c>
       <c r="J306" t="n">
-        <v>-10.2505</v>
+        <v>-10.317</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>2.1</v>
       </c>
       <c r="I307" t="n">
-        <v>1.8338</v>
+        <v>1.8414</v>
       </c>
       <c r="J307" t="n">
-        <v>34.8422</v>
+        <v>34.9866</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.73</v>
       </c>
       <c r="I308" t="n">
-        <v>1.4042</v>
+        <v>1.3878</v>
       </c>
       <c r="J308" t="n">
-        <v>26.6798</v>
+        <v>26.3682</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.95</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2713</v>
+        <v>-0.2519</v>
       </c>
       <c r="J309" t="n">
-        <v>-5.1547</v>
+        <v>-4.7861</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.87</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.4719</v>
       </c>
       <c r="J310" t="n">
-        <v>-9.663399999999999</v>
+        <v>-8.966100000000001</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.78</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.7454</v>
+        <v>-0.6843</v>
       </c>
       <c r="J311" t="n">
-        <v>-14.1626</v>
+        <v>-13.0017</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.7</v>
       </c>
       <c r="I312" t="n">
-        <v>1.2009</v>
+        <v>1.1711</v>
       </c>
       <c r="J312" t="n">
-        <v>22.8171</v>
+        <v>22.2509</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.03</v>
       </c>
       <c r="I313" t="n">
-        <v>0.1152</v>
+        <v>0.1169</v>
       </c>
       <c r="J313" t="n">
-        <v>2.1888</v>
+        <v>2.2211</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.3342</v>
+        <v>-0.3478</v>
       </c>
       <c r="J314" t="n">
-        <v>-6.3498</v>
+        <v>-6.6082</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.63</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3906</v>
+        <v>-0.4021</v>
       </c>
       <c r="J315" t="n">
-        <v>-7.4214</v>
+        <v>-7.6399</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.47</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5369</v>
+        <v>-0.5409</v>
       </c>
       <c r="J316" t="n">
-        <v>-10.2011</v>
+        <v>-10.2771</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>2.22</v>
       </c>
       <c r="I317" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J317" t="n">
-        <v>34.8422</v>
+        <v>36.8068</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.3</v>
       </c>
       <c r="I318" t="n">
-        <v>0.7689</v>
+        <v>0.7362</v>
       </c>
       <c r="J318" t="n">
-        <v>14.6091</v>
+        <v>13.9878</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.25</v>
       </c>
       <c r="I319" t="n">
-        <v>0.6551</v>
+        <v>0.6352</v>
       </c>
       <c r="J319" t="n">
-        <v>12.4469</v>
+        <v>12.0688</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.07</v>
       </c>
       <c r="I320" t="n">
-        <v>0.1841</v>
+        <v>0.2072</v>
       </c>
       <c r="J320" t="n">
-        <v>3.4979</v>
+        <v>3.9368</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.6226</v>
       </c>
       <c r="J321" t="n">
-        <v>-12.8801</v>
+        <v>-11.8294</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7557/event_7557_evp_summary.xlsx
+++ b/database/event/7557/event_7557_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.190200000000001</v>
+        <v>8.402200000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7211</v>
+        <v>3.8174</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1041</v>
+        <v>3.1393</v>
       </c>
       <c r="E2" t="n">
-        <v>8.190200000000001</v>
+        <v>8.402200000000001</v>
       </c>
       <c r="F2" t="n">
         <v>2.9277</v>
@@ -538,93 +538,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.2544</v>
+        <v>6.4664</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8416</v>
+        <v>2.9379</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2229</v>
+        <v>2.2746</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2544</v>
+        <v>6.4664</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0542</v>
+        <v>2.4626</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2002</v>
+        <v>3.6714</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9598</v>
+        <v>2.6649</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9598</v>
+        <v>2.6649</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2002</v>
+        <v>3.6714</v>
       </c>
       <c r="K3" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="L3" t="n">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="M3" t="n">
-        <v>7.16</v>
+        <v>6.3363</v>
       </c>
       <c r="N3" t="n">
-        <v>211</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.134</v>
+        <v>6.447</v>
       </c>
       <c r="C4" t="n">
-        <v>2.7869</v>
+        <v>2.9291</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1681</v>
+        <v>2.2659</v>
       </c>
       <c r="E4" t="n">
-        <v>6.134</v>
+        <v>6.447</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4626</v>
+        <v>3.0542</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6714</v>
+        <v>3.2002</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6649</v>
+        <v>3.9598</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6649</v>
+        <v>3.9598</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6714</v>
+        <v>3.2002</v>
       </c>
       <c r="K4" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="L4" t="n">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="M4" t="n">
-        <v>6.3363</v>
+        <v>7.16</v>
       </c>
       <c r="N4" t="n">
-        <v>267</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5">
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.4205</v>
+        <v>5.5485</v>
       </c>
       <c r="C5" t="n">
-        <v>2.4627</v>
+        <v>2.5209</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8433</v>
+        <v>1.8646</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4205</v>
+        <v>5.5485</v>
       </c>
       <c r="F5" t="n">
         <v>2.9951</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4157</v>
+        <v>4.5056</v>
       </c>
       <c r="C6" t="n">
-        <v>2.0062</v>
+        <v>2.0471</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3859</v>
+        <v>1.3987</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4157</v>
+        <v>4.5056</v>
       </c>
       <c r="F6" t="n">
         <v>2.624</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.9007</v>
+        <v>4.1036</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7722</v>
+        <v>1.8644</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1515</v>
+        <v>1.2192</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9007</v>
+        <v>4.1036</v>
       </c>
       <c r="F7" t="n">
         <v>2.7689</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6665</v>
+        <v>3.8462</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6658</v>
+        <v>1.7475</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0449</v>
+        <v>1.1042</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6665</v>
+        <v>3.8462</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5033</v>
+        <v>3.4351</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1632</v>
+        <v>0.1083</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5033</v>
+        <v>6.4395</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5033</v>
+        <v>3.4773</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1632</v>
+        <v>0.1083</v>
       </c>
       <c r="K8" t="n">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="L8" t="n">
-        <v>169</v>
+        <v>52</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6665</v>
+        <v>3.5856</v>
       </c>
       <c r="N8" t="n">
-        <v>267</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5434</v>
+        <v>3.8047</v>
       </c>
       <c r="C9" t="n">
-        <v>1.6099</v>
+        <v>1.7286</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9888</v>
+        <v>1.0857</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5434</v>
+        <v>3.8047</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4351</v>
+        <v>1.5033</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1083</v>
+        <v>2.1632</v>
       </c>
       <c r="H9" t="n">
-        <v>6.4395</v>
+        <v>1.5033</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4773</v>
+        <v>1.5033</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1083</v>
+        <v>2.1632</v>
       </c>
       <c r="K9" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="L9" t="n">
-        <v>52</v>
+        <v>169</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5856</v>
+        <v>3.6665</v>
       </c>
       <c r="N9" t="n">
-        <v>132</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2908</v>
+        <v>3.4304</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4951</v>
+        <v>1.5586</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8738</v>
+        <v>0.9185</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2908</v>
+        <v>3.4304</v>
       </c>
       <c r="F10" t="n">
         <v>3.0921</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8662</v>
+        <v>3.1197</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3022</v>
+        <v>1.4174</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6805</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8662</v>
+        <v>3.1197</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9928</v>
+        <v>2.8097</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8734</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9928</v>
+        <v>3.4246</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5361</v>
+        <v>3.4246</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8734</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L11" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.4095</v>
+        <v>3.4246</v>
       </c>
       <c r="N11" t="n">
-        <v>225</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8097</v>
+        <v>2.9538</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2765</v>
+        <v>1.342</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6548</v>
+        <v>0.7056</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8097</v>
+        <v>2.9538</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8097</v>
+        <v>2.5893</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4246</v>
+        <v>2.9422</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4246</v>
+        <v>2.9422</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4246</v>
+        <v>2.9422</v>
       </c>
       <c r="N12" t="n">
-        <v>97</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13">
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7834</v>
+        <v>2.7894</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2646</v>
+        <v>1.2673</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6429</v>
+        <v>0.6321</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7834</v>
+        <v>2.7894</v>
       </c>
       <c r="F13" t="n">
         <v>1.6964</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5893</v>
+        <v>2.7574</v>
       </c>
       <c r="C14" t="n">
-        <v>1.1764</v>
+        <v>1.2528</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5545</v>
+        <v>0.6179</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5893</v>
+        <v>2.7574</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5893</v>
+        <v>0.9928</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1.8734</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9422</v>
+        <v>0.9928</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9422</v>
+        <v>0.5361</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.8734</v>
       </c>
       <c r="K14" t="n">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9422</v>
+        <v>2.4095</v>
       </c>
       <c r="N14" t="n">
-        <v>114</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4535</v>
+        <v>2.6416</v>
       </c>
       <c r="C15" t="n">
-        <v>1.1147</v>
+        <v>1.2002</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4927</v>
+        <v>0.5661</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4535</v>
+        <v>2.6416</v>
       </c>
       <c r="F15" t="n">
         <v>2.5169</v>
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1752</v>
+        <v>2.2357</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9883</v>
+        <v>1.0158</v>
       </c>
       <c r="D16" t="n">
-        <v>0.366</v>
+        <v>0.3848</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1752</v>
+        <v>2.2357</v>
       </c>
       <c r="F16" t="n">
         <v>-0.3989</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0153</v>
+        <v>2.1666</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9156</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2932</v>
+        <v>0.354</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0153</v>
+        <v>2.1666</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0153</v>
+        <v>2.0505</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.1193</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0153</v>
+        <v>2.0505</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0153</v>
+        <v>2.0505</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.1193</v>
       </c>
       <c r="K17" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0153</v>
+        <v>1.9312</v>
       </c>
       <c r="N17" t="n">
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9312</v>
+        <v>2.1203</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8774</v>
+        <v>0.9633</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2549</v>
+        <v>0.3333</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9312</v>
+        <v>2.1203</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0505</v>
+        <v>2.0153</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1193</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0505</v>
+        <v>2.0153</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0505</v>
+        <v>2.0153</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1193</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="L18" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9312</v>
+        <v>2.0153</v>
       </c>
       <c r="N18" t="n">
-        <v>133</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19">
@@ -1278,16 +1278,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.805</v>
+        <v>1.8819</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.855</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1975</v>
+        <v>0.2268</v>
       </c>
       <c r="E19" t="n">
-        <v>1.805</v>
+        <v>1.8819</v>
       </c>
       <c r="F19" t="n">
         <v>1.3586</v>
@@ -1324,16 +1324,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5092</v>
+        <v>1.5404</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6857</v>
+        <v>0.6999</v>
       </c>
       <c r="D20" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0742</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5092</v>
+        <v>1.5404</v>
       </c>
       <c r="F20" t="n">
         <v>1.5092</v>
@@ -1366,47 +1366,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1907</v>
+        <v>1.2729</v>
       </c>
       <c r="C21" t="n">
-        <v>0.541</v>
+        <v>0.5783</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0822</v>
+        <v>-0.0452</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1907</v>
+        <v>1.2729</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3261</v>
+        <v>1.1741</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1354</v>
+        <v>-0.0108</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3261</v>
+        <v>1.1741</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7161</v>
+        <v>1.1741</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1354</v>
+        <v>-0.0108</v>
       </c>
       <c r="K21" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="L21" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5807</v>
+        <v>1.1633</v>
       </c>
       <c r="N21" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22">
@@ -1416,16 +1416,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1763</v>
+        <v>1.1811</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5344</v>
+        <v>0.5366</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0887</v>
+        <v>-0.0862</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1763</v>
+        <v>1.1811</v>
       </c>
       <c r="F22" t="n">
         <v>1.3583</v>
@@ -1458,219 +1458,219 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1636</v>
+        <v>1.1241</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.5107</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0945</v>
+        <v>-0.1117</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1636</v>
+        <v>1.1241</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4</v>
+        <v>0.6879</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.3874</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4</v>
+        <v>0.6879</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>0.6879</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.3874</v>
       </c>
       <c r="K23" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L23" t="n">
-        <v>169</v>
+        <v>38</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1636</v>
+        <v>1.0753</v>
       </c>
       <c r="N23" t="n">
-        <v>267</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1633</v>
+        <v>1.1118</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5285</v>
+        <v>0.5051</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0946</v>
+        <v>-0.1172</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1633</v>
+        <v>1.1118</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1741</v>
+        <v>1.3261</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0108</v>
+        <v>-0.1354</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1741</v>
+        <v>1.3261</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1741</v>
+        <v>0.7161</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0108</v>
+        <v>-0.1354</v>
       </c>
       <c r="K24" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="L24" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1633</v>
+        <v>0.5807</v>
       </c>
       <c r="N24" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0753</v>
+        <v>1.0186</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4885</v>
+        <v>0.4628</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1347</v>
+        <v>-0.1588</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0753</v>
+        <v>1.0186</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6879</v>
+        <v>0.4</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3874</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6879</v>
+        <v>0.4</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6879</v>
+        <v>0.4</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3874</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L25" t="n">
-        <v>38</v>
+        <v>169</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0753</v>
+        <v>1.1636</v>
       </c>
       <c r="N25" t="n">
-        <v>133</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3481</v>
+        <v>0.346</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1582</v>
+        <v>0.1572</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4657</v>
+        <v>-0.4593</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3481</v>
+        <v>0.346</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1495</v>
+        <v>0.3191</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4976</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1495</v>
+        <v>0.3191</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1495</v>
+        <v>0.3191</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4976</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L26" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3481</v>
+        <v>0.3191</v>
       </c>
       <c r="N26" t="n">
-        <v>267</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3447</v>
+        <v>0.2817</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1566</v>
+        <v>0.128</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4673</v>
+        <v>-0.488</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3447</v>
+        <v>0.2817</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4504</v>
+        <v>-0.1495</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7951</v>
+        <v>0.4976</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.4504</v>
+        <v>-0.1495</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.4504</v>
+        <v>-0.1495</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7951</v>
+        <v>0.4976</v>
       </c>
       <c r="K27" t="n">
         <v>98</v>
@@ -1679,7 +1679,7 @@
         <v>169</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3447</v>
+        <v>0.3481</v>
       </c>
       <c r="N27" t="n">
         <v>267</v>
@@ -1688,139 +1688,139 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3191</v>
+        <v>0.1772</v>
       </c>
       <c r="C28" t="n">
-        <v>0.145</v>
+        <v>0.0805</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4789</v>
+        <v>-0.5347</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3191</v>
+        <v>0.1772</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3191</v>
+        <v>-0.4504</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.7951</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3191</v>
+        <v>-0.4504</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3191</v>
+        <v>-0.4504</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.7951</v>
       </c>
       <c r="K28" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3191</v>
+        <v>0.3447</v>
       </c>
       <c r="N28" t="n">
-        <v>97</v>
+        <v>267</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1491</v>
+        <v>0.0347</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0677</v>
+        <v>0.0158</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5563</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1491</v>
+        <v>0.0347</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1941</v>
+        <v>0.1311</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3432</v>
+        <v>-0.039</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1941</v>
+        <v>0.1311</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1941</v>
+        <v>0.1311</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3432</v>
+        <v>-0.039</v>
       </c>
       <c r="K29" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L29" t="n">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1491</v>
+        <v>0.09209999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>211</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0921</v>
+        <v>0.0288</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0418</v>
+        <v>0.0131</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5823</v>
+        <v>-0.601</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0921</v>
+        <v>0.0288</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1311</v>
+        <v>-0.1941</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.039</v>
+        <v>0.3432</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1311</v>
+        <v>-0.1941</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1311</v>
+        <v>-0.1941</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.039</v>
+        <v>0.3432</v>
       </c>
       <c r="K30" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L30" t="n">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="M30" t="n">
-        <v>0.09209999999999999</v>
+        <v>0.1491</v>
       </c>
       <c r="N30" t="n">
-        <v>171</v>
+        <v>211</v>
       </c>
     </row>
     <row r="31">
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.19</v>
+        <v>-0.2794</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0863</v>
+        <v>-0.1269</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7107</v>
+        <v>-0.7386</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.19</v>
+        <v>-0.2794</v>
       </c>
       <c r="F31" t="n">
         <v>-0.19</v>
@@ -1872,124 +1872,124 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5374</v>
+        <v>-0.6853</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2442</v>
+        <v>-0.3114</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8688</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5374</v>
+        <v>-0.6853</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2556</v>
+        <v>-0.5848</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.793</v>
+        <v>0.0063</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2556</v>
+        <v>-0.5848</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2556</v>
+        <v>-0.5848</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.793</v>
+        <v>0.0063</v>
       </c>
       <c r="K32" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="L32" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5374000000000001</v>
+        <v>-0.5785</v>
       </c>
       <c r="N32" t="n">
-        <v>133</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5785</v>
+        <v>-0.8537</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2628</v>
+        <v>-0.3879</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8875</v>
+        <v>-0.9951</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5785</v>
+        <v>-0.8537</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5848</v>
+        <v>0.2556</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0063</v>
+        <v>-0.793</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5848</v>
+        <v>0.2556</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5848</v>
+        <v>0.2556</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0063</v>
+        <v>-0.793</v>
       </c>
       <c r="K33" t="n">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="L33" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5785</v>
+        <v>-0.5374000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>171</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6973</v>
+        <v>-0.9764</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3168</v>
+        <v>-0.4436</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9416</v>
+        <v>-1.05</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6973</v>
+        <v>-0.9764</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6973</v>
+        <v>-0.7032</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6973</v>
+        <v>-0.7032</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6973</v>
+        <v>-0.7032</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6973</v>
+        <v>-0.7032</v>
       </c>
       <c r="N34" t="n">
         <v>97</v>
@@ -2010,32 +2010,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7032</v>
+        <v>-0.9806</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3195</v>
+        <v>-0.4455</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9443</v>
+        <v>-1.0518</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7032</v>
+        <v>-0.9806</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7032</v>
+        <v>-0.8395</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7032</v>
+        <v>-0.8395</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7032</v>
+        <v>-0.8395</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7032</v>
+        <v>-0.8395</v>
       </c>
       <c r="N35" t="n">
         <v>97</v>
@@ -2056,32 +2056,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8395</v>
+        <v>-1.0367</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3814</v>
+        <v>-0.471</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0064</v>
+        <v>-1.0769</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8395</v>
+        <v>-1.0367</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8395</v>
+        <v>-0.6973</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8395</v>
+        <v>-0.6973</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8395</v>
+        <v>-0.6973</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8395</v>
+        <v>-0.6973</v>
       </c>
       <c r="N36" t="n">
         <v>97</v>
@@ -2106,16 +2106,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.386</v>
+        <v>-1.5767</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.6297</v>
+        <v>-0.7163</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2551</v>
+        <v>-1.3181</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.386</v>
+        <v>-1.5767</v>
       </c>
       <c r="F37" t="n">
         <v>-1.386</v>
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.9749</v>
+        <v>-2.3287</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.8973</v>
+        <v>-1.058</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.5232</v>
+        <v>-1.654</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.9749</v>
+        <v>-2.3287</v>
       </c>
       <c r="F38" t="n">
         <v>-1.1014</v>
@@ -2198,16 +2198,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.1012</v>
+        <v>-2.3353</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.9546</v>
+        <v>-1.061</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.5807</v>
+        <v>-1.6569</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.1012</v>
+        <v>-2.3353</v>
       </c>
       <c r="F39" t="n">
         <v>-0.8625</v>
@@ -2244,16 +2244,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.139</v>
+        <v>-2.3409</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.9718</v>
+        <v>-1.0636</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5979</v>
+        <v>-1.6594</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.139</v>
+        <v>-2.3409</v>
       </c>
       <c r="F40" t="n">
         <v>-1.6</v>
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.1401</v>
+        <v>-3.4555</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.4267</v>
+        <v>-1.57</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.0536</v>
+        <v>-2.1573</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.1401</v>
+        <v>-3.4555</v>
       </c>
       <c r="F41" t="n">
         <v>-3.5714</v>

--- a/database/event/7557/event_7557_evp_summary.xlsx
+++ b/database/event/7557/event_7557_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.402200000000001</v>
+        <v>8.444800000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8174</v>
+        <v>3.8368</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1393</v>
+        <v>3.2412</v>
       </c>
       <c r="E2" t="n">
-        <v>8.402200000000001</v>
+        <v>8.444800000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9277</v>
+        <v>2.98</v>
       </c>
       <c r="G2" t="n">
-        <v>5.2624</v>
+        <v>5.2528</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7654</v>
+        <v>4.7456</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5733</v>
+        <v>2.6645</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2624</v>
+        <v>5.2528</v>
       </c>
       <c r="K2" t="n">
         <v>103</v>
@@ -529,7 +529,7 @@
         <v>122</v>
       </c>
       <c r="M2" t="n">
-        <v>7.835700000000001</v>
+        <v>7.917299999999999</v>
       </c>
       <c r="N2" t="n">
         <v>225</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4664</v>
+        <v>6.2951</v>
       </c>
       <c r="C3" t="n">
-        <v>2.9379</v>
+        <v>2.8601</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2746</v>
+        <v>2.2619</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4664</v>
+        <v>6.2951</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4626</v>
+        <v>2.3753</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6714</v>
+        <v>3.5874</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6649</v>
+        <v>2.4933</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6649</v>
+        <v>2.4933</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6714</v>
+        <v>3.5874</v>
       </c>
       <c r="K3" t="n">
         <v>98</v>
@@ -575,7 +575,7 @@
         <v>169</v>
       </c>
       <c r="M3" t="n">
-        <v>6.3363</v>
+        <v>6.0807</v>
       </c>
       <c r="N3" t="n">
         <v>267</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.447</v>
+        <v>6.2579</v>
       </c>
       <c r="C4" t="n">
-        <v>2.9291</v>
+        <v>2.8432</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2659</v>
+        <v>2.245</v>
       </c>
       <c r="E4" t="n">
-        <v>6.447</v>
+        <v>6.2579</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0542</v>
+        <v>3.0123</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2002</v>
+        <v>3.0529</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9598</v>
+        <v>3.9532</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9598</v>
+        <v>3.9532</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2002</v>
+        <v>3.0529</v>
       </c>
       <c r="K4" t="n">
         <v>109</v>
@@ -621,7 +621,7 @@
         <v>102</v>
       </c>
       <c r="M4" t="n">
-        <v>7.16</v>
+        <v>7.0061</v>
       </c>
       <c r="N4" t="n">
         <v>211</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.5485</v>
+        <v>5.554</v>
       </c>
       <c r="C5" t="n">
-        <v>2.5209</v>
+        <v>2.5234</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8646</v>
+        <v>1.9243</v>
       </c>
       <c r="E5" t="n">
-        <v>5.5485</v>
+        <v>5.554</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9951</v>
+        <v>3.0004</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4254</v>
+        <v>2.4256</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9877</v>
+        <v>4.8224</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6933</v>
+        <v>2.7076</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4254</v>
+        <v>2.4256</v>
       </c>
       <c r="K5" t="n">
         <v>103</v>
@@ -667,7 +667,7 @@
         <v>122</v>
       </c>
       <c r="M5" t="n">
-        <v>5.1187</v>
+        <v>5.1332</v>
       </c>
       <c r="N5" t="n">
         <v>225</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5056</v>
+        <v>4.4012</v>
       </c>
       <c r="C6" t="n">
-        <v>2.0471</v>
+        <v>1.9996</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3987</v>
+        <v>1.3992</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5056</v>
+        <v>4.4012</v>
       </c>
       <c r="F6" t="n">
-        <v>2.624</v>
+        <v>2.6198</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7917</v>
+        <v>1.6915</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7634</v>
+        <v>3.3932</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0322</v>
+        <v>1.9052</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7917</v>
+        <v>1.6915</v>
       </c>
       <c r="K6" t="n">
         <v>103</v>
@@ -713,7 +713,7 @@
         <v>122</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8239</v>
+        <v>3.5967</v>
       </c>
       <c r="N6" t="n">
         <v>225</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1036</v>
+        <v>4.0707</v>
       </c>
       <c r="C7" t="n">
-        <v>1.8644</v>
+        <v>1.8495</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2192</v>
+        <v>1.2486</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1036</v>
+        <v>4.0707</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7689</v>
+        <v>2.8285</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1318</v>
+        <v>1.0393</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2415</v>
+        <v>4.1769</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2904</v>
+        <v>2.3452</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1318</v>
+        <v>1.0393</v>
       </c>
       <c r="K7" t="n">
         <v>80</v>
@@ -759,7 +759,7 @@
         <v>52</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4222</v>
+        <v>3.3845</v>
       </c>
       <c r="N7" t="n">
         <v>132</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8462</v>
+        <v>3.7482</v>
       </c>
       <c r="C8" t="n">
-        <v>1.7475</v>
+        <v>1.7029</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1042</v>
+        <v>1.1017</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8462</v>
+        <v>3.7482</v>
       </c>
       <c r="F8" t="n">
-        <v>3.4351</v>
+        <v>1.438</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1083</v>
+        <v>2.172</v>
       </c>
       <c r="H8" t="n">
-        <v>6.4395</v>
+        <v>1.438</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4773</v>
+        <v>1.438</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1083</v>
+        <v>2.172</v>
       </c>
       <c r="K8" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="L8" t="n">
-        <v>52</v>
+        <v>169</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5856</v>
+        <v>3.61</v>
       </c>
       <c r="N8" t="n">
-        <v>132</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.8047</v>
+        <v>3.7338</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7286</v>
+        <v>1.6964</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0857</v>
+        <v>1.0951</v>
       </c>
       <c r="E9" t="n">
-        <v>3.8047</v>
+        <v>3.7338</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5033</v>
+        <v>3.3555</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1632</v>
+        <v>0.0755</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5033</v>
+        <v>6.1553</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5033</v>
+        <v>3.456</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1632</v>
+        <v>0.0755</v>
       </c>
       <c r="K9" t="n">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="L9" t="n">
-        <v>169</v>
+        <v>52</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6665</v>
+        <v>3.5315</v>
       </c>
       <c r="N9" t="n">
-        <v>267</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4304</v>
+        <v>3.4508</v>
       </c>
       <c r="C10" t="n">
-        <v>1.5586</v>
+        <v>1.5678</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9185</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4304</v>
+        <v>3.4508</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0921</v>
+        <v>3.1043</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1987</v>
+        <v>0.2069</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3079</v>
+        <v>5.2122</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8662</v>
+        <v>2.9265</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1987</v>
+        <v>0.2069</v>
       </c>
       <c r="K10" t="n">
         <v>80</v>
@@ -897,7 +897,7 @@
         <v>52</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0649</v>
+        <v>3.1334</v>
       </c>
       <c r="N10" t="n">
         <v>132</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1197</v>
+        <v>3.0006</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4174</v>
+        <v>1.3633</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7611</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1197</v>
+        <v>3.0006</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8097</v>
+        <v>2.6906</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4246</v>
+        <v>3.216</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4246</v>
+        <v>3.216</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4246</v>
+        <v>3.216</v>
       </c>
       <c r="N11" t="n">
         <v>97</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9538</v>
+        <v>2.8143</v>
       </c>
       <c r="C12" t="n">
-        <v>1.342</v>
+        <v>1.2786</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7056</v>
+        <v>0.6763</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9538</v>
+        <v>2.8143</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5893</v>
+        <v>2.4498</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9422</v>
+        <v>2.664</v>
       </c>
       <c r="I12" t="n">
-        <v>2.9422</v>
+        <v>2.664</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9422</v>
+        <v>2.664</v>
       </c>
       <c r="N12" t="n">
         <v>114</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7894</v>
+        <v>2.764</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2673</v>
+        <v>1.2558</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6321</v>
+        <v>0.6533</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7894</v>
+        <v>2.764</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6964</v>
+        <v>1.7361</v>
       </c>
       <c r="G13" t="n">
-        <v>1.087</v>
+        <v>1.0219</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6964</v>
+        <v>1.7361</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6964</v>
+        <v>1.7361</v>
       </c>
       <c r="J13" t="n">
-        <v>1.087</v>
+        <v>1.0219</v>
       </c>
       <c r="K13" t="n">
         <v>109</v>
@@ -1035,7 +1035,7 @@
         <v>102</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7834</v>
+        <v>2.758</v>
       </c>
       <c r="N13" t="n">
         <v>211</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7574</v>
+        <v>2.6983</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2528</v>
+        <v>1.2259</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6179</v>
+        <v>0.6234</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7574</v>
+        <v>2.6983</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9928</v>
+        <v>0.872</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8734</v>
+        <v>1.9351</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9928</v>
+        <v>0.872</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5361</v>
+        <v>0.4896</v>
       </c>
       <c r="J14" t="n">
-        <v>1.8734</v>
+        <v>1.9351</v>
       </c>
       <c r="K14" t="n">
         <v>103</v>
@@ -1081,7 +1081,7 @@
         <v>122</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4095</v>
+        <v>2.4247</v>
       </c>
       <c r="N14" t="n">
         <v>225</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6416</v>
+        <v>2.582</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2002</v>
+        <v>1.1731</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5661</v>
+        <v>0.5704</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6416</v>
+        <v>2.582</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5169</v>
+        <v>2.4552</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0634</v>
+        <v>-0.0613</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7838</v>
+        <v>2.6765</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7838</v>
+        <v>2.6765</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0634</v>
+        <v>-0.0613</v>
       </c>
       <c r="K15" t="n">
         <v>112</v>
@@ -1127,7 +1127,7 @@
         <v>59</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7204</v>
+        <v>2.6152</v>
       </c>
       <c r="N15" t="n">
         <v>171</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2357</v>
+        <v>2.2688</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0158</v>
+        <v>1.0308</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3848</v>
+        <v>0.4278</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2357</v>
+        <v>2.2688</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3989</v>
+        <v>-0.3342</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5741</v>
+        <v>2.5425</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3989</v>
+        <v>-0.3342</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3989</v>
+        <v>-0.3342</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5741</v>
+        <v>2.5425</v>
       </c>
       <c r="K16" t="n">
         <v>109</v>
@@ -1173,7 +1173,7 @@
         <v>102</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1752</v>
+        <v>2.2083</v>
       </c>
       <c r="N16" t="n">
         <v>211</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1666</v>
+        <v>2.0996</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.9539</v>
       </c>
       <c r="D17" t="n">
-        <v>0.354</v>
+        <v>0.3507</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1666</v>
+        <v>2.0996</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0505</v>
+        <v>1.9909</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1193</v>
+        <v>-0.1267</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0505</v>
+        <v>1.9909</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0505</v>
+        <v>1.9909</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1193</v>
+        <v>-0.1267</v>
       </c>
       <c r="K17" t="n">
         <v>95</v>
@@ -1219,7 +1219,7 @@
         <v>38</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9312</v>
+        <v>1.8642</v>
       </c>
       <c r="N17" t="n">
         <v>133</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.1203</v>
+        <v>1.9402</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9633</v>
+        <v>0.8815</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3333</v>
+        <v>0.2781</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1203</v>
+        <v>1.9402</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0153</v>
+        <v>1.8352</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0153</v>
+        <v>1.8352</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0153</v>
+        <v>1.8352</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.0153</v>
+        <v>1.8352</v>
       </c>
       <c r="N18" t="n">
         <v>114</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8819</v>
+        <v>1.9371</v>
       </c>
       <c r="C19" t="n">
-        <v>0.855</v>
+        <v>0.8801</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2268</v>
+        <v>0.2767</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8819</v>
+        <v>1.9371</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3586</v>
+        <v>1.4244</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4464</v>
+        <v>0.4358</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3586</v>
+        <v>1.4244</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3586</v>
+        <v>1.4244</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4464</v>
+        <v>0.4358</v>
       </c>
       <c r="K19" t="n">
         <v>112</v>
@@ -1311,7 +1311,7 @@
         <v>59</v>
       </c>
       <c r="M19" t="n">
-        <v>1.805</v>
+        <v>1.8602</v>
       </c>
       <c r="N19" t="n">
         <v>171</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5404</v>
+        <v>1.4189</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6999</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0742</v>
+        <v>0.0406</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5404</v>
+        <v>1.4189</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5092</v>
+        <v>1.3877</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5092</v>
+        <v>1.3877</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5092</v>
+        <v>1.3877</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5092</v>
+        <v>1.3877</v>
       </c>
       <c r="N20" t="n">
         <v>114</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2729</v>
+        <v>1.2695</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5783</v>
+        <v>0.5768</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0452</v>
+        <v>-0.0275</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2729</v>
+        <v>1.2695</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1741</v>
+        <v>1.2076</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0108</v>
+        <v>-0.0477</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1741</v>
+        <v>1.2076</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1741</v>
+        <v>1.2076</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0108</v>
+        <v>-0.0477</v>
       </c>
       <c r="K21" t="n">
         <v>95</v>
@@ -1403,7 +1403,7 @@
         <v>38</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1633</v>
+        <v>1.1599</v>
       </c>
       <c r="N21" t="n">
         <v>133</v>
@@ -1412,139 +1412,139 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1811</v>
+        <v>1.1082</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5366</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0862</v>
+        <v>-0.1009</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1811</v>
+        <v>1.1082</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3583</v>
+        <v>1.3411</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.182</v>
+        <v>-0.154</v>
       </c>
       <c r="H22" t="n">
-        <v>1.3583</v>
+        <v>1.3411</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3583</v>
+        <v>0.753</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.182</v>
+        <v>-0.154</v>
       </c>
       <c r="K22" t="n">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="L22" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1763</v>
+        <v>0.599</v>
       </c>
       <c r="N22" t="n">
-        <v>171</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1241</v>
+        <v>1.0503</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5107</v>
+        <v>0.4772</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1117</v>
+        <v>-0.1273</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1241</v>
+        <v>1.0503</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6879</v>
+        <v>1.2792</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3874</v>
+        <v>-0.2337</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6879</v>
+        <v>1.2792</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6879</v>
+        <v>1.2792</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3874</v>
+        <v>-0.2337</v>
       </c>
       <c r="K23" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="L23" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0753</v>
+        <v>1.0455</v>
       </c>
       <c r="N23" t="n">
-        <v>133</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1118</v>
+        <v>0.9977</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5051</v>
+        <v>0.4533</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1172</v>
+        <v>-0.1513</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1118</v>
+        <v>0.9977</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3261</v>
+        <v>0.5636</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1354</v>
+        <v>0.3853</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3261</v>
+        <v>0.5636</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7161</v>
+        <v>0.5636</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1354</v>
+        <v>0.3853</v>
       </c>
       <c r="K24" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="L24" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5807</v>
+        <v>0.9489</v>
       </c>
       <c r="N24" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0186</v>
+        <v>0.8182</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4628</v>
+        <v>0.3717</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1588</v>
+        <v>-0.2331</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0186</v>
+        <v>0.8182</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4</v>
+        <v>0.3234</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.6398</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4</v>
+        <v>0.3234</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4</v>
+        <v>0.3234</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.6398</v>
       </c>
       <c r="K25" t="n">
         <v>98</v>
@@ -1587,7 +1587,7 @@
         <v>169</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1636</v>
+        <v>0.9632000000000001</v>
       </c>
       <c r="N25" t="n">
         <v>267</v>
@@ -1596,81 +1596,81 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.346</v>
+        <v>0.2678</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1572</v>
+        <v>0.1217</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4593</v>
+        <v>-0.4838</v>
       </c>
       <c r="E26" t="n">
-        <v>0.346</v>
+        <v>0.2678</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3191</v>
+        <v>-0.1863</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.5205</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3191</v>
+        <v>-0.1863</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3191</v>
+        <v>-0.1863</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.5205</v>
       </c>
       <c r="K26" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3191</v>
+        <v>0.3341999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>97</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2817</v>
+        <v>0.2626</v>
       </c>
       <c r="C27" t="n">
-        <v>0.128</v>
+        <v>0.1193</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.488</v>
+        <v>-0.4862</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2817</v>
+        <v>0.2626</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1495</v>
+        <v>-0.4309</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4976</v>
+        <v>0.861</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1495</v>
+        <v>-0.4309</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1495</v>
+        <v>-0.4309</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4976</v>
+        <v>0.861</v>
       </c>
       <c r="K27" t="n">
         <v>98</v>
@@ -1679,7 +1679,7 @@
         <v>169</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3481</v>
+        <v>0.4301</v>
       </c>
       <c r="N27" t="n">
         <v>267</v>
@@ -1688,47 +1688,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1772</v>
+        <v>0.2088</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0805</v>
+        <v>0.0949</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5347</v>
+        <v>-0.5107</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1772</v>
+        <v>0.2088</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4504</v>
+        <v>0.1819</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7951</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4504</v>
+        <v>0.1819</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4504</v>
+        <v>0.1819</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7951</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L28" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3447</v>
+        <v>0.1819</v>
       </c>
       <c r="N28" t="n">
-        <v>267</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29">
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0347</v>
+        <v>0.1215</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0158</v>
+        <v>0.0552</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5504</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0347</v>
+        <v>0.1215</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1311</v>
+        <v>0.2266</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.039</v>
+        <v>-0.0477</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1311</v>
+        <v>0.2266</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1311</v>
+        <v>0.2266</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.039</v>
+        <v>-0.0477</v>
       </c>
       <c r="K29" t="n">
         <v>112</v>
@@ -1771,7 +1771,7 @@
         <v>59</v>
       </c>
       <c r="M29" t="n">
-        <v>0.09209999999999999</v>
+        <v>0.1789</v>
       </c>
       <c r="N29" t="n">
         <v>171</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0288</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0131</v>
+        <v>0.0415</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.601</v>
+        <v>-0.5642</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0288</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1941</v>
+        <v>-0.1411</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3432</v>
+        <v>0.3527</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1941</v>
+        <v>-0.1411</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1941</v>
+        <v>-0.1411</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3432</v>
+        <v>0.3527</v>
       </c>
       <c r="K30" t="n">
         <v>109</v>
@@ -1817,7 +1817,7 @@
         <v>102</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1491</v>
+        <v>0.2116</v>
       </c>
       <c r="N30" t="n">
         <v>211</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2794</v>
+        <v>-0.2752</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1269</v>
+        <v>-0.125</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7386</v>
+        <v>-0.7312</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2794</v>
+        <v>-0.2752</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.19</v>
+        <v>-0.1858</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.19</v>
+        <v>-0.1858</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.19</v>
+        <v>-0.1858</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.19</v>
+        <v>-0.1858</v>
       </c>
       <c r="N31" t="n">
         <v>114</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6853</v>
+        <v>-0.6863</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3114</v>
+        <v>-0.3118</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9199000000000001</v>
+        <v>-0.9184</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6853</v>
+        <v>-0.6863</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5848</v>
+        <v>-0.5724</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0063</v>
+        <v>-0.0071</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5848</v>
+        <v>-0.5724</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5848</v>
+        <v>-0.5724</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0063</v>
+        <v>-0.0071</v>
       </c>
       <c r="K32" t="n">
         <v>112</v>
@@ -1909,7 +1909,7 @@
         <v>59</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5785</v>
+        <v>-0.5795</v>
       </c>
       <c r="N32" t="n">
         <v>171</v>
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8537</v>
+        <v>-0.8646</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3879</v>
+        <v>-0.3928</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9951</v>
+        <v>-0.9997</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8537</v>
+        <v>-0.8646</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2556</v>
+        <v>0.2223</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.793</v>
+        <v>-0.7706</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2556</v>
+        <v>0.2223</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2556</v>
+        <v>0.2223</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.793</v>
+        <v>-0.7706</v>
       </c>
       <c r="K33" t="n">
         <v>95</v>
@@ -1955,7 +1955,7 @@
         <v>38</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5374000000000001</v>
+        <v>-0.5483</v>
       </c>
       <c r="N33" t="n">
         <v>133</v>
@@ -1964,32 +1964,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9764</v>
+        <v>-0.9549</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4436</v>
+        <v>-0.4338</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.05</v>
+        <v>-1.0408</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9764</v>
+        <v>-0.9549</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7032</v>
+        <v>-0.8138</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7032</v>
+        <v>-0.8138</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7032</v>
+        <v>-0.8138</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7032</v>
+        <v>-0.8138</v>
       </c>
       <c r="N34" t="n">
         <v>97</v>
@@ -2010,32 +2010,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9806</v>
+        <v>-0.9704</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4455</v>
+        <v>-0.4409</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0518</v>
+        <v>-1.0479</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9806</v>
+        <v>-0.9704</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8395</v>
+        <v>-0.6972</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8395</v>
+        <v>-0.6972</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8395</v>
+        <v>-0.6972</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8395</v>
+        <v>-0.6972</v>
       </c>
       <c r="N35" t="n">
         <v>97</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0367</v>
+        <v>-1.067</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.471</v>
+        <v>-0.4848</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0769</v>
+        <v>-1.0919</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0367</v>
+        <v>-1.067</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6973</v>
+        <v>-0.7276</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6973</v>
+        <v>-0.7276</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6973</v>
+        <v>-0.7276</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6973</v>
+        <v>-0.7276</v>
       </c>
       <c r="N36" t="n">
         <v>97</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.5767</v>
+        <v>-1.5854</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.7163</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.3181</v>
+        <v>-1.328</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.5767</v>
+        <v>-1.5854</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.386</v>
+        <v>-1.3947</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.386</v>
+        <v>-1.3947</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.386</v>
+        <v>-1.3947</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.386</v>
+        <v>-1.3947</v>
       </c>
       <c r="N37" t="n">
         <v>114</v>
@@ -2148,139 +2148,139 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.3287</v>
+        <v>-2.1659</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.058</v>
+        <v>-0.984</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.654</v>
+        <v>-1.5925</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.3287</v>
+        <v>-2.1659</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.1014</v>
+        <v>-1.3999</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.5641</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.1014</v>
+        <v>-1.3999</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.1014</v>
+        <v>-0.786</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.5641</v>
       </c>
       <c r="K38" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="L38" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.9749</v>
+        <v>-1.3501</v>
       </c>
       <c r="N38" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.3353</v>
+        <v>-2.3319</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.061</v>
+        <v>-1.0595</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.6569</v>
+        <v>-1.6681</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.3353</v>
+        <v>-2.3319</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.8625</v>
+        <v>-1.1202</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.2387</v>
+        <v>-0.8579</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.8625</v>
+        <v>-1.1202</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.8625</v>
+        <v>-1.1202</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.2387</v>
+        <v>-0.8579</v>
       </c>
       <c r="K39" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="L39" t="n">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.1012</v>
+        <v>-1.9781</v>
       </c>
       <c r="N39" t="n">
-        <v>211</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.3409</v>
+        <v>-2.4405</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.0636</v>
+        <v>-1.1088</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6594</v>
+        <v>-1.7176</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.3409</v>
+        <v>-2.4405</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.6</v>
+        <v>-0.9197</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.539</v>
+        <v>-1.2867</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.6</v>
+        <v>-0.9197</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.864</v>
+        <v>-0.9197</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.539</v>
+        <v>-1.2867</v>
       </c>
       <c r="K40" t="n">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="L40" t="n">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.403</v>
+        <v>-2.2064</v>
       </c>
       <c r="N40" t="n">
-        <v>132</v>
+        <v>211</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.4555</v>
+        <v>-3.1693</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.57</v>
+        <v>-1.4399</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.1573</v>
+        <v>-2.0496</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.4555</v>
+        <v>-3.1693</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.5714</v>
+        <v>-3.2606</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4313</v>
+        <v>0.4067</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.5714</v>
+        <v>-3.2606</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.9285</v>
+        <v>-1.8307</v>
       </c>
       <c r="J41" t="n">
-        <v>0.4313</v>
+        <v>0.4067</v>
       </c>
       <c r="K41" t="n">
         <v>103</v>
@@ -2323,7 +2323,7 @@
         <v>122</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.4972</v>
+        <v>-1.424</v>
       </c>
       <c r="N41" t="n">
         <v>225</v>
@@ -2429,10 +2429,10 @@
         <v>1.43</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0018</v>
+        <v>0.9944</v>
       </c>
       <c r="J2" t="n">
-        <v>20.036</v>
+        <v>19.888</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.43</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0018</v>
+        <v>0.9944</v>
       </c>
       <c r="J3" t="n">
-        <v>20.036</v>
+        <v>19.888</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.39</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9254</v>
+        <v>0.9111</v>
       </c>
       <c r="J4" t="n">
-        <v>18.508</v>
+        <v>18.222</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1654</v>
+        <v>0.1394</v>
       </c>
       <c r="J5" t="n">
-        <v>3.308</v>
+        <v>2.788</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.583</v>
+        <v>-0.5475</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.66</v>
+        <v>-10.95</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.24</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5226</v>
+        <v>0.4656</v>
       </c>
       <c r="J7" t="n">
-        <v>10.452</v>
+        <v>9.311999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.03</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1126</v>
+        <v>0.0833</v>
       </c>
       <c r="J8" t="n">
-        <v>2.252</v>
+        <v>1.666</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1627</v>
+        <v>-0.1436</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.254</v>
+        <v>-2.872</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.84</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2049</v>
+        <v>-0.1849</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.098</v>
+        <v>-3.698</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.63</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.404</v>
+        <v>-0.3935</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.08</v>
+        <v>-7.87</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>2.02</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8453</v>
+        <v>1.9018</v>
       </c>
       <c r="J12" t="n">
-        <v>33.2154</v>
+        <v>34.2324</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.31</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7477</v>
+        <v>0.7297</v>
       </c>
       <c r="J13" t="n">
-        <v>13.4586</v>
+        <v>13.1346</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.28</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6877</v>
+        <v>0.6664</v>
       </c>
       <c r="J14" t="n">
-        <v>12.3786</v>
+        <v>11.9952</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.23</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5835</v>
+        <v>0.5574</v>
       </c>
       <c r="J15" t="n">
-        <v>10.503</v>
+        <v>10.0332</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.14</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3795</v>
+        <v>0.3476</v>
       </c>
       <c r="J16" t="n">
-        <v>6.831</v>
+        <v>6.2568</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.28</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6145</v>
+        <v>0.5639</v>
       </c>
       <c r="J17" t="n">
-        <v>11.061</v>
+        <v>10.1502</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.27</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5977</v>
+        <v>0.5465</v>
       </c>
       <c r="J18" t="n">
-        <v>10.7586</v>
+        <v>9.837</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.68</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3522</v>
+        <v>-0.3371</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.3396</v>
+        <v>-6.0678</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.59</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.433</v>
+        <v>-0.4248</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.794</v>
+        <v>-7.6464</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.47</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5369</v>
+        <v>-0.542</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.664199999999999</v>
+        <v>-9.756</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>2.28</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J22" t="n">
-        <v>36.906</v>
+        <v>39.644</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.35</v>
       </c>
       <c r="I23" t="n">
-        <v>0.845</v>
+        <v>0.825</v>
       </c>
       <c r="J23" t="n">
-        <v>16.9</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.08</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2503</v>
+        <v>0.2199</v>
       </c>
       <c r="J24" t="n">
-        <v>5.006</v>
+        <v>4.398</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.91</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3597</v>
+        <v>-0.3198</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.194</v>
+        <v>-6.396</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.57</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.1145</v>
+        <v>-1.1334</v>
       </c>
       <c r="J26" t="n">
-        <v>-22.29</v>
+        <v>-22.668</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.66</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1684</v>
+        <v>1.1642</v>
       </c>
       <c r="J27" t="n">
-        <v>23.368</v>
+        <v>23.284</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.96</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0667</v>
+        <v>-0.0548</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.334</v>
+        <v>-1.096</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.78</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2637</v>
+        <v>-0.2443</v>
       </c>
       <c r="J29" t="n">
-        <v>-5.274</v>
+        <v>-4.886</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.73</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3115</v>
+        <v>-0.294</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.23</v>
+        <v>-5.88</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.43</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.5869</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.502</v>
+        <v>-11.738</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.19</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4619</v>
+        <v>0.4196</v>
       </c>
       <c r="J32" t="n">
-        <v>8.3142</v>
+        <v>7.5528</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.86</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.177</v>
+        <v>-0.1599</v>
       </c>
       <c r="J33" t="n">
-        <v>-3.186</v>
+        <v>-2.8782</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.8</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2362</v>
+        <v>-0.2179</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.2516</v>
+        <v>-3.9222</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.67</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3581</v>
+        <v>-0.3435</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.4458</v>
+        <v>-6.183</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.62</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4032</v>
+        <v>-0.392</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.2576</v>
+        <v>-7.056</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.74</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2342</v>
+        <v>1.2323</v>
       </c>
       <c r="J37" t="n">
-        <v>22.2156</v>
+        <v>22.1814</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.7</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1842</v>
+        <v>1.1797</v>
       </c>
       <c r="J38" t="n">
-        <v>21.3156</v>
+        <v>21.2346</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.36</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7399</v>
+        <v>0.7305</v>
       </c>
       <c r="J39" t="n">
-        <v>13.3182</v>
+        <v>13.149</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.19</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4834</v>
+        <v>0.4695</v>
       </c>
       <c r="J40" t="n">
-        <v>8.7012</v>
+        <v>8.451000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.88</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4599</v>
+        <v>-0.4245</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.2782</v>
+        <v>-7.641</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.32</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0916</v>
+        <v>1.0319</v>
       </c>
       <c r="J42" t="n">
-        <v>17.4656</v>
+        <v>16.5104</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>2.01</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8974</v>
+        <v>0.8408</v>
       </c>
       <c r="J43" t="n">
-        <v>14.3584</v>
+        <v>13.4528</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.19</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2672</v>
+        <v>0.2208</v>
       </c>
       <c r="J44" t="n">
-        <v>4.2752</v>
+        <v>3.5328</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.091</v>
+        <v>-0.079</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.456</v>
+        <v>-1.264</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.79</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2942</v>
+        <v>-0.2811</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.7072</v>
+        <v>-4.4976</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.98</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.008</v>
+        <v>0.0019</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.128</v>
+        <v>0.0304</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2181</v>
+        <v>-0.2025</v>
       </c>
       <c r="J48" t="n">
-        <v>-3.4896</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.75</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2762</v>
+        <v>-0.2607</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.4192</v>
+        <v>-4.1712</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.6</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4106</v>
+        <v>-0.4001</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.5696</v>
+        <v>-6.4016</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.55</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4549</v>
+        <v>-0.4483</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.2784</v>
+        <v>-7.1728</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.24</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5259</v>
+        <v>0.5038</v>
       </c>
       <c r="J52" t="n">
-        <v>9.466200000000001</v>
+        <v>9.0684</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.12</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3358</v>
+        <v>0.287</v>
       </c>
       <c r="J53" t="n">
-        <v>6.0444</v>
+        <v>5.166</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.64</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3859</v>
+        <v>-0.3733</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.9462</v>
+        <v>-6.7194</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.6</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4217</v>
+        <v>-0.4122</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.5906</v>
+        <v>-7.4196</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.57</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4481</v>
+        <v>-0.4414</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.065799999999999</v>
+        <v>-7.9452</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.74</v>
       </c>
       <c r="I57" t="n">
-        <v>1.2293</v>
+        <v>1.2272</v>
       </c>
       <c r="J57" t="n">
-        <v>22.1274</v>
+        <v>22.0896</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.55</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9892</v>
+        <v>0.9788</v>
       </c>
       <c r="J58" t="n">
-        <v>17.8056</v>
+        <v>17.6184</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.5</v>
       </c>
       <c r="I59" t="n">
-        <v>0.9242</v>
+        <v>0.9132</v>
       </c>
       <c r="J59" t="n">
-        <v>16.6356</v>
+        <v>16.4376</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.27</v>
       </c>
       <c r="I60" t="n">
-        <v>0.6072</v>
+        <v>0.603</v>
       </c>
       <c r="J60" t="n">
-        <v>10.9296</v>
+        <v>10.854</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2998</v>
+        <v>-0.2665</v>
       </c>
       <c r="J61" t="n">
-        <v>-5.3964</v>
+        <v>-4.797</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>2.26</v>
       </c>
       <c r="I62" t="n">
-        <v>1.8782</v>
+        <v>1.949</v>
       </c>
       <c r="J62" t="n">
-        <v>43.1986</v>
+        <v>44.827</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.08</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2404</v>
+        <v>0.2102</v>
       </c>
       <c r="J63" t="n">
-        <v>5.5292</v>
+        <v>4.8346</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.08</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2404</v>
+        <v>0.2102</v>
       </c>
       <c r="J64" t="n">
-        <v>5.5292</v>
+        <v>4.8346</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.05</v>
       </c>
       <c r="I65" t="n">
-        <v>0.153</v>
+        <v>0.1269</v>
       </c>
       <c r="J65" t="n">
-        <v>3.519</v>
+        <v>2.9187</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.02</v>
       </c>
       <c r="I66" t="n">
-        <v>0.0511</v>
+        <v>0.0343</v>
       </c>
       <c r="J66" t="n">
-        <v>1.1753</v>
+        <v>0.7889</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.7</v>
       </c>
       <c r="I67" t="n">
-        <v>0.993</v>
+        <v>0.9633</v>
       </c>
       <c r="J67" t="n">
-        <v>22.839</v>
+        <v>22.1559</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.35</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6178</v>
+        <v>0.5896</v>
       </c>
       <c r="J68" t="n">
-        <v>14.2094</v>
+        <v>13.5608</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.65</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3915</v>
+        <v>-0.3802</v>
       </c>
       <c r="J69" t="n">
-        <v>-9.0045</v>
+        <v>-8.7446</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.62</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4181</v>
+        <v>-0.4096</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.616300000000001</v>
+        <v>-9.4208</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.59</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4445</v>
+        <v>-0.4388</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.2235</v>
+        <v>-10.0924</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.2</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3834</v>
+        <v>0.3858</v>
       </c>
       <c r="J72" t="n">
-        <v>7.668</v>
+        <v>7.716</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.04</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1281</v>
+        <v>0.114</v>
       </c>
       <c r="J73" t="n">
-        <v>2.562</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.78</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2553</v>
+        <v>-0.237</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.106</v>
+        <v>-4.74</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.7</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3304</v>
+        <v>-0.3142</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.608</v>
+        <v>-6.284</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.41</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.585</v>
+        <v>-0.5971</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.7</v>
+        <v>-11.942</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.57</v>
       </c>
       <c r="I77" t="n">
-        <v>0.617</v>
+        <v>0.5783</v>
       </c>
       <c r="J77" t="n">
-        <v>12.34</v>
+        <v>11.566</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.5</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5312</v>
       </c>
       <c r="J78" t="n">
-        <v>11.32</v>
+        <v>10.624</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.46</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5364</v>
+        <v>0.4993</v>
       </c>
       <c r="J79" t="n">
-        <v>10.728</v>
+        <v>9.986000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.26</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3618</v>
+        <v>0.3057</v>
       </c>
       <c r="J80" t="n">
-        <v>7.236</v>
+        <v>6.114</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.72</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3513</v>
+        <v>-0.3402</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.026</v>
+        <v>-6.804</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.37</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.7668</v>
       </c>
       <c r="J82" t="n">
-        <v>16.4388</v>
+        <v>16.1028</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.23</v>
       </c>
       <c r="I83" t="n">
-        <v>0.57</v>
+        <v>0.5602</v>
       </c>
       <c r="J83" t="n">
-        <v>11.97</v>
+        <v>11.7642</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3178</v>
+        <v>0.2834</v>
       </c>
       <c r="J84" t="n">
-        <v>6.6738</v>
+        <v>5.9514</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.07</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2367</v>
+        <v>0.2058</v>
       </c>
       <c r="J85" t="n">
-        <v>4.9707</v>
+        <v>4.3218</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.99</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.0848</v>
+        <v>-0.0639</v>
       </c>
       <c r="J86" t="n">
-        <v>-1.7808</v>
+        <v>-1.3419</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.11</v>
       </c>
       <c r="I87" t="n">
-        <v>0.299</v>
+        <v>0.2496</v>
       </c>
       <c r="J87" t="n">
-        <v>6.279</v>
+        <v>5.2416</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.05</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1707</v>
+        <v>0.1333</v>
       </c>
       <c r="J88" t="n">
-        <v>3.5847</v>
+        <v>2.7993</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.0771</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.9089</v>
+        <v>-1.6191</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.77</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2708</v>
+        <v>-0.2518</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.6868</v>
+        <v>-5.2878</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4621</v>
+        <v>-0.4574</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.7041</v>
+        <v>-9.605399999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.36</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6362</v>
+        <v>0.6081</v>
       </c>
       <c r="J92" t="n">
-        <v>14.6326</v>
+        <v>13.9863</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.03</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1069</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="J93" t="n">
-        <v>2.4587</v>
+        <v>1.8101</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.93</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.108</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="J94" t="n">
-        <v>-2.484</v>
+        <v>-2.0999</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.92</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.12</v>
+        <v>-0.1024</v>
       </c>
       <c r="J95" t="n">
-        <v>-2.76</v>
+        <v>-2.3552</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.53</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.494</v>
+        <v>-0.4942</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.362</v>
+        <v>-11.3666</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.44</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8851</v>
+        <v>0.8698</v>
       </c>
       <c r="J97" t="n">
-        <v>20.3573</v>
+        <v>20.0054</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.32</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7098</v>
+        <v>0.6946</v>
       </c>
       <c r="J98" t="n">
-        <v>16.3254</v>
+        <v>15.9758</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.24</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5867</v>
+        <v>0.5758</v>
       </c>
       <c r="J99" t="n">
-        <v>13.4941</v>
+        <v>13.2434</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.93</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2874</v>
+        <v>-0.2473</v>
       </c>
       <c r="J100" t="n">
-        <v>-6.6102</v>
+        <v>-5.6879</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.8</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.616</v>
+        <v>-0.5803</v>
       </c>
       <c r="J101" t="n">
-        <v>-14.168</v>
+        <v>-13.3469</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.13</v>
       </c>
       <c r="I102" t="n">
-        <v>0.312</v>
+        <v>0.2605</v>
       </c>
       <c r="J102" t="n">
-        <v>11.232</v>
+        <v>9.378</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.04</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1263</v>
+        <v>0.0953</v>
       </c>
       <c r="J103" t="n">
-        <v>4.5468</v>
+        <v>3.4308</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.01</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0446</v>
+        <v>0.03</v>
       </c>
       <c r="J104" t="n">
-        <v>1.6056</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.9</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1459</v>
+        <v>-0.1264</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.2524</v>
+        <v>-4.5504</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.86</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1898</v>
+        <v>-0.1693</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.8328</v>
+        <v>-6.0948</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.34</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7433</v>
+        <v>0.7274</v>
       </c>
       <c r="J107" t="n">
-        <v>26.7588</v>
+        <v>26.1864</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.27</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.6232</v>
       </c>
       <c r="J108" t="n">
-        <v>22.9176</v>
+        <v>22.4352</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.16</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4575</v>
+        <v>0.4264</v>
       </c>
       <c r="J109" t="n">
-        <v>16.47</v>
+        <v>15.3504</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.02</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0803</v>
+        <v>0.0633</v>
       </c>
       <c r="J110" t="n">
-        <v>2.8908</v>
+        <v>2.2788</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.85</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4943</v>
+        <v>-0.4531</v>
       </c>
       <c r="J111" t="n">
-        <v>-17.7948</v>
+        <v>-16.3116</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.14</v>
       </c>
       <c r="I112" t="n">
-        <v>0.381</v>
+        <v>0.3319</v>
       </c>
       <c r="J112" t="n">
-        <v>7.239</v>
+        <v>6.3061</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.85</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1865</v>
+        <v>-0.1694</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.5435</v>
+        <v>-3.2186</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.8</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2354</v>
+        <v>-0.2174</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.4726</v>
+        <v>-4.1306</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.68</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3479</v>
+        <v>-0.3327</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.6101</v>
+        <v>-6.3213</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.62</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4021</v>
+        <v>-0.3908</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.6399</v>
+        <v>-7.4252</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.58</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0537</v>
+        <v>1.043</v>
       </c>
       <c r="J117" t="n">
-        <v>20.0203</v>
+        <v>19.817</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.57</v>
       </c>
       <c r="I118" t="n">
-        <v>1.0405</v>
+        <v>1.0293</v>
       </c>
       <c r="J118" t="n">
-        <v>19.7695</v>
+        <v>19.5567</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.51</v>
       </c>
       <c r="I119" t="n">
-        <v>0.96</v>
+        <v>0.9464</v>
       </c>
       <c r="J119" t="n">
-        <v>18.24</v>
+        <v>17.9816</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.98</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1439</v>
+        <v>-0.1172</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.7341</v>
+        <v>-2.2268</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.62</v>
       </c>
       <c r="I121" t="n">
-        <v>-1.0171</v>
+        <v>-1.0229</v>
       </c>
       <c r="J121" t="n">
-        <v>-19.3249</v>
+        <v>-19.4351</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.27</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5739</v>
+        <v>0.5574</v>
       </c>
       <c r="J122" t="n">
-        <v>10.9041</v>
+        <v>10.5906</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.02</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1161</v>
+        <v>0.0907</v>
       </c>
       <c r="J123" t="n">
-        <v>2.2059</v>
+        <v>1.7233</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.63</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3918</v>
+        <v>-0.3796</v>
       </c>
       <c r="J124" t="n">
-        <v>-7.4442</v>
+        <v>-7.2124</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.57</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4451</v>
+        <v>-0.4379</v>
       </c>
       <c r="J125" t="n">
-        <v>-8.456899999999999</v>
+        <v>-8.3201</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.54</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4714</v>
+        <v>-0.4671</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.9566</v>
+        <v>-8.8749</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.61</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0899</v>
+        <v>1.0807</v>
       </c>
       <c r="J127" t="n">
-        <v>20.7081</v>
+        <v>20.5333</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.52</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9705</v>
+        <v>0.9573</v>
       </c>
       <c r="J128" t="n">
-        <v>18.4395</v>
+        <v>18.1887</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.33</v>
       </c>
       <c r="I129" t="n">
-        <v>0.7065</v>
+        <v>0.6944</v>
       </c>
       <c r="J129" t="n">
-        <v>13.4235</v>
+        <v>13.1936</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.03</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0926</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="J130" t="n">
-        <v>1.7594</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.85</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5185</v>
+        <v>-0.4814</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.8515</v>
+        <v>-9.146599999999999</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.34</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8569</v>
+        <v>0.8348</v>
       </c>
       <c r="J132" t="n">
-        <v>24.8501</v>
+        <v>24.2092</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.18</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5145</v>
+        <v>0.4752</v>
       </c>
       <c r="J133" t="n">
-        <v>14.9205</v>
+        <v>13.7808</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.01</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0429</v>
+        <v>0.032</v>
       </c>
       <c r="J134" t="n">
-        <v>1.2441</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.01</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0429</v>
+        <v>0.032</v>
       </c>
       <c r="J135" t="n">
-        <v>1.2441</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.99</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.0765</v>
+        <v>-0.0562</v>
       </c>
       <c r="J136" t="n">
-        <v>-2.2185</v>
+        <v>-1.6298</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.5</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9045</v>
+        <v>0.8616</v>
       </c>
       <c r="J137" t="n">
-        <v>26.2305</v>
+        <v>24.9864</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.05</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1503</v>
+        <v>0.1156</v>
       </c>
       <c r="J138" t="n">
-        <v>4.3587</v>
+        <v>3.3524</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.96</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.0575</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.0706</v>
+        <v>-1.6675</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.241</v>
+        <v>-0.2208</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.989</v>
+        <v>-6.4032</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.6</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4359</v>
+        <v>-0.4293</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.6411</v>
+        <v>-12.4497</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.36</v>
       </c>
       <c r="I142" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.8622</v>
       </c>
       <c r="J142" t="n">
-        <v>20.2768</v>
+        <v>19.8306</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.31</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7812</v>
+        <v>0.7544</v>
       </c>
       <c r="J143" t="n">
-        <v>17.9676</v>
+        <v>17.3512</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.26</v>
       </c>
       <c r="I144" t="n">
-        <v>0.678</v>
+        <v>0.6456</v>
       </c>
       <c r="J144" t="n">
-        <v>15.594</v>
+        <v>14.8488</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.08</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2629</v>
+        <v>0.231</v>
       </c>
       <c r="J145" t="n">
-        <v>6.0467</v>
+        <v>5.313</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.8</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6188</v>
+        <v>-0.5837</v>
       </c>
       <c r="J146" t="n">
-        <v>-14.2324</v>
+        <v>-13.4251</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.28</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5598</v>
+        <v>0.5002</v>
       </c>
       <c r="J147" t="n">
-        <v>12.8754</v>
+        <v>11.5046</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.12</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2869</v>
+        <v>0.2377</v>
       </c>
       <c r="J148" t="n">
-        <v>6.5987</v>
+        <v>5.4671</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.1</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2487</v>
+        <v>0.203</v>
       </c>
       <c r="J149" t="n">
-        <v>5.7201</v>
+        <v>4.669</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.09</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2291</v>
+        <v>0.1853</v>
       </c>
       <c r="J150" t="n">
-        <v>5.2693</v>
+        <v>4.2619</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.52</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.5107</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.6748</v>
+        <v>-11.7461</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.47</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6062</v>
+        <v>0.5352</v>
       </c>
       <c r="J152" t="n">
-        <v>13.9426</v>
+        <v>12.3096</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.12</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2035</v>
+        <v>0.1611</v>
       </c>
       <c r="J153" t="n">
-        <v>4.6805</v>
+        <v>3.7053</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.08</v>
       </c>
       <c r="I154" t="n">
-        <v>0.147</v>
+        <v>0.1133</v>
       </c>
       <c r="J154" t="n">
-        <v>3.381</v>
+        <v>2.6059</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.01</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0212</v>
+        <v>0.0136</v>
       </c>
       <c r="J155" t="n">
-        <v>0.4876</v>
+        <v>0.3128</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.97</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.0683</v>
+        <v>-0.054</v>
       </c>
       <c r="J156" t="n">
-        <v>-1.5709</v>
+        <v>-1.242</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.66</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.961</v>
       </c>
       <c r="J157" t="n">
-        <v>20.1365</v>
+        <v>22.103</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.97</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0593</v>
+        <v>-0.0464</v>
       </c>
       <c r="J158" t="n">
-        <v>-1.3639</v>
+        <v>-1.0672</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1003</v>
+        <v>-0.0832</v>
       </c>
       <c r="J159" t="n">
-        <v>-2.3069</v>
+        <v>-1.9136</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.76</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2928</v>
+        <v>-0.2746</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.7344</v>
+        <v>-6.3158</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.75</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3024</v>
+        <v>-0.2847</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.9552</v>
+        <v>-6.5481</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.08</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2949</v>
+        <v>0.2585</v>
       </c>
       <c r="J162" t="n">
-        <v>4.7184</v>
+        <v>4.136</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.77</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.2568</v>
+        <v>-0.2416</v>
       </c>
       <c r="J163" t="n">
-        <v>-4.1088</v>
+        <v>-3.8656</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.7</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.3202</v>
+        <v>-0.3054</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.1232</v>
+        <v>-4.8864</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.57</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4365</v>
+        <v>-0.4281</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.984</v>
+        <v>-6.8496</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.54</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4629</v>
+        <v>-0.4572</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.4064</v>
+        <v>-7.3152</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.69</v>
       </c>
       <c r="I167" t="n">
-        <v>1.3231</v>
+        <v>1.3436</v>
       </c>
       <c r="J167" t="n">
-        <v>21.1696</v>
+        <v>21.4976</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.37</v>
       </c>
       <c r="I168" t="n">
-        <v>0.8661</v>
+        <v>0.8531</v>
       </c>
       <c r="J168" t="n">
-        <v>13.8576</v>
+        <v>13.6496</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.36</v>
       </c>
       <c r="I169" t="n">
-        <v>0.8476</v>
+        <v>0.8334</v>
       </c>
       <c r="J169" t="n">
-        <v>13.5616</v>
+        <v>13.3344</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.3</v>
       </c>
       <c r="I170" t="n">
-        <v>0.7336</v>
+        <v>0.7131</v>
       </c>
       <c r="J170" t="n">
-        <v>11.7376</v>
+        <v>11.4096</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.04</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1127</v>
+        <v>0.0881</v>
       </c>
       <c r="J171" t="n">
-        <v>1.8032</v>
+        <v>1.4096</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.46</v>
       </c>
       <c r="I172" t="n">
-        <v>0.8149</v>
+        <v>0.7612</v>
       </c>
       <c r="J172" t="n">
-        <v>19.5576</v>
+        <v>18.2688</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.23</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4667</v>
+        <v>0.4086</v>
       </c>
       <c r="J173" t="n">
-        <v>11.2008</v>
+        <v>9.8064</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.1</v>
       </c>
       <c r="I174" t="n">
-        <v>0.241</v>
+        <v>0.1978</v>
       </c>
       <c r="J174" t="n">
-        <v>5.784</v>
+        <v>4.7472</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.82</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2394</v>
+        <v>-0.2195</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.7456</v>
+        <v>-5.268</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.79</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2693</v>
+        <v>-0.2504</v>
       </c>
       <c r="J176" t="n">
-        <v>-6.4632</v>
+        <v>-6.0096</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.74</v>
       </c>
       <c r="I177" t="n">
-        <v>1.4765</v>
+        <v>1.5206</v>
       </c>
       <c r="J177" t="n">
-        <v>35.436</v>
+        <v>36.4944</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.32</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8341</v>
+        <v>0.8105</v>
       </c>
       <c r="J178" t="n">
-        <v>20.0184</v>
+        <v>19.452</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.98</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1073</v>
+        <v>-0.082</v>
       </c>
       <c r="J179" t="n">
-        <v>-2.5752</v>
+        <v>-1.968</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.7</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.8186</v>
+        <v>-0.796</v>
       </c>
       <c r="J180" t="n">
-        <v>-19.6464</v>
+        <v>-19.104</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.5</v>
       </c>
       <c r="I181" t="n">
-        <v>-1.2247</v>
+        <v>-1.2546</v>
       </c>
       <c r="J181" t="n">
-        <v>-29.3928</v>
+        <v>-30.1104</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.62</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2667</v>
+        <v>1.2852</v>
       </c>
       <c r="J182" t="n">
-        <v>25.334</v>
+        <v>25.704</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.41</v>
       </c>
       <c r="I183" t="n">
-        <v>0.9673</v>
+        <v>0.9587</v>
       </c>
       <c r="J183" t="n">
-        <v>19.346</v>
+        <v>19.174</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.09</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2841</v>
+        <v>0.2521</v>
       </c>
       <c r="J184" t="n">
-        <v>5.682</v>
+        <v>5.042</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.04</v>
       </c>
       <c r="I185" t="n">
-        <v>0.1381</v>
+        <v>0.1145</v>
       </c>
       <c r="J185" t="n">
-        <v>2.762</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.83</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.555</v>
+        <v>-0.5175</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.1</v>
+        <v>-10.35</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.13</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3282</v>
+        <v>0.2762</v>
       </c>
       <c r="J187" t="n">
-        <v>6.564</v>
+        <v>5.524</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.95</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.081</v>
+        <v>-0.0675</v>
       </c>
       <c r="J188" t="n">
-        <v>-1.62</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.95</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.081</v>
+        <v>-0.0675</v>
       </c>
       <c r="J189" t="n">
-        <v>-1.62</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.87</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1732</v>
+        <v>-0.1537</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.464</v>
+        <v>-3.074</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.7</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3402</v>
+        <v>-0.3244</v>
       </c>
       <c r="J191" t="n">
-        <v>-6.804</v>
+        <v>-6.488</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.45</v>
       </c>
       <c r="I192" t="n">
-        <v>1.0428</v>
+        <v>1.0471</v>
       </c>
       <c r="J192" t="n">
-        <v>22.9416</v>
+        <v>23.0362</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.34</v>
       </c>
       <c r="I193" t="n">
-        <v>0.8433</v>
+        <v>0.8207</v>
       </c>
       <c r="J193" t="n">
-        <v>18.5526</v>
+        <v>18.0554</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.23</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6156</v>
+        <v>0.5806</v>
       </c>
       <c r="J194" t="n">
-        <v>13.5432</v>
+        <v>12.7732</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2599</v>
+        <v>-0.2211</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.7178</v>
+        <v>-4.8642</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.82</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5713</v>
+        <v>-0.5335</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.5686</v>
+        <v>-11.737</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.26</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5339</v>
+        <v>0.4747</v>
       </c>
       <c r="J197" t="n">
-        <v>11.7458</v>
+        <v>10.4434</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.22</v>
       </c>
       <c r="I198" t="n">
-        <v>0.468</v>
+        <v>0.4096</v>
       </c>
       <c r="J198" t="n">
-        <v>10.296</v>
+        <v>9.011200000000001</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1</v>
       </c>
       <c r="I199" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="J199" t="n">
-        <v>0.0022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.83</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.222</v>
+        <v>-0.2015</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.884</v>
+        <v>-4.433</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.68</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3658</v>
+        <v>-0.3524</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.047599999999999</v>
+        <v>-7.7528</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>2.21</v>
       </c>
       <c r="I202" t="n">
-        <v>1.1746</v>
+        <v>1.1411</v>
       </c>
       <c r="J202" t="n">
-        <v>22.3174</v>
+        <v>21.6809</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.69</v>
       </c>
       <c r="I203" t="n">
-        <v>0.7774</v>
+        <v>0.7062</v>
       </c>
       <c r="J203" t="n">
-        <v>14.7706</v>
+        <v>13.4178</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.36</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4608</v>
+        <v>0.4</v>
       </c>
       <c r="J204" t="n">
-        <v>8.7552</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.11</v>
       </c>
       <c r="I205" t="n">
-        <v>0.1644</v>
+        <v>0.1289</v>
       </c>
       <c r="J205" t="n">
-        <v>3.1236</v>
+        <v>2.4491</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.78</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3025</v>
+        <v>-0.2895</v>
       </c>
       <c r="J206" t="n">
-        <v>-5.7475</v>
+        <v>-5.5005</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.26</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4982</v>
+        <v>0.5288</v>
       </c>
       <c r="J207" t="n">
-        <v>9.4658</v>
+        <v>10.0472</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.65</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.3671</v>
+        <v>-0.3536</v>
       </c>
       <c r="J208" t="n">
-        <v>-6.9749</v>
+        <v>-6.7184</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.64</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.3761</v>
+        <v>-0.3631</v>
       </c>
       <c r="J209" t="n">
-        <v>-7.1459</v>
+        <v>-6.8989</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.6</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4118</v>
+        <v>-0.4013</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.8242</v>
+        <v>-7.6247</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.59</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4207</v>
+        <v>-0.411</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.9933</v>
+        <v>-7.809</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.15</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3715</v>
+        <v>0.318</v>
       </c>
       <c r="J212" t="n">
-        <v>7.8015</v>
+        <v>6.678</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.13</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3339</v>
+        <v>0.282</v>
       </c>
       <c r="J213" t="n">
-        <v>7.0119</v>
+        <v>5.922</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.83</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.213</v>
+        <v>-0.1932</v>
       </c>
       <c r="J214" t="n">
-        <v>-4.473</v>
+        <v>-4.0572</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.77</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2722</v>
+        <v>-0.2531</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.7162</v>
+        <v>-5.3151</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.62</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4106</v>
+        <v>-0.4005</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.6226</v>
+        <v>-8.410500000000001</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.54</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1498</v>
+        <v>1.1628</v>
       </c>
       <c r="J217" t="n">
-        <v>24.1458</v>
+        <v>24.4188</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.46</v>
       </c>
       <c r="I218" t="n">
-        <v>1.0392</v>
+        <v>1.0434</v>
       </c>
       <c r="J218" t="n">
-        <v>21.8232</v>
+        <v>21.9114</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.22</v>
       </c>
       <c r="I219" t="n">
-        <v>0.5836</v>
+        <v>0.5523</v>
       </c>
       <c r="J219" t="n">
-        <v>12.2556</v>
+        <v>11.5983</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.2</v>
       </c>
       <c r="I220" t="n">
-        <v>0.5407</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J220" t="n">
-        <v>11.3547</v>
+        <v>10.6806</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.79</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.655</v>
+        <v>-0.6242</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.755</v>
+        <v>-13.1082</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.12</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3262</v>
+        <v>0.2763</v>
       </c>
       <c r="J222" t="n">
-        <v>6.1978</v>
+        <v>5.2497</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.91</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.1251</v>
+        <v>-0.1094</v>
       </c>
       <c r="J223" t="n">
-        <v>-2.3769</v>
+        <v>-2.0786</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.9</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1366</v>
+        <v>-0.1203</v>
       </c>
       <c r="J224" t="n">
-        <v>-2.5954</v>
+        <v>-2.2857</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.72</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3157</v>
+        <v>-0.2985</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.9983</v>
+        <v>-5.6715</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.66</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3709</v>
+        <v>-0.3571</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.0471</v>
+        <v>-6.7849</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.73</v>
       </c>
       <c r="I227" t="n">
-        <v>1.3814</v>
+        <v>1.4053</v>
       </c>
       <c r="J227" t="n">
-        <v>26.2466</v>
+        <v>26.7007</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.61</v>
       </c>
       <c r="I228" t="n">
-        <v>1.228</v>
+        <v>1.2441</v>
       </c>
       <c r="J228" t="n">
-        <v>23.332</v>
+        <v>23.6379</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.22</v>
       </c>
       <c r="I229" t="n">
-        <v>0.574</v>
+        <v>0.5455</v>
       </c>
       <c r="J229" t="n">
-        <v>10.906</v>
+        <v>10.3645</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.05</v>
       </c>
       <c r="I230" t="n">
-        <v>0.1504</v>
+        <v>0.1242</v>
       </c>
       <c r="J230" t="n">
-        <v>2.8576</v>
+        <v>2.3598</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.96</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2245</v>
+        <v>-0.1922</v>
       </c>
       <c r="J231" t="n">
-        <v>-4.2655</v>
+        <v>-3.6518</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.41</v>
       </c>
       <c r="I232" t="n">
-        <v>0.7766</v>
+        <v>0.7255</v>
       </c>
       <c r="J232" t="n">
-        <v>17.0852</v>
+        <v>15.961</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.96</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.0706</v>
+        <v>-0.0571</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.5532</v>
+        <v>-1.2562</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.92</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1212</v>
+        <v>-0.1032</v>
       </c>
       <c r="J234" t="n">
-        <v>-2.6664</v>
+        <v>-2.2704</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1329</v>
+        <v>-0.1143</v>
       </c>
       <c r="J235" t="n">
-        <v>-2.9238</v>
+        <v>-2.5146</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.65</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3904</v>
+        <v>-0.3789</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.588800000000001</v>
+        <v>-8.335800000000001</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.43</v>
       </c>
       <c r="I237" t="n">
-        <v>1.0236</v>
+        <v>1.025</v>
       </c>
       <c r="J237" t="n">
-        <v>22.5192</v>
+        <v>22.55</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.21</v>
       </c>
       <c r="I238" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.5432</v>
       </c>
       <c r="J238" t="n">
-        <v>12.7842</v>
+        <v>11.9504</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.11</v>
       </c>
       <c r="I239" t="n">
-        <v>0.3483</v>
+        <v>0.3109</v>
       </c>
       <c r="J239" t="n">
-        <v>7.6626</v>
+        <v>6.8398</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.98</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1186</v>
+        <v>-0.0917</v>
       </c>
       <c r="J240" t="n">
-        <v>-2.6092</v>
+        <v>-2.0174</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.82</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5628</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="J241" t="n">
-        <v>-12.3816</v>
+        <v>-11.5214</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.36</v>
       </c>
       <c r="I242" t="n">
-        <v>0.7185</v>
+        <v>0.6676</v>
       </c>
       <c r="J242" t="n">
-        <v>17.244</v>
+        <v>16.0224</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.07</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2074</v>
+        <v>0.1651</v>
       </c>
       <c r="J243" t="n">
-        <v>4.9776</v>
+        <v>3.9624</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.82</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2249</v>
+        <v>-0.2049</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.3976</v>
+        <v>-4.9176</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.71</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3309</v>
+        <v>-0.3145</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.9416</v>
+        <v>-7.548</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.64</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3947</v>
+        <v>-0.3833</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.472799999999999</v>
+        <v>-9.199199999999999</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.34</v>
       </c>
       <c r="I247" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="J247" t="n">
-        <v>20.4552</v>
+        <v>19.92</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.22</v>
       </c>
       <c r="I248" t="n">
-        <v>0.6005</v>
+        <v>0.5637</v>
       </c>
       <c r="J248" t="n">
-        <v>14.412</v>
+        <v>13.5288</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.1</v>
       </c>
       <c r="I249" t="n">
-        <v>0.322</v>
+        <v>0.2861</v>
       </c>
       <c r="J249" t="n">
-        <v>7.728</v>
+        <v>6.8664</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.02</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0814</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="J250" t="n">
-        <v>1.9536</v>
+        <v>1.5408</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.93</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2829</v>
+        <v>-0.2426</v>
       </c>
       <c r="J251" t="n">
-        <v>-6.7896</v>
+        <v>-5.8224</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.08</v>
       </c>
       <c r="I252" t="n">
-        <v>0.3569</v>
+        <v>0.4269</v>
       </c>
       <c r="J252" t="n">
-        <v>4.6397</v>
+        <v>5.5497</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.47</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.4943</v>
+        <v>-0.4934</v>
       </c>
       <c r="J253" t="n">
-        <v>-6.4259</v>
+        <v>-6.4142</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.47</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.4943</v>
+        <v>-0.4934</v>
       </c>
       <c r="J254" t="n">
-        <v>-6.4259</v>
+        <v>-6.4142</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.35</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.6011</v>
+        <v>-0.6118</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.8143</v>
+        <v>-7.9534</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.25</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6916</v>
+        <v>-0.7186</v>
       </c>
       <c r="J256" t="n">
-        <v>-8.9908</v>
+        <v>-9.341799999999999</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>2.4</v>
       </c>
       <c r="I257" t="n">
-        <v>1.2427</v>
+        <v>1.2054</v>
       </c>
       <c r="J257" t="n">
-        <v>16.1551</v>
+        <v>15.6702</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>2.12</v>
       </c>
       <c r="I258" t="n">
-        <v>1.079</v>
+        <v>1.0383</v>
       </c>
       <c r="J258" t="n">
-        <v>14.027</v>
+        <v>13.4979</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.89</v>
       </c>
       <c r="I259" t="n">
-        <v>0.918</v>
+        <v>0.8547</v>
       </c>
       <c r="J259" t="n">
-        <v>11.934</v>
+        <v>11.1111</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.83</v>
       </c>
       <c r="I260" t="n">
-        <v>0.8693</v>
+        <v>0.8055</v>
       </c>
       <c r="J260" t="n">
-        <v>11.3009</v>
+        <v>10.4715</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.91</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.1864</v>
+        <v>-0.1754</v>
       </c>
       <c r="J261" t="n">
-        <v>-2.4232</v>
+        <v>-2.2802</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>2.39</v>
       </c>
       <c r="I262" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J262" t="n">
-        <v>36.8068</v>
+        <v>37.6542</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.38</v>
       </c>
       <c r="I263" t="n">
-        <v>0.8914</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="J263" t="n">
-        <v>16.9366</v>
+        <v>16.6725</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.96</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2226</v>
+        <v>-0.19</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.2294</v>
+        <v>-3.61</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2849</v>
+        <v>-0.2488</v>
       </c>
       <c r="J265" t="n">
-        <v>-5.4131</v>
+        <v>-4.7272</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.84</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.513</v>
       </c>
       <c r="J266" t="n">
-        <v>-10.4101</v>
+        <v>-9.747</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.41</v>
       </c>
       <c r="I267" t="n">
-        <v>0.8129</v>
+        <v>0.7719</v>
       </c>
       <c r="J267" t="n">
-        <v>15.4451</v>
+        <v>14.6661</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.99</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.015</v>
+        <v>-0.0105</v>
       </c>
       <c r="J268" t="n">
-        <v>-0.285</v>
+        <v>-0.1995</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.8</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2412</v>
+        <v>-0.2217</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.5828</v>
+        <v>-4.2123</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.68</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3547</v>
+        <v>-0.3398</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.7393</v>
+        <v>-6.4562</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.53</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4877</v>
+        <v>-0.4862</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.266299999999999</v>
+        <v>-9.2378</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2</v>
       </c>
       <c r="I272" t="n">
-        <v>1.7239</v>
+        <v>1.7802</v>
       </c>
       <c r="J272" t="n">
-        <v>32.7541</v>
+        <v>33.8238</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.2</v>
       </c>
       <c r="I273" t="n">
-        <v>0.5357</v>
+        <v>0.505</v>
       </c>
       <c r="J273" t="n">
-        <v>10.1783</v>
+        <v>9.595000000000001</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.16</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4453</v>
+        <v>0.4132</v>
       </c>
       <c r="J274" t="n">
-        <v>8.460699999999999</v>
+        <v>7.8508</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.1</v>
       </c>
       <c r="I275" t="n">
-        <v>0.2975</v>
+        <v>0.2659</v>
       </c>
       <c r="J275" t="n">
-        <v>5.6525</v>
+        <v>5.0521</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.93</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3104</v>
+        <v>-0.2726</v>
       </c>
       <c r="J276" t="n">
-        <v>-5.8976</v>
+        <v>-5.1794</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.44</v>
       </c>
       <c r="I277" t="n">
-        <v>0.827</v>
+        <v>0.7801</v>
       </c>
       <c r="J277" t="n">
-        <v>15.713</v>
+        <v>14.8219</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.26</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5458</v>
+        <v>0.4877</v>
       </c>
       <c r="J278" t="n">
-        <v>10.3702</v>
+        <v>9.266299999999999</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0958</v>
+        <v>-0.08</v>
       </c>
       <c r="J279" t="n">
-        <v>-1.8202</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.74</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3063</v>
+        <v>-0.2886</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.8197</v>
+        <v>-5.4834</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.4</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6031</v>
+        <v>-0.6203</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.4589</v>
+        <v>-11.7857</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.31</v>
       </c>
       <c r="I282" t="n">
-        <v>0.7768</v>
+        <v>0.7504</v>
       </c>
       <c r="J282" t="n">
-        <v>22.5272</v>
+        <v>21.7616</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.29</v>
       </c>
       <c r="I283" t="n">
-        <v>0.7361</v>
+        <v>0.7074</v>
       </c>
       <c r="J283" t="n">
-        <v>21.3469</v>
+        <v>20.5146</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.15</v>
       </c>
       <c r="I284" t="n">
-        <v>0.436</v>
+        <v>0.4006</v>
       </c>
       <c r="J284" t="n">
-        <v>12.644</v>
+        <v>11.6174</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.11</v>
       </c>
       <c r="I285" t="n">
-        <v>0.3388</v>
+        <v>0.3049</v>
       </c>
       <c r="J285" t="n">
-        <v>9.825200000000001</v>
+        <v>8.8421</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.05</v>
       </c>
       <c r="I286" t="n">
-        <v>0.1726</v>
+        <v>0.1462</v>
       </c>
       <c r="J286" t="n">
-        <v>5.0054</v>
+        <v>4.2398</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.14</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3676</v>
+        <v>0.3164</v>
       </c>
       <c r="J287" t="n">
-        <v>10.6604</v>
+        <v>9.175599999999999</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.87</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1687</v>
+        <v>-0.1511</v>
       </c>
       <c r="J288" t="n">
-        <v>-4.8923</v>
+        <v>-4.3819</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.85</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.189</v>
+        <v>-0.1708</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.481</v>
+        <v>-4.9532</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2288</v>
+        <v>-0.2098</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.6352</v>
+        <v>-6.0842</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.6</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4238</v>
+        <v>-0.4146</v>
       </c>
       <c r="J291" t="n">
-        <v>-12.2902</v>
+        <v>-12.0234</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.62</v>
       </c>
       <c r="I292" t="n">
-        <v>1.3045</v>
+        <v>1.3304</v>
       </c>
       <c r="J292" t="n">
-        <v>31.308</v>
+        <v>31.9296</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.46</v>
       </c>
       <c r="I293" t="n">
-        <v>1.08</v>
+        <v>1.0912</v>
       </c>
       <c r="J293" t="n">
-        <v>25.92</v>
+        <v>26.1888</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.02</v>
       </c>
       <c r="I294" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.0711</v>
       </c>
       <c r="J294" t="n">
-        <v>2.1576</v>
+        <v>1.7064</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.8444</v>
+        <v>-0.8249</v>
       </c>
       <c r="J295" t="n">
-        <v>-20.2656</v>
+        <v>-19.7976</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.57</v>
       </c>
       <c r="I296" t="n">
-        <v>-1.0906</v>
+        <v>-1.1009</v>
       </c>
       <c r="J296" t="n">
-        <v>-26.1744</v>
+        <v>-26.4216</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.5</v>
       </c>
       <c r="I297" t="n">
-        <v>0.8719</v>
+        <v>0.8214</v>
       </c>
       <c r="J297" t="n">
-        <v>20.9256</v>
+        <v>19.7136</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.31</v>
       </c>
       <c r="I298" t="n">
-        <v>0.5928</v>
+        <v>0.533</v>
       </c>
       <c r="J298" t="n">
-        <v>14.2272</v>
+        <v>12.792</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.03</v>
       </c>
       <c r="I299" t="n">
-        <v>0.0921</v>
+        <v>0.0697</v>
       </c>
       <c r="J299" t="n">
-        <v>2.2104</v>
+        <v>1.6728</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2494</v>
+        <v>-0.2298</v>
       </c>
       <c r="J300" t="n">
-        <v>-5.9856</v>
+        <v>-5.5152</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.75</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3078</v>
+        <v>-0.291</v>
       </c>
       <c r="J301" t="n">
-        <v>-7.3872</v>
+        <v>-6.984</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.22</v>
       </c>
       <c r="I302" t="n">
-        <v>0.4868</v>
+        <v>0.4296</v>
       </c>
       <c r="J302" t="n">
-        <v>9.2492</v>
+        <v>8.1624</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.16</v>
       </c>
       <c r="I303" t="n">
-        <v>0.3812</v>
+        <v>0.3264</v>
       </c>
       <c r="J303" t="n">
-        <v>7.2428</v>
+        <v>6.2016</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.93</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1067</v>
+        <v>-0.0906</v>
       </c>
       <c r="J304" t="n">
-        <v>-2.0273</v>
+        <v>-1.7214</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.87</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.174</v>
+        <v>-0.1544</v>
       </c>
       <c r="J305" t="n">
-        <v>-3.306</v>
+        <v>-2.9336</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.47</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.543</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="J306" t="n">
-        <v>-10.317</v>
+        <v>-10.4481</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>2.1</v>
       </c>
       <c r="I307" t="n">
-        <v>1.8414</v>
+        <v>1.9119</v>
       </c>
       <c r="J307" t="n">
-        <v>34.9866</v>
+        <v>36.3261</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.73</v>
       </c>
       <c r="I308" t="n">
-        <v>1.3878</v>
+        <v>1.4124</v>
       </c>
       <c r="J308" t="n">
-        <v>26.3682</v>
+        <v>26.8356</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.95</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2519</v>
+        <v>-0.2169</v>
       </c>
       <c r="J309" t="n">
-        <v>-4.7861</v>
+        <v>-4.1211</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.87</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4719</v>
+        <v>-0.4341</v>
       </c>
       <c r="J310" t="n">
-        <v>-8.966100000000001</v>
+        <v>-8.2479</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.78</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6843</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="J311" t="n">
-        <v>-13.0017</v>
+        <v>-12.4792</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.7</v>
       </c>
       <c r="I312" t="n">
-        <v>1.1711</v>
+        <v>1.1766</v>
       </c>
       <c r="J312" t="n">
-        <v>22.2509</v>
+        <v>22.3554</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.03</v>
       </c>
       <c r="I313" t="n">
-        <v>0.1169</v>
+        <v>0.0871</v>
       </c>
       <c r="J313" t="n">
-        <v>2.2211</v>
+        <v>1.6549</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.3478</v>
+        <v>-0.3325</v>
       </c>
       <c r="J314" t="n">
-        <v>-6.6082</v>
+        <v>-6.3175</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.63</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.4021</v>
+        <v>-0.3912</v>
       </c>
       <c r="J315" t="n">
-        <v>-7.6399</v>
+        <v>-7.4328</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.47</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5409</v>
+        <v>-0.5471</v>
       </c>
       <c r="J316" t="n">
-        <v>-10.2771</v>
+        <v>-10.3949</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>2.22</v>
       </c>
       <c r="I317" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J317" t="n">
-        <v>36.8068</v>
+        <v>37.6542</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.3</v>
       </c>
       <c r="I318" t="n">
-        <v>0.7362</v>
+        <v>0.7147</v>
       </c>
       <c r="J318" t="n">
-        <v>13.9878</v>
+        <v>13.5793</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.25</v>
       </c>
       <c r="I319" t="n">
-        <v>0.6352</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="J319" t="n">
-        <v>12.0688</v>
+        <v>11.5786</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.07</v>
       </c>
       <c r="I320" t="n">
-        <v>0.2072</v>
+        <v>0.1778</v>
       </c>
       <c r="J320" t="n">
-        <v>3.9368</v>
+        <v>3.3782</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.6226</v>
+        <v>-0.5923</v>
       </c>
       <c r="J321" t="n">
-        <v>-11.8294</v>
+        <v>-11.2537</v>
       </c>
     </row>
   </sheetData>
